--- a/data/raw/01_FormatosRA_ReformaCurricular/Formato RA_NegIntl_VNAL.xlsx
+++ b/data/raw/01_FormatosRA_ReformaCurricular/Formato RA_NegIntl_VNAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Analisis_Curricular/data/raw/01_FormatosRA_ReformaCurricular/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4322" documentId="13_ncr:1_{D69AA465-0F16-4CD4-A28F-76D6A3A07DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B62A217-E1C8-4A62-A9D1-39C914F4ED71}"/>
+  <xr:revisionPtr revIDLastSave="4323" documentId="13_ncr:1_{D69AA465-0F16-4CD4-A28F-76D6A3A07DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59A4B676-F205-48F2-8319-70899FE2637C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BD68381A-4EB3-42BA-ADD5-D7B5B6C7E498}"/>
   </bookViews>
@@ -2146,6 +2146,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Gill Sans MT"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Analiza los instrumentos de política comercial que fomentan o restringen el intercambio con base en los elementos conceptuales para describir el impacto en el comercio internacional.
 </t>
@@ -2155,6 +2156,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Gill Sans MT"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -2164,6 +2166,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Gill Sans MT"/>
+        <family val="2"/>
       </rPr>
       <t>Describe las interrelaciones monetarias y macroeconómicas que definen la relación del sistema financiero nacional e internacional con base en los principios de la macroeconomía abierta, para analizar sus efectos a los diferentes agentes económicos y/o empresa.</t>
     </r>
@@ -3801,7 +3804,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3961,22 +3964,19 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Gill Sans MT"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Gill Sans MT"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Gill Sans MT"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Gill Sans MT"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -4578,7 +4578,7 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4599,94 +4599,17 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4698,6 +4621,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4750,6 +4685,71 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7940,7 +7940,7 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="3" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+  <tableStyles count="4" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Estilo de tabla 1" pivot="0" count="1" xr9:uid="{D31AC5D5-9EFB-4153-9086-9AA6037B7BF8}">
       <tableStyleElement type="headerRow" dxfId="151"/>
     </tableStyle>
@@ -7950,6 +7950,7 @@
     <tableStyle name="Estilo de tabla 3" pivot="0" count="1" xr9:uid="{BD8219D8-F95E-4ADD-BD98-5883EDA7E91C}">
       <tableStyleElement type="headerRow" dxfId="149"/>
     </tableStyle>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{4A312BA0-91AE-45AC-9AD9-2DF43CF6B7F6}"/>
   </tableStyles>
   <colors>
     <mruColors>
@@ -8938,16 +8939,16 @@
       <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="149" t="s">
+      <c r="E1" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="149"/>
-      <c r="G1" s="149"/>
-      <c r="H1" s="149" t="s">
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="149"/>
-      <c r="J1" s="149"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
       <c r="K1" s="119" t="s">
         <v>6</v>
       </c>
@@ -8988,16 +8989,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="129" t="s">
+      <c r="A3" s="128" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="129" t="s">
+      <c r="B3" s="128" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="150" t="s">
+      <c r="C3" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="141" t="s">
+      <c r="D3" s="126" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="16" t="s">
@@ -9009,24 +9010,24 @@
       <c r="G3" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="151" t="s">
+      <c r="H3" s="129" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="151" t="s">
+      <c r="I3" s="129" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="151" t="s">
+      <c r="J3" s="129" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="129" t="s">
+      <c r="K3" s="128" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="129"/>
-      <c r="B4" s="129"/>
-      <c r="C4" s="150"/>
-      <c r="D4" s="141"/>
+      <c r="A4" s="128"/>
+      <c r="B4" s="128"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="126"/>
       <c r="E4" s="21" t="s">
         <v>29</v>
       </c>
@@ -9036,16 +9037,16 @@
       <c r="G4" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="152"/>
-      <c r="I4" s="152"/>
-      <c r="J4" s="152"/>
-      <c r="K4" s="129"/>
+      <c r="H4" s="130"/>
+      <c r="I4" s="130"/>
+      <c r="J4" s="130"/>
+      <c r="K4" s="128"/>
     </row>
     <row r="5" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="129"/>
-      <c r="B5" s="129"/>
-      <c r="C5" s="150"/>
-      <c r="D5" s="141"/>
+      <c r="A5" s="128"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="126"/>
       <c r="E5" s="16" t="s">
         <v>32</v>
       </c>
@@ -9055,16 +9056,16 @@
       <c r="G5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="152"/>
-      <c r="I5" s="152"/>
-      <c r="J5" s="152"/>
-      <c r="K5" s="129"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="130"/>
+      <c r="J5" s="130"/>
+      <c r="K5" s="128"/>
     </row>
     <row r="6" spans="1:11" ht="54" x14ac:dyDescent="0.3">
-      <c r="A6" s="129"/>
-      <c r="B6" s="129"/>
-      <c r="C6" s="150"/>
-      <c r="D6" s="141"/>
+      <c r="A6" s="128"/>
+      <c r="B6" s="128"/>
+      <c r="C6" s="127"/>
+      <c r="D6" s="126"/>
       <c r="E6" s="98" t="s">
         <v>35</v>
       </c>
@@ -9074,16 +9075,16 @@
       <c r="G6" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="152"/>
-      <c r="I6" s="152"/>
-      <c r="J6" s="152"/>
-      <c r="K6" s="129"/>
+      <c r="H6" s="130"/>
+      <c r="I6" s="130"/>
+      <c r="J6" s="130"/>
+      <c r="K6" s="128"/>
     </row>
     <row r="7" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A7" s="129"/>
-      <c r="B7" s="129"/>
-      <c r="C7" s="150"/>
-      <c r="D7" s="141"/>
+      <c r="A7" s="128"/>
+      <c r="B7" s="128"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="126"/>
       <c r="E7" s="20" t="s">
         <v>38</v>
       </c>
@@ -9093,16 +9094,16 @@
       <c r="G7" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="152"/>
-      <c r="I7" s="152"/>
-      <c r="J7" s="152"/>
-      <c r="K7" s="129"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="130"/>
+      <c r="J7" s="130"/>
+      <c r="K7" s="128"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="129"/>
-      <c r="B8" s="129"/>
-      <c r="C8" s="150"/>
-      <c r="D8" s="141"/>
+      <c r="A8" s="128"/>
+      <c r="B8" s="128"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="126"/>
       <c r="H8" s="16"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -9182,15 +9183,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="153" t="s">
+      <c r="A1" s="131" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="154"/>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="154"/>
-      <c r="F1" s="154"/>
-      <c r="G1" s="154"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
     </row>
     <row r="2" spans="1:7" s="31" customFormat="1" ht="60" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
@@ -10020,16 +10021,16 @@
       <c r="A3" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="156" t="s">
+      <c r="B3" s="138" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="159" t="s">
+      <c r="C3" s="141" t="s">
         <v>123</v>
       </c>
       <c r="D3" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="E3" s="155" t="s">
+      <c r="E3" s="137" t="s">
         <v>125</v>
       </c>
       <c r="F3" s="17" t="s">
@@ -10040,12 +10041,12 @@
       <c r="A4" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="157"/>
-      <c r="C4" s="160"/>
+      <c r="B4" s="139"/>
+      <c r="C4" s="142"/>
       <c r="D4" s="46" t="s">
         <v>127</v>
       </c>
-      <c r="E4" s="141"/>
+      <c r="E4" s="126"/>
       <c r="F4" s="20" t="s">
         <v>128</v>
       </c>
@@ -10054,12 +10055,12 @@
       <c r="A5" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="B5" s="157"/>
-      <c r="C5" s="160"/>
+      <c r="B5" s="139"/>
+      <c r="C5" s="142"/>
       <c r="D5" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="E5" s="141"/>
+      <c r="E5" s="126"/>
       <c r="F5" s="20" t="s">
         <v>130</v>
       </c>
@@ -10068,26 +10069,26 @@
       <c r="A6" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="158"/>
-      <c r="C6" s="161"/>
+      <c r="B6" s="140"/>
+      <c r="C6" s="143"/>
       <c r="D6" s="48"/>
-      <c r="E6" s="142"/>
+      <c r="E6" s="134"/>
       <c r="F6" s="42"/>
     </row>
     <row r="7" spans="1:6" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="162" t="s">
+      <c r="B7" s="144" t="s">
         <v>131</v>
       </c>
-      <c r="C7" s="163" t="s">
+      <c r="C7" s="145" t="s">
         <v>132</v>
       </c>
       <c r="D7" s="49" t="s">
         <v>124</v>
       </c>
-      <c r="E7" s="144" t="s">
+      <c r="E7" s="133" t="s">
         <v>133</v>
       </c>
       <c r="F7" s="50" t="s">
@@ -10098,12 +10099,12 @@
       <c r="A8" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="B8" s="157"/>
-      <c r="C8" s="160"/>
+      <c r="B8" s="139"/>
+      <c r="C8" s="142"/>
       <c r="D8" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="E8" s="141"/>
+      <c r="E8" s="126"/>
       <c r="F8" s="20" t="s">
         <v>128</v>
       </c>
@@ -10112,12 +10113,12 @@
       <c r="A9" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="B9" s="157"/>
-      <c r="C9" s="160"/>
+      <c r="B9" s="139"/>
+      <c r="C9" s="142"/>
       <c r="D9" s="46" t="s">
         <v>135</v>
       </c>
-      <c r="E9" s="141"/>
+      <c r="E9" s="126"/>
       <c r="F9" s="20" t="s">
         <v>130</v>
       </c>
@@ -10126,36 +10127,36 @@
       <c r="A10" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="B10" s="157"/>
-      <c r="C10" s="160"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="142"/>
       <c r="D10" s="46"/>
-      <c r="E10" s="141"/>
+      <c r="E10" s="126"/>
       <c r="F10" s="20"/>
     </row>
     <row r="11" spans="1:6" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="B11" s="158"/>
-      <c r="C11" s="161"/>
+      <c r="B11" s="140"/>
+      <c r="C11" s="143"/>
       <c r="D11" s="48"/>
-      <c r="E11" s="142"/>
+      <c r="E11" s="134"/>
       <c r="F11" s="42"/>
     </row>
     <row r="12" spans="1:6" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="B12" s="162" t="s">
+      <c r="B12" s="144" t="s">
         <v>136</v>
       </c>
-      <c r="C12" s="164" t="s">
+      <c r="C12" s="146" t="s">
         <v>137</v>
       </c>
       <c r="D12" s="49" t="s">
         <v>124</v>
       </c>
-      <c r="E12" s="144" t="s">
+      <c r="E12" s="133" t="s">
         <v>138</v>
       </c>
       <c r="F12" s="50" t="s">
@@ -10166,12 +10167,12 @@
       <c r="A13" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="B13" s="157"/>
-      <c r="C13" s="152"/>
+      <c r="B13" s="139"/>
+      <c r="C13" s="130"/>
       <c r="D13" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="E13" s="141"/>
+      <c r="E13" s="126"/>
       <c r="F13" s="20" t="s">
         <v>128</v>
       </c>
@@ -10180,12 +10181,12 @@
       <c r="A14" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="B14" s="157"/>
-      <c r="C14" s="152"/>
+      <c r="B14" s="139"/>
+      <c r="C14" s="130"/>
       <c r="D14" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="E14" s="141"/>
+      <c r="E14" s="126"/>
       <c r="F14" s="20" t="s">
         <v>130</v>
       </c>
@@ -10194,36 +10195,36 @@
       <c r="A15" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="B15" s="157"/>
-      <c r="C15" s="152"/>
+      <c r="B15" s="139"/>
+      <c r="C15" s="130"/>
       <c r="D15" s="46"/>
-      <c r="E15" s="141"/>
+      <c r="E15" s="126"/>
       <c r="F15" s="20"/>
     </row>
     <row r="16" spans="1:6" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="B16" s="158"/>
-      <c r="C16" s="165"/>
+      <c r="B16" s="140"/>
+      <c r="C16" s="147"/>
       <c r="D16" s="48"/>
-      <c r="E16" s="142"/>
+      <c r="E16" s="134"/>
       <c r="F16" s="42"/>
     </row>
     <row r="17" spans="1:6" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="B17" s="128" t="s">
+      <c r="B17" s="135" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="128" t="s">
+      <c r="C17" s="135" t="s">
         <v>141</v>
       </c>
       <c r="D17" s="46" t="s">
         <v>124</v>
       </c>
-      <c r="E17" s="144" t="s">
+      <c r="E17" s="133" t="s">
         <v>138</v>
       </c>
       <c r="F17" s="20" t="s">
@@ -10234,12 +10235,12 @@
       <c r="A18" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="B18" s="129"/>
-      <c r="C18" s="129"/>
+      <c r="B18" s="128"/>
+      <c r="C18" s="128"/>
       <c r="D18" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="E18" s="141"/>
+      <c r="E18" s="126"/>
       <c r="F18" s="20" t="s">
         <v>128</v>
       </c>
@@ -10248,12 +10249,12 @@
       <c r="A19" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="129"/>
-      <c r="C19" s="129"/>
+      <c r="B19" s="128"/>
+      <c r="C19" s="128"/>
       <c r="D19" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="E19" s="141"/>
+      <c r="E19" s="126"/>
       <c r="F19" s="20" t="s">
         <v>130</v>
       </c>
@@ -10262,34 +10263,34 @@
       <c r="A20" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="B20" s="129"/>
-      <c r="C20" s="129"/>
-      <c r="E20" s="141"/>
+      <c r="B20" s="128"/>
+      <c r="C20" s="128"/>
+      <c r="E20" s="126"/>
     </row>
     <row r="21" spans="1:6" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="B21" s="130"/>
-      <c r="C21" s="130"/>
+      <c r="B21" s="136"/>
+      <c r="C21" s="136"/>
       <c r="D21" s="43"/>
-      <c r="E21" s="142"/>
+      <c r="E21" s="134"/>
       <c r="F21" s="43"/>
     </row>
     <row r="22" spans="1:6" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="B22" s="128" t="s">
+      <c r="B22" s="135" t="s">
         <v>143</v>
       </c>
-      <c r="C22" s="144" t="s">
+      <c r="C22" s="133" t="s">
         <v>144</v>
       </c>
       <c r="D22" s="49" t="s">
         <v>124</v>
       </c>
-      <c r="E22" s="144" t="s">
+      <c r="E22" s="133" t="s">
         <v>145</v>
       </c>
       <c r="F22" s="50" t="s">
@@ -10300,12 +10301,12 @@
       <c r="A23" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="B23" s="129"/>
-      <c r="C23" s="141"/>
+      <c r="B23" s="128"/>
+      <c r="C23" s="126"/>
       <c r="D23" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="E23" s="141"/>
+      <c r="E23" s="126"/>
       <c r="F23" s="20" t="s">
         <v>128</v>
       </c>
@@ -10314,12 +10315,12 @@
       <c r="A24" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="B24" s="129"/>
-      <c r="C24" s="141"/>
+      <c r="B24" s="128"/>
+      <c r="C24" s="126"/>
       <c r="D24" s="46" t="s">
         <v>146</v>
       </c>
-      <c r="E24" s="141"/>
+      <c r="E24" s="126"/>
       <c r="F24" s="20" t="s">
         <v>130</v>
       </c>
@@ -10328,34 +10329,34 @@
       <c r="A25" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="B25" s="129"/>
-      <c r="C25" s="141"/>
-      <c r="E25" s="141"/>
+      <c r="B25" s="128"/>
+      <c r="C25" s="126"/>
+      <c r="E25" s="126"/>
     </row>
     <row r="26" spans="1:6" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="B26" s="130"/>
-      <c r="C26" s="142"/>
+      <c r="B26" s="136"/>
+      <c r="C26" s="134"/>
       <c r="D26" s="43"/>
-      <c r="E26" s="142"/>
+      <c r="E26" s="134"/>
       <c r="F26" s="43"/>
     </row>
     <row r="27" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A27" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="B27" s="166" t="s">
+      <c r="B27" s="148" t="s">
         <v>147</v>
       </c>
-      <c r="C27" s="169" t="s">
+      <c r="C27" s="151" t="s">
         <v>148</v>
       </c>
       <c r="D27" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="E27" s="144" t="s">
+      <c r="E27" s="133" t="s">
         <v>149</v>
       </c>
       <c r="F27" s="12" t="s">
@@ -10366,12 +10367,12 @@
       <c r="A28" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="B28" s="167"/>
-      <c r="C28" s="150"/>
+      <c r="B28" s="149"/>
+      <c r="C28" s="127"/>
       <c r="D28" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="E28" s="141"/>
+      <c r="E28" s="126"/>
       <c r="F28" s="12" t="s">
         <v>130</v>
       </c>
@@ -10380,10 +10381,10 @@
       <c r="A29" s="111" t="s">
         <v>100</v>
       </c>
-      <c r="B29" s="168"/>
-      <c r="C29" s="170"/>
+      <c r="B29" s="150"/>
+      <c r="C29" s="152"/>
       <c r="D29" s="112"/>
-      <c r="E29" s="171"/>
+      <c r="E29" s="153"/>
       <c r="F29" s="112"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -10476,11 +10477,11 @@
       <c r="F1" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="G1" s="148" t="s">
+      <c r="G1" s="171" t="s">
         <v>157</v>
       </c>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
       <c r="J1" s="15" t="s">
         <v>158</v>
       </c>
@@ -10567,48 +10568,48 @@
       <c r="B3" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="146" t="s">
+      <c r="C3" s="169" t="s">
         <v>182</v>
       </c>
-      <c r="D3" s="146" t="s">
+      <c r="D3" s="169" t="s">
         <v>183</v>
       </c>
-      <c r="E3" s="131" t="s">
+      <c r="E3" s="157" t="s">
         <v>184</v>
       </c>
-      <c r="F3" s="146" t="s">
+      <c r="F3" s="169" t="s">
         <v>185</v>
       </c>
-      <c r="G3" s="146"/>
-      <c r="H3" s="146" t="s">
+      <c r="G3" s="169"/>
+      <c r="H3" s="169" t="s">
         <v>186</v>
       </c>
-      <c r="I3" s="146"/>
-      <c r="J3" s="146">
+      <c r="I3" s="169"/>
+      <c r="J3" s="169">
         <v>3</v>
       </c>
-      <c r="K3" s="146">
+      <c r="K3" s="169">
         <f>J3*12</f>
         <v>36</v>
       </c>
-      <c r="L3" s="146">
+      <c r="L3" s="169">
         <f>36*J3</f>
         <v>108</v>
       </c>
-      <c r="M3" s="146">
+      <c r="M3" s="169">
         <f>SUM(K3:L3)</f>
         <v>144</v>
       </c>
-      <c r="N3" s="131" t="s">
+      <c r="N3" s="157" t="s">
         <v>187</v>
       </c>
-      <c r="O3" s="131" t="s">
+      <c r="O3" s="157" t="s">
         <v>188</v>
       </c>
-      <c r="P3" s="131" t="s">
+      <c r="P3" s="157" t="s">
         <v>189</v>
       </c>
-      <c r="Q3" s="131" t="s">
+      <c r="Q3" s="157" t="s">
         <v>190</v>
       </c>
     </row>
@@ -10620,21 +10621,21 @@
       <c r="B4" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="146"/>
-      <c r="D4" s="146"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="146"/>
-      <c r="K4" s="146"/>
-      <c r="L4" s="146"/>
-      <c r="M4" s="146"/>
-      <c r="N4" s="131"/>
-      <c r="O4" s="131"/>
-      <c r="P4" s="131"/>
-      <c r="Q4" s="131"/>
+      <c r="C4" s="169"/>
+      <c r="D4" s="169"/>
+      <c r="E4" s="157"/>
+      <c r="F4" s="169"/>
+      <c r="G4" s="169"/>
+      <c r="H4" s="169"/>
+      <c r="I4" s="169"/>
+      <c r="J4" s="169"/>
+      <c r="K4" s="169"/>
+      <c r="L4" s="169"/>
+      <c r="M4" s="169"/>
+      <c r="N4" s="157"/>
+      <c r="O4" s="157"/>
+      <c r="P4" s="157"/>
+      <c r="Q4" s="157"/>
     </row>
     <row r="5" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="97" t="str">
@@ -10644,21 +10645,21 @@
       <c r="B5" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="147"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="132"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="147"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
-      <c r="L5" s="147"/>
-      <c r="M5" s="147"/>
-      <c r="N5" s="132"/>
-      <c r="O5" s="132"/>
-      <c r="P5" s="132"/>
-      <c r="Q5" s="132"/>
+      <c r="C5" s="170"/>
+      <c r="D5" s="170"/>
+      <c r="E5" s="158"/>
+      <c r="F5" s="170"/>
+      <c r="G5" s="170"/>
+      <c r="H5" s="170"/>
+      <c r="I5" s="170"/>
+      <c r="J5" s="170"/>
+      <c r="K5" s="170"/>
+      <c r="L5" s="170"/>
+      <c r="M5" s="170"/>
+      <c r="N5" s="158"/>
+      <c r="O5" s="158"/>
+      <c r="P5" s="158"/>
+      <c r="Q5" s="158"/>
     </row>
     <row r="6" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="str">
@@ -10668,48 +10669,48 @@
       <c r="B6" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="145" t="s">
+      <c r="C6" s="168" t="s">
         <v>182</v>
       </c>
-      <c r="D6" s="128" t="s">
+      <c r="D6" s="135" t="s">
         <v>191</v>
       </c>
-      <c r="E6" s="144" t="s">
+      <c r="E6" s="133" t="s">
         <v>192</v>
       </c>
-      <c r="F6" s="128" t="s">
+      <c r="F6" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="G6" s="128"/>
-      <c r="H6" s="128" t="s">
+      <c r="G6" s="135"/>
+      <c r="H6" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I6" s="128"/>
-      <c r="J6" s="128">
+      <c r="I6" s="135"/>
+      <c r="J6" s="135">
         <v>3</v>
       </c>
-      <c r="K6" s="128">
+      <c r="K6" s="135">
         <f>J6*12</f>
         <v>36</v>
       </c>
-      <c r="L6" s="128">
+      <c r="L6" s="135">
         <f>36*J6</f>
         <v>108</v>
       </c>
-      <c r="M6" s="128">
+      <c r="M6" s="135">
         <f>SUM(K6:L6)</f>
         <v>144</v>
       </c>
-      <c r="N6" s="144" t="s">
+      <c r="N6" s="133" t="s">
         <v>194</v>
       </c>
-      <c r="O6" s="144" t="s">
+      <c r="O6" s="133" t="s">
         <v>195</v>
       </c>
-      <c r="P6" s="144" t="s">
+      <c r="P6" s="133" t="s">
         <v>196</v>
       </c>
-      <c r="Q6" s="144" t="s">
+      <c r="Q6" s="133" t="s">
         <v>190</v>
       </c>
     </row>
@@ -10721,21 +10722,21 @@
       <c r="B7" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="146"/>
-      <c r="D7" s="129"/>
-      <c r="E7" s="141"/>
-      <c r="F7" s="129"/>
-      <c r="G7" s="129"/>
-      <c r="H7" s="129"/>
-      <c r="I7" s="129"/>
-      <c r="J7" s="129"/>
-      <c r="K7" s="129"/>
-      <c r="L7" s="129"/>
-      <c r="M7" s="129"/>
-      <c r="N7" s="141"/>
-      <c r="O7" s="141"/>
-      <c r="P7" s="141"/>
-      <c r="Q7" s="141"/>
+      <c r="C7" s="169"/>
+      <c r="D7" s="128"/>
+      <c r="E7" s="126"/>
+      <c r="F7" s="128"/>
+      <c r="G7" s="128"/>
+      <c r="H7" s="128"/>
+      <c r="I7" s="128"/>
+      <c r="J7" s="128"/>
+      <c r="K7" s="128"/>
+      <c r="L7" s="128"/>
+      <c r="M7" s="128"/>
+      <c r="N7" s="126"/>
+      <c r="O7" s="126"/>
+      <c r="P7" s="126"/>
+      <c r="Q7" s="126"/>
     </row>
     <row r="8" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="97" t="str">
@@ -10745,21 +10746,21 @@
       <c r="B8" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="147"/>
-      <c r="D8" s="130"/>
-      <c r="E8" s="142"/>
-      <c r="F8" s="130"/>
-      <c r="G8" s="130"/>
-      <c r="H8" s="130"/>
-      <c r="I8" s="130"/>
-      <c r="J8" s="130"/>
-      <c r="K8" s="130"/>
-      <c r="L8" s="130"/>
-      <c r="M8" s="130"/>
-      <c r="N8" s="142"/>
-      <c r="O8" s="142"/>
-      <c r="P8" s="142"/>
-      <c r="Q8" s="142"/>
+      <c r="C8" s="170"/>
+      <c r="D8" s="136"/>
+      <c r="E8" s="134"/>
+      <c r="F8" s="136"/>
+      <c r="G8" s="136"/>
+      <c r="H8" s="136"/>
+      <c r="I8" s="136"/>
+      <c r="J8" s="136"/>
+      <c r="K8" s="136"/>
+      <c r="L8" s="136"/>
+      <c r="M8" s="136"/>
+      <c r="N8" s="134"/>
+      <c r="O8" s="134"/>
+      <c r="P8" s="134"/>
+      <c r="Q8" s="134"/>
     </row>
     <row r="9" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="str">
@@ -10769,48 +10770,48 @@
       <c r="B9" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C9" s="145" t="s">
+      <c r="C9" s="168" t="s">
         <v>182</v>
       </c>
-      <c r="D9" s="145" t="s">
+      <c r="D9" s="168" t="s">
         <v>197</v>
       </c>
-      <c r="E9" s="125" t="s">
+      <c r="E9" s="154" t="s">
         <v>198</v>
       </c>
-      <c r="F9" s="145" t="s">
+      <c r="F9" s="168" t="s">
         <v>185</v>
       </c>
-      <c r="G9" s="145"/>
-      <c r="H9" s="145" t="s">
+      <c r="G9" s="168"/>
+      <c r="H9" s="168" t="s">
         <v>186</v>
       </c>
-      <c r="I9" s="145"/>
-      <c r="J9" s="145">
+      <c r="I9" s="168"/>
+      <c r="J9" s="168">
         <v>3</v>
       </c>
-      <c r="K9" s="145">
+      <c r="K9" s="168">
         <f>J9*12</f>
         <v>36</v>
       </c>
-      <c r="L9" s="145">
+      <c r="L9" s="168">
         <f>36*J9</f>
         <v>108</v>
       </c>
-      <c r="M9" s="145">
+      <c r="M9" s="168">
         <f>SUM(K9:L9)</f>
         <v>144</v>
       </c>
-      <c r="N9" s="125" t="s">
+      <c r="N9" s="154" t="s">
         <v>199</v>
       </c>
-      <c r="O9" s="125" t="s">
+      <c r="O9" s="154" t="s">
         <v>200</v>
       </c>
-      <c r="P9" s="125" t="s">
+      <c r="P9" s="154" t="s">
         <v>201</v>
       </c>
-      <c r="Q9" s="125" t="s">
+      <c r="Q9" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -10822,21 +10823,21 @@
       <c r="B10" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C10" s="146"/>
-      <c r="D10" s="146"/>
-      <c r="E10" s="126"/>
-      <c r="F10" s="146"/>
-      <c r="G10" s="146"/>
-      <c r="H10" s="146"/>
-      <c r="I10" s="146"/>
-      <c r="J10" s="146"/>
-      <c r="K10" s="146"/>
-      <c r="L10" s="146"/>
-      <c r="M10" s="146"/>
-      <c r="N10" s="126"/>
-      <c r="O10" s="126"/>
-      <c r="P10" s="126"/>
-      <c r="Q10" s="126"/>
+      <c r="C10" s="169"/>
+      <c r="D10" s="169"/>
+      <c r="E10" s="155"/>
+      <c r="F10" s="169"/>
+      <c r="G10" s="169"/>
+      <c r="H10" s="169"/>
+      <c r="I10" s="169"/>
+      <c r="J10" s="169"/>
+      <c r="K10" s="169"/>
+      <c r="L10" s="169"/>
+      <c r="M10" s="169"/>
+      <c r="N10" s="155"/>
+      <c r="O10" s="155"/>
+      <c r="P10" s="155"/>
+      <c r="Q10" s="155"/>
     </row>
     <row r="11" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="str">
@@ -10846,21 +10847,21 @@
       <c r="B11" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="146"/>
-      <c r="D11" s="146"/>
-      <c r="E11" s="126"/>
-      <c r="F11" s="146"/>
-      <c r="G11" s="146"/>
-      <c r="H11" s="146"/>
-      <c r="I11" s="146"/>
-      <c r="J11" s="146"/>
-      <c r="K11" s="146"/>
-      <c r="L11" s="146"/>
-      <c r="M11" s="146"/>
-      <c r="N11" s="126"/>
-      <c r="O11" s="126"/>
-      <c r="P11" s="126"/>
-      <c r="Q11" s="126"/>
+      <c r="C11" s="169"/>
+      <c r="D11" s="169"/>
+      <c r="E11" s="155"/>
+      <c r="F11" s="169"/>
+      <c r="G11" s="169"/>
+      <c r="H11" s="169"/>
+      <c r="I11" s="169"/>
+      <c r="J11" s="169"/>
+      <c r="K11" s="169"/>
+      <c r="L11" s="169"/>
+      <c r="M11" s="169"/>
+      <c r="N11" s="155"/>
+      <c r="O11" s="155"/>
+      <c r="P11" s="155"/>
+      <c r="Q11" s="155"/>
     </row>
     <row r="12" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="97" t="str">
@@ -10870,21 +10871,21 @@
       <c r="B12" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="147"/>
-      <c r="D12" s="147"/>
-      <c r="E12" s="127"/>
-      <c r="F12" s="147"/>
-      <c r="G12" s="147"/>
-      <c r="H12" s="147"/>
-      <c r="I12" s="147"/>
-      <c r="J12" s="147"/>
-      <c r="K12" s="147"/>
-      <c r="L12" s="147"/>
-      <c r="M12" s="147"/>
-      <c r="N12" s="127"/>
-      <c r="O12" s="127"/>
-      <c r="P12" s="127"/>
-      <c r="Q12" s="127"/>
+      <c r="C12" s="170"/>
+      <c r="D12" s="170"/>
+      <c r="E12" s="156"/>
+      <c r="F12" s="170"/>
+      <c r="G12" s="170"/>
+      <c r="H12" s="170"/>
+      <c r="I12" s="170"/>
+      <c r="J12" s="170"/>
+      <c r="K12" s="170"/>
+      <c r="L12" s="170"/>
+      <c r="M12" s="170"/>
+      <c r="N12" s="156"/>
+      <c r="O12" s="156"/>
+      <c r="P12" s="156"/>
+      <c r="Q12" s="156"/>
     </row>
     <row r="13" spans="1:17" s="52" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A13" s="107" t="str">
@@ -11000,48 +11001,48 @@
       <c r="B15" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C15" s="128">
+      <c r="C15" s="135">
         <v>2</v>
       </c>
-      <c r="D15" s="128" t="s">
+      <c r="D15" s="135" t="s">
         <v>212</v>
       </c>
-      <c r="E15" s="125" t="s">
+      <c r="E15" s="154" t="s">
         <v>213</v>
       </c>
-      <c r="F15" s="128" t="s">
+      <c r="F15" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G15" s="128"/>
-      <c r="H15" s="128" t="s">
+      <c r="G15" s="135"/>
+      <c r="H15" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I15" s="128"/>
-      <c r="J15" s="128">
+      <c r="I15" s="135"/>
+      <c r="J15" s="135">
         <v>3</v>
       </c>
-      <c r="K15" s="128">
+      <c r="K15" s="135">
         <f>J15*12</f>
         <v>36</v>
       </c>
-      <c r="L15" s="128">
+      <c r="L15" s="135">
         <f>36*J15</f>
         <v>108</v>
       </c>
-      <c r="M15" s="128">
+      <c r="M15" s="135">
         <f>SUM(K15:L15)</f>
         <v>144</v>
       </c>
-      <c r="N15" s="125" t="s">
+      <c r="N15" s="154" t="s">
         <v>214</v>
       </c>
-      <c r="O15" s="125" t="s">
+      <c r="O15" s="154" t="s">
         <v>188</v>
       </c>
-      <c r="P15" s="125" t="s">
+      <c r="P15" s="154" t="s">
         <v>189</v>
       </c>
-      <c r="Q15" s="125" t="s">
+      <c r="Q15" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -11053,21 +11054,21 @@
       <c r="B16" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="129"/>
-      <c r="D16" s="129"/>
-      <c r="E16" s="126"/>
-      <c r="F16" s="129"/>
-      <c r="G16" s="129"/>
-      <c r="H16" s="129"/>
-      <c r="I16" s="129"/>
-      <c r="J16" s="129"/>
-      <c r="K16" s="129"/>
-      <c r="L16" s="129"/>
-      <c r="M16" s="129"/>
-      <c r="N16" s="126"/>
-      <c r="O16" s="126"/>
-      <c r="P16" s="126"/>
-      <c r="Q16" s="126"/>
+      <c r="C16" s="128"/>
+      <c r="D16" s="128"/>
+      <c r="E16" s="155"/>
+      <c r="F16" s="128"/>
+      <c r="G16" s="128"/>
+      <c r="H16" s="128"/>
+      <c r="I16" s="128"/>
+      <c r="J16" s="128"/>
+      <c r="K16" s="128"/>
+      <c r="L16" s="128"/>
+      <c r="M16" s="128"/>
+      <c r="N16" s="155"/>
+      <c r="O16" s="155"/>
+      <c r="P16" s="155"/>
+      <c r="Q16" s="155"/>
     </row>
     <row r="17" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="113" t="str">
@@ -11077,21 +11078,21 @@
       <c r="B17" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="129"/>
-      <c r="D17" s="129"/>
-      <c r="E17" s="126"/>
-      <c r="F17" s="129"/>
-      <c r="G17" s="129"/>
-      <c r="H17" s="129"/>
-      <c r="I17" s="129"/>
-      <c r="J17" s="129"/>
-      <c r="K17" s="129"/>
-      <c r="L17" s="129"/>
-      <c r="M17" s="129"/>
-      <c r="N17" s="126"/>
-      <c r="O17" s="126"/>
-      <c r="P17" s="126"/>
-      <c r="Q17" s="126"/>
+      <c r="C17" s="128"/>
+      <c r="D17" s="128"/>
+      <c r="E17" s="155"/>
+      <c r="F17" s="128"/>
+      <c r="G17" s="128"/>
+      <c r="H17" s="128"/>
+      <c r="I17" s="128"/>
+      <c r="J17" s="128"/>
+      <c r="K17" s="128"/>
+      <c r="L17" s="128"/>
+      <c r="M17" s="128"/>
+      <c r="N17" s="155"/>
+      <c r="O17" s="155"/>
+      <c r="P17" s="155"/>
+      <c r="Q17" s="155"/>
     </row>
     <row r="18" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A18" s="23" t="str">
@@ -11101,48 +11102,48 @@
       <c r="B18" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="128">
+      <c r="C18" s="135">
         <v>2</v>
       </c>
-      <c r="D18" s="128" t="s">
+      <c r="D18" s="135" t="s">
         <v>215</v>
       </c>
-      <c r="E18" s="125" t="s">
+      <c r="E18" s="154" t="s">
         <v>216</v>
       </c>
-      <c r="F18" s="128" t="s">
+      <c r="F18" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="G18" s="128"/>
-      <c r="H18" s="128" t="s">
+      <c r="G18" s="135"/>
+      <c r="H18" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I18" s="128"/>
-      <c r="J18" s="128">
+      <c r="I18" s="135"/>
+      <c r="J18" s="135">
         <v>3</v>
       </c>
-      <c r="K18" s="128">
+      <c r="K18" s="135">
         <f>J18*12</f>
         <v>36</v>
       </c>
-      <c r="L18" s="128">
+      <c r="L18" s="135">
         <f>36*J18</f>
         <v>108</v>
       </c>
-      <c r="M18" s="128">
+      <c r="M18" s="135">
         <f>SUM(K18:L18)</f>
         <v>144</v>
       </c>
-      <c r="N18" s="125" t="s">
+      <c r="N18" s="154" t="s">
         <v>217</v>
       </c>
-      <c r="O18" s="125" t="s">
+      <c r="O18" s="154" t="s">
         <v>195</v>
       </c>
-      <c r="P18" s="125" t="s">
+      <c r="P18" s="154" t="s">
         <v>196</v>
       </c>
-      <c r="Q18" s="125" t="s">
+      <c r="Q18" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -11154,21 +11155,21 @@
       <c r="B19" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="129"/>
-      <c r="D19" s="129"/>
-      <c r="E19" s="126"/>
-      <c r="F19" s="129"/>
-      <c r="G19" s="129"/>
-      <c r="H19" s="129"/>
-      <c r="I19" s="129"/>
-      <c r="J19" s="129"/>
-      <c r="K19" s="129"/>
-      <c r="L19" s="129"/>
-      <c r="M19" s="129"/>
-      <c r="N19" s="126"/>
-      <c r="O19" s="126"/>
-      <c r="P19" s="126"/>
-      <c r="Q19" s="126"/>
+      <c r="C19" s="128"/>
+      <c r="D19" s="128"/>
+      <c r="E19" s="155"/>
+      <c r="F19" s="128"/>
+      <c r="G19" s="128"/>
+      <c r="H19" s="128"/>
+      <c r="I19" s="128"/>
+      <c r="J19" s="128"/>
+      <c r="K19" s="128"/>
+      <c r="L19" s="128"/>
+      <c r="M19" s="128"/>
+      <c r="N19" s="155"/>
+      <c r="O19" s="155"/>
+      <c r="P19" s="155"/>
+      <c r="Q19" s="155"/>
     </row>
     <row r="20" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A20" s="23" t="str">
@@ -11178,21 +11179,21 @@
       <c r="B20" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C20" s="129"/>
-      <c r="D20" s="129"/>
-      <c r="E20" s="126"/>
-      <c r="F20" s="129"/>
-      <c r="G20" s="129"/>
-      <c r="H20" s="129"/>
-      <c r="I20" s="129"/>
-      <c r="J20" s="129"/>
-      <c r="K20" s="129"/>
-      <c r="L20" s="129"/>
-      <c r="M20" s="129"/>
-      <c r="N20" s="126"/>
-      <c r="O20" s="126"/>
-      <c r="P20" s="126"/>
-      <c r="Q20" s="126"/>
+      <c r="C20" s="128"/>
+      <c r="D20" s="128"/>
+      <c r="E20" s="155"/>
+      <c r="F20" s="128"/>
+      <c r="G20" s="128"/>
+      <c r="H20" s="128"/>
+      <c r="I20" s="128"/>
+      <c r="J20" s="128"/>
+      <c r="K20" s="128"/>
+      <c r="L20" s="128"/>
+      <c r="M20" s="128"/>
+      <c r="N20" s="155"/>
+      <c r="O20" s="155"/>
+      <c r="P20" s="155"/>
+      <c r="Q20" s="155"/>
     </row>
     <row r="21" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A21" s="23" t="str">
@@ -11202,21 +11203,21 @@
       <c r="B21" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C21" s="129"/>
-      <c r="D21" s="129"/>
-      <c r="E21" s="126"/>
-      <c r="F21" s="129"/>
-      <c r="G21" s="129"/>
-      <c r="H21" s="129"/>
-      <c r="I21" s="129"/>
-      <c r="J21" s="129"/>
-      <c r="K21" s="129"/>
-      <c r="L21" s="129"/>
-      <c r="M21" s="129"/>
-      <c r="N21" s="126"/>
-      <c r="O21" s="126"/>
-      <c r="P21" s="126"/>
-      <c r="Q21" s="126"/>
+      <c r="C21" s="128"/>
+      <c r="D21" s="128"/>
+      <c r="E21" s="155"/>
+      <c r="F21" s="128"/>
+      <c r="G21" s="128"/>
+      <c r="H21" s="128"/>
+      <c r="I21" s="128"/>
+      <c r="J21" s="128"/>
+      <c r="K21" s="128"/>
+      <c r="L21" s="128"/>
+      <c r="M21" s="128"/>
+      <c r="N21" s="155"/>
+      <c r="O21" s="155"/>
+      <c r="P21" s="155"/>
+      <c r="Q21" s="155"/>
     </row>
     <row r="22" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A22" s="97" t="str">
@@ -11226,21 +11227,21 @@
       <c r="B22" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C22" s="130"/>
-      <c r="D22" s="130"/>
-      <c r="E22" s="127"/>
-      <c r="F22" s="130"/>
-      <c r="G22" s="130"/>
-      <c r="H22" s="130"/>
-      <c r="I22" s="130"/>
-      <c r="J22" s="130"/>
-      <c r="K22" s="130"/>
-      <c r="L22" s="130"/>
-      <c r="M22" s="130"/>
-      <c r="N22" s="127"/>
-      <c r="O22" s="127"/>
-      <c r="P22" s="127"/>
-      <c r="Q22" s="127"/>
+      <c r="C22" s="136"/>
+      <c r="D22" s="136"/>
+      <c r="E22" s="156"/>
+      <c r="F22" s="136"/>
+      <c r="G22" s="136"/>
+      <c r="H22" s="136"/>
+      <c r="I22" s="136"/>
+      <c r="J22" s="136"/>
+      <c r="K22" s="136"/>
+      <c r="L22" s="136"/>
+      <c r="M22" s="136"/>
+      <c r="N22" s="156"/>
+      <c r="O22" s="156"/>
+      <c r="P22" s="156"/>
+      <c r="Q22" s="156"/>
     </row>
     <row r="23" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A23" s="23" t="str">
@@ -11250,48 +11251,48 @@
       <c r="B23" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C23" s="128">
+      <c r="C23" s="135">
         <v>2</v>
       </c>
-      <c r="D23" s="128" t="s">
+      <c r="D23" s="135" t="s">
         <v>218</v>
       </c>
-      <c r="E23" s="125" t="s">
+      <c r="E23" s="154" t="s">
         <v>219</v>
       </c>
-      <c r="F23" s="128" t="s">
+      <c r="F23" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G23" s="128"/>
-      <c r="H23" s="128" t="s">
+      <c r="G23" s="135"/>
+      <c r="H23" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I23" s="128"/>
-      <c r="J23" s="128">
+      <c r="I23" s="135"/>
+      <c r="J23" s="135">
         <v>3</v>
       </c>
-      <c r="K23" s="128">
+      <c r="K23" s="135">
         <f>J23*12</f>
         <v>36</v>
       </c>
-      <c r="L23" s="128">
+      <c r="L23" s="135">
         <f>36*J23</f>
         <v>108</v>
       </c>
-      <c r="M23" s="128">
+      <c r="M23" s="135">
         <f>SUM(K23:L23)</f>
         <v>144</v>
       </c>
-      <c r="N23" s="125" t="s">
+      <c r="N23" s="154" t="s">
         <v>220</v>
       </c>
-      <c r="O23" s="125" t="s">
+      <c r="O23" s="154" t="s">
         <v>221</v>
       </c>
-      <c r="P23" s="125" t="s">
+      <c r="P23" s="154" t="s">
         <v>222</v>
       </c>
-      <c r="Q23" s="125" t="s">
+      <c r="Q23" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -11303,21 +11304,21 @@
       <c r="B24" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C24" s="129"/>
-      <c r="D24" s="129"/>
-      <c r="E24" s="126"/>
-      <c r="F24" s="129"/>
-      <c r="G24" s="129"/>
-      <c r="H24" s="129"/>
-      <c r="I24" s="129"/>
-      <c r="J24" s="129"/>
-      <c r="K24" s="129"/>
-      <c r="L24" s="129"/>
-      <c r="M24" s="129"/>
-      <c r="N24" s="126"/>
-      <c r="O24" s="126"/>
-      <c r="P24" s="126"/>
-      <c r="Q24" s="126"/>
+      <c r="C24" s="128"/>
+      <c r="D24" s="128"/>
+      <c r="E24" s="155"/>
+      <c r="F24" s="128"/>
+      <c r="G24" s="128"/>
+      <c r="H24" s="128"/>
+      <c r="I24" s="128"/>
+      <c r="J24" s="128"/>
+      <c r="K24" s="128"/>
+      <c r="L24" s="128"/>
+      <c r="M24" s="128"/>
+      <c r="N24" s="155"/>
+      <c r="O24" s="155"/>
+      <c r="P24" s="155"/>
+      <c r="Q24" s="155"/>
     </row>
     <row r="25" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A25" s="23" t="str">
@@ -11327,21 +11328,21 @@
       <c r="B25" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="129"/>
-      <c r="D25" s="129"/>
-      <c r="E25" s="126"/>
-      <c r="F25" s="129"/>
-      <c r="G25" s="129"/>
-      <c r="H25" s="129"/>
-      <c r="I25" s="129"/>
-      <c r="J25" s="129"/>
-      <c r="K25" s="129"/>
-      <c r="L25" s="129"/>
-      <c r="M25" s="129"/>
-      <c r="N25" s="126"/>
-      <c r="O25" s="126"/>
-      <c r="P25" s="126"/>
-      <c r="Q25" s="126"/>
+      <c r="C25" s="128"/>
+      <c r="D25" s="128"/>
+      <c r="E25" s="155"/>
+      <c r="F25" s="128"/>
+      <c r="G25" s="128"/>
+      <c r="H25" s="128"/>
+      <c r="I25" s="128"/>
+      <c r="J25" s="128"/>
+      <c r="K25" s="128"/>
+      <c r="L25" s="128"/>
+      <c r="M25" s="128"/>
+      <c r="N25" s="155"/>
+      <c r="O25" s="155"/>
+      <c r="P25" s="155"/>
+      <c r="Q25" s="155"/>
     </row>
     <row r="26" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="97" t="str">
@@ -11351,21 +11352,21 @@
       <c r="B26" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="130"/>
-      <c r="D26" s="130"/>
-      <c r="E26" s="127"/>
-      <c r="F26" s="130"/>
-      <c r="G26" s="130"/>
-      <c r="H26" s="130"/>
-      <c r="I26" s="130"/>
-      <c r="J26" s="130"/>
-      <c r="K26" s="130"/>
-      <c r="L26" s="130"/>
-      <c r="M26" s="130"/>
-      <c r="N26" s="127"/>
-      <c r="O26" s="127"/>
-      <c r="P26" s="127"/>
-      <c r="Q26" s="127"/>
+      <c r="C26" s="136"/>
+      <c r="D26" s="136"/>
+      <c r="E26" s="156"/>
+      <c r="F26" s="136"/>
+      <c r="G26" s="136"/>
+      <c r="H26" s="136"/>
+      <c r="I26" s="136"/>
+      <c r="J26" s="136"/>
+      <c r="K26" s="136"/>
+      <c r="L26" s="136"/>
+      <c r="M26" s="136"/>
+      <c r="N26" s="156"/>
+      <c r="O26" s="156"/>
+      <c r="P26" s="156"/>
+      <c r="Q26" s="156"/>
     </row>
     <row r="27" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A27" s="23" t="str">
@@ -11375,48 +11376,48 @@
       <c r="B27" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="128">
+      <c r="C27" s="135">
         <v>2</v>
       </c>
-      <c r="D27" s="128" t="s">
+      <c r="D27" s="135" t="s">
         <v>223</v>
       </c>
-      <c r="E27" s="125" t="s">
+      <c r="E27" s="154" t="s">
         <v>224</v>
       </c>
-      <c r="F27" s="128" t="s">
+      <c r="F27" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="G27" s="128"/>
-      <c r="H27" s="128" t="s">
+      <c r="G27" s="135"/>
+      <c r="H27" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I27" s="128"/>
-      <c r="J27" s="128">
+      <c r="I27" s="135"/>
+      <c r="J27" s="135">
         <v>3</v>
       </c>
-      <c r="K27" s="128">
+      <c r="K27" s="135">
         <f>J27*12</f>
         <v>36</v>
       </c>
-      <c r="L27" s="128">
+      <c r="L27" s="135">
         <f>36*J27</f>
         <v>108</v>
       </c>
-      <c r="M27" s="128">
+      <c r="M27" s="135">
         <f>SUM(K27:L27)</f>
         <v>144</v>
       </c>
-      <c r="N27" s="125" t="s">
+      <c r="N27" s="154" t="s">
         <v>225</v>
       </c>
-      <c r="O27" s="125" t="s">
+      <c r="O27" s="154" t="s">
         <v>195</v>
       </c>
-      <c r="P27" s="125" t="s">
+      <c r="P27" s="154" t="s">
         <v>226</v>
       </c>
-      <c r="Q27" s="125" t="s">
+      <c r="Q27" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -11428,21 +11429,21 @@
       <c r="B28" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C28" s="129"/>
-      <c r="D28" s="129"/>
-      <c r="E28" s="126"/>
-      <c r="F28" s="129"/>
-      <c r="G28" s="129"/>
-      <c r="H28" s="129"/>
-      <c r="I28" s="129"/>
-      <c r="J28" s="129"/>
-      <c r="K28" s="129"/>
-      <c r="L28" s="129"/>
-      <c r="M28" s="129"/>
-      <c r="N28" s="126"/>
-      <c r="O28" s="126"/>
-      <c r="P28" s="126"/>
-      <c r="Q28" s="126"/>
+      <c r="C28" s="128"/>
+      <c r="D28" s="128"/>
+      <c r="E28" s="155"/>
+      <c r="F28" s="128"/>
+      <c r="G28" s="128"/>
+      <c r="H28" s="128"/>
+      <c r="I28" s="128"/>
+      <c r="J28" s="128"/>
+      <c r="K28" s="128"/>
+      <c r="L28" s="128"/>
+      <c r="M28" s="128"/>
+      <c r="N28" s="155"/>
+      <c r="O28" s="155"/>
+      <c r="P28" s="155"/>
+      <c r="Q28" s="155"/>
     </row>
     <row r="29" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A29" s="23" t="str">
@@ -11452,21 +11453,21 @@
       <c r="B29" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C29" s="129"/>
-      <c r="D29" s="129"/>
-      <c r="E29" s="126"/>
-      <c r="F29" s="129"/>
-      <c r="G29" s="129"/>
-      <c r="H29" s="129"/>
-      <c r="I29" s="129"/>
-      <c r="J29" s="129"/>
-      <c r="K29" s="129"/>
-      <c r="L29" s="129"/>
-      <c r="M29" s="129"/>
-      <c r="N29" s="126"/>
-      <c r="O29" s="126"/>
-      <c r="P29" s="126"/>
-      <c r="Q29" s="126"/>
+      <c r="C29" s="128"/>
+      <c r="D29" s="128"/>
+      <c r="E29" s="155"/>
+      <c r="F29" s="128"/>
+      <c r="G29" s="128"/>
+      <c r="H29" s="128"/>
+      <c r="I29" s="128"/>
+      <c r="J29" s="128"/>
+      <c r="K29" s="128"/>
+      <c r="L29" s="128"/>
+      <c r="M29" s="128"/>
+      <c r="N29" s="155"/>
+      <c r="O29" s="155"/>
+      <c r="P29" s="155"/>
+      <c r="Q29" s="155"/>
     </row>
     <row r="30" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="97" t="str">
@@ -11476,21 +11477,21 @@
       <c r="B30" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="130"/>
-      <c r="D30" s="130"/>
-      <c r="E30" s="127"/>
-      <c r="F30" s="130"/>
-      <c r="G30" s="130"/>
-      <c r="H30" s="130"/>
-      <c r="I30" s="130"/>
-      <c r="J30" s="130"/>
-      <c r="K30" s="130"/>
-      <c r="L30" s="130"/>
-      <c r="M30" s="130"/>
-      <c r="N30" s="127"/>
-      <c r="O30" s="127"/>
-      <c r="P30" s="127"/>
-      <c r="Q30" s="127"/>
+      <c r="C30" s="136"/>
+      <c r="D30" s="136"/>
+      <c r="E30" s="156"/>
+      <c r="F30" s="136"/>
+      <c r="G30" s="136"/>
+      <c r="H30" s="136"/>
+      <c r="I30" s="136"/>
+      <c r="J30" s="136"/>
+      <c r="K30" s="136"/>
+      <c r="L30" s="136"/>
+      <c r="M30" s="136"/>
+      <c r="N30" s="156"/>
+      <c r="O30" s="156"/>
+      <c r="P30" s="156"/>
+      <c r="Q30" s="156"/>
     </row>
     <row r="31" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A31" s="23" t="str">
@@ -11500,48 +11501,48 @@
       <c r="B31" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C31" s="128">
+      <c r="C31" s="135">
         <v>2</v>
       </c>
-      <c r="D31" s="128" t="s">
+      <c r="D31" s="135" t="s">
         <v>227</v>
       </c>
-      <c r="E31" s="125" t="s">
+      <c r="E31" s="154" t="s">
         <v>228</v>
       </c>
-      <c r="F31" s="128" t="s">
+      <c r="F31" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G31" s="128"/>
-      <c r="H31" s="128" t="s">
+      <c r="G31" s="135"/>
+      <c r="H31" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I31" s="128"/>
-      <c r="J31" s="128">
+      <c r="I31" s="135"/>
+      <c r="J31" s="135">
         <v>3</v>
       </c>
-      <c r="K31" s="128">
+      <c r="K31" s="135">
         <f>J31*12</f>
         <v>36</v>
       </c>
-      <c r="L31" s="128">
+      <c r="L31" s="135">
         <f>36*J31</f>
         <v>108</v>
       </c>
-      <c r="M31" s="128">
+      <c r="M31" s="135">
         <f>SUM(K31:L31)</f>
         <v>144</v>
       </c>
-      <c r="N31" s="125" t="s">
+      <c r="N31" s="154" t="s">
         <v>229</v>
       </c>
-      <c r="O31" s="125" t="s">
+      <c r="O31" s="154" t="s">
         <v>195</v>
       </c>
-      <c r="P31" s="125" t="s">
+      <c r="P31" s="154" t="s">
         <v>230</v>
       </c>
-      <c r="Q31" s="125" t="s">
+      <c r="Q31" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -11553,21 +11554,21 @@
       <c r="B32" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C32" s="129"/>
-      <c r="D32" s="129"/>
-      <c r="E32" s="126"/>
-      <c r="F32" s="129"/>
-      <c r="G32" s="129"/>
-      <c r="H32" s="129"/>
-      <c r="I32" s="129"/>
-      <c r="J32" s="129"/>
-      <c r="K32" s="129"/>
-      <c r="L32" s="129"/>
-      <c r="M32" s="129"/>
-      <c r="N32" s="126"/>
-      <c r="O32" s="126"/>
-      <c r="P32" s="126"/>
-      <c r="Q32" s="126"/>
+      <c r="C32" s="128"/>
+      <c r="D32" s="128"/>
+      <c r="E32" s="155"/>
+      <c r="F32" s="128"/>
+      <c r="G32" s="128"/>
+      <c r="H32" s="128"/>
+      <c r="I32" s="128"/>
+      <c r="J32" s="128"/>
+      <c r="K32" s="128"/>
+      <c r="L32" s="128"/>
+      <c r="M32" s="128"/>
+      <c r="N32" s="155"/>
+      <c r="O32" s="155"/>
+      <c r="P32" s="155"/>
+      <c r="Q32" s="155"/>
     </row>
     <row r="33" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A33" s="97" t="str">
@@ -11577,21 +11578,21 @@
       <c r="B33" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="C33" s="130"/>
-      <c r="D33" s="130"/>
-      <c r="E33" s="127"/>
-      <c r="F33" s="130"/>
-      <c r="G33" s="130"/>
-      <c r="H33" s="130"/>
-      <c r="I33" s="130"/>
-      <c r="J33" s="130"/>
-      <c r="K33" s="130"/>
-      <c r="L33" s="130"/>
-      <c r="M33" s="130"/>
-      <c r="N33" s="127"/>
-      <c r="O33" s="127"/>
-      <c r="P33" s="127"/>
-      <c r="Q33" s="127"/>
+      <c r="C33" s="136"/>
+      <c r="D33" s="136"/>
+      <c r="E33" s="156"/>
+      <c r="F33" s="136"/>
+      <c r="G33" s="136"/>
+      <c r="H33" s="136"/>
+      <c r="I33" s="136"/>
+      <c r="J33" s="136"/>
+      <c r="K33" s="136"/>
+      <c r="L33" s="136"/>
+      <c r="M33" s="136"/>
+      <c r="N33" s="156"/>
+      <c r="O33" s="156"/>
+      <c r="P33" s="156"/>
+      <c r="Q33" s="156"/>
     </row>
     <row r="34" spans="1:17" s="52" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A34" s="107" t="str">
@@ -11654,48 +11655,48 @@
       <c r="B35" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="128">
+      <c r="C35" s="135">
         <v>3</v>
       </c>
-      <c r="D35" s="128" t="s">
+      <c r="D35" s="135" t="s">
         <v>234</v>
       </c>
-      <c r="E35" s="125" t="s">
+      <c r="E35" s="154" t="s">
         <v>235</v>
       </c>
-      <c r="F35" s="128" t="s">
+      <c r="F35" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G35" s="128"/>
-      <c r="H35" s="128" t="s">
+      <c r="G35" s="135"/>
+      <c r="H35" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I35" s="128"/>
-      <c r="J35" s="128">
+      <c r="I35" s="135"/>
+      <c r="J35" s="135">
         <v>3</v>
       </c>
-      <c r="K35" s="128">
+      <c r="K35" s="135">
         <f>J35*12</f>
         <v>36</v>
       </c>
-      <c r="L35" s="128">
+      <c r="L35" s="135">
         <f>36*J35</f>
         <v>108</v>
       </c>
-      <c r="M35" s="128">
+      <c r="M35" s="135">
         <f>SUM(K35:L35)</f>
         <v>144</v>
       </c>
-      <c r="N35" s="125" t="s">
+      <c r="N35" s="154" t="s">
         <v>236</v>
       </c>
-      <c r="O35" s="125" t="s">
+      <c r="O35" s="154" t="s">
         <v>195</v>
       </c>
-      <c r="P35" s="125" t="s">
+      <c r="P35" s="154" t="s">
         <v>189</v>
       </c>
-      <c r="Q35" s="125" t="s">
+      <c r="Q35" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -11707,21 +11708,21 @@
       <c r="B36" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C36" s="129"/>
-      <c r="D36" s="129"/>
-      <c r="E36" s="126"/>
-      <c r="F36" s="129"/>
-      <c r="G36" s="129"/>
-      <c r="H36" s="129"/>
-      <c r="I36" s="129"/>
-      <c r="J36" s="129"/>
-      <c r="K36" s="129"/>
-      <c r="L36" s="129"/>
-      <c r="M36" s="129"/>
-      <c r="N36" s="126"/>
-      <c r="O36" s="126"/>
-      <c r="P36" s="126"/>
-      <c r="Q36" s="126"/>
+      <c r="C36" s="128"/>
+      <c r="D36" s="128"/>
+      <c r="E36" s="155"/>
+      <c r="F36" s="128"/>
+      <c r="G36" s="128"/>
+      <c r="H36" s="128"/>
+      <c r="I36" s="128"/>
+      <c r="J36" s="128"/>
+      <c r="K36" s="128"/>
+      <c r="L36" s="128"/>
+      <c r="M36" s="128"/>
+      <c r="N36" s="155"/>
+      <c r="O36" s="155"/>
+      <c r="P36" s="155"/>
+      <c r="Q36" s="155"/>
     </row>
     <row r="37" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A37" s="23" t="str">
@@ -11731,21 +11732,21 @@
       <c r="B37" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C37" s="129"/>
-      <c r="D37" s="129"/>
-      <c r="E37" s="126"/>
-      <c r="F37" s="129"/>
-      <c r="G37" s="129"/>
-      <c r="H37" s="129"/>
-      <c r="I37" s="129"/>
-      <c r="J37" s="129"/>
-      <c r="K37" s="129"/>
-      <c r="L37" s="129"/>
-      <c r="M37" s="129"/>
-      <c r="N37" s="126"/>
-      <c r="O37" s="126"/>
-      <c r="P37" s="126"/>
-      <c r="Q37" s="126"/>
+      <c r="C37" s="128"/>
+      <c r="D37" s="128"/>
+      <c r="E37" s="155"/>
+      <c r="F37" s="128"/>
+      <c r="G37" s="128"/>
+      <c r="H37" s="128"/>
+      <c r="I37" s="128"/>
+      <c r="J37" s="128"/>
+      <c r="K37" s="128"/>
+      <c r="L37" s="128"/>
+      <c r="M37" s="128"/>
+      <c r="N37" s="155"/>
+      <c r="O37" s="155"/>
+      <c r="P37" s="155"/>
+      <c r="Q37" s="155"/>
     </row>
     <row r="38" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A38" s="23" t="str">
@@ -11755,21 +11756,21 @@
       <c r="B38" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C38" s="129"/>
-      <c r="D38" s="129"/>
-      <c r="E38" s="126"/>
-      <c r="F38" s="129"/>
-      <c r="G38" s="129"/>
-      <c r="H38" s="129"/>
-      <c r="I38" s="129"/>
-      <c r="J38" s="129"/>
-      <c r="K38" s="129"/>
-      <c r="L38" s="129"/>
-      <c r="M38" s="129"/>
-      <c r="N38" s="126"/>
-      <c r="O38" s="126"/>
-      <c r="P38" s="126"/>
-      <c r="Q38" s="126"/>
+      <c r="C38" s="128"/>
+      <c r="D38" s="128"/>
+      <c r="E38" s="155"/>
+      <c r="F38" s="128"/>
+      <c r="G38" s="128"/>
+      <c r="H38" s="128"/>
+      <c r="I38" s="128"/>
+      <c r="J38" s="128"/>
+      <c r="K38" s="128"/>
+      <c r="L38" s="128"/>
+      <c r="M38" s="128"/>
+      <c r="N38" s="155"/>
+      <c r="O38" s="155"/>
+      <c r="P38" s="155"/>
+      <c r="Q38" s="155"/>
     </row>
     <row r="39" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="97" t="str">
@@ -11779,21 +11780,21 @@
       <c r="B39" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C39" s="130"/>
-      <c r="D39" s="130"/>
-      <c r="E39" s="127"/>
-      <c r="F39" s="130"/>
-      <c r="G39" s="130"/>
-      <c r="H39" s="130"/>
-      <c r="I39" s="130"/>
-      <c r="J39" s="130"/>
-      <c r="K39" s="130"/>
-      <c r="L39" s="130"/>
-      <c r="M39" s="130"/>
-      <c r="N39" s="127"/>
-      <c r="O39" s="127"/>
-      <c r="P39" s="127"/>
-      <c r="Q39" s="127"/>
+      <c r="C39" s="136"/>
+      <c r="D39" s="136"/>
+      <c r="E39" s="156"/>
+      <c r="F39" s="136"/>
+      <c r="G39" s="136"/>
+      <c r="H39" s="136"/>
+      <c r="I39" s="136"/>
+      <c r="J39" s="136"/>
+      <c r="K39" s="136"/>
+      <c r="L39" s="136"/>
+      <c r="M39" s="136"/>
+      <c r="N39" s="156"/>
+      <c r="O39" s="156"/>
+      <c r="P39" s="156"/>
+      <c r="Q39" s="156"/>
     </row>
     <row r="40" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A40" s="23" t="str">
@@ -11803,48 +11804,48 @@
       <c r="B40" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C40" s="128">
+      <c r="C40" s="135">
         <v>3</v>
       </c>
-      <c r="D40" s="128" t="s">
+      <c r="D40" s="135" t="s">
         <v>237</v>
       </c>
-      <c r="E40" s="125" t="s">
+      <c r="E40" s="154" t="s">
         <v>238</v>
       </c>
-      <c r="F40" s="128" t="s">
+      <c r="F40" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="G40" s="128"/>
-      <c r="H40" s="128" t="s">
+      <c r="G40" s="135"/>
+      <c r="H40" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I40" s="128"/>
-      <c r="J40" s="128">
+      <c r="I40" s="135"/>
+      <c r="J40" s="135">
         <v>3</v>
       </c>
-      <c r="K40" s="128">
+      <c r="K40" s="135">
         <f>J40*12</f>
         <v>36</v>
       </c>
-      <c r="L40" s="128">
+      <c r="L40" s="135">
         <f>36*J40</f>
         <v>108</v>
       </c>
-      <c r="M40" s="128">
+      <c r="M40" s="135">
         <f>SUM(K40:L40)</f>
         <v>144</v>
       </c>
-      <c r="N40" s="125" t="s">
+      <c r="N40" s="154" t="s">
         <v>239</v>
       </c>
-      <c r="O40" s="125" t="s">
+      <c r="O40" s="154" t="s">
         <v>195</v>
       </c>
-      <c r="P40" s="125" t="s">
+      <c r="P40" s="154" t="s">
         <v>240</v>
       </c>
-      <c r="Q40" s="125" t="s">
+      <c r="Q40" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -11856,21 +11857,21 @@
       <c r="B41" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C41" s="129"/>
-      <c r="D41" s="129"/>
-      <c r="E41" s="126"/>
-      <c r="F41" s="129"/>
-      <c r="G41" s="129"/>
-      <c r="H41" s="129"/>
-      <c r="I41" s="129"/>
-      <c r="J41" s="129"/>
-      <c r="K41" s="129"/>
-      <c r="L41" s="129"/>
-      <c r="M41" s="129"/>
-      <c r="N41" s="126"/>
-      <c r="O41" s="126"/>
-      <c r="P41" s="126"/>
-      <c r="Q41" s="126"/>
+      <c r="C41" s="128"/>
+      <c r="D41" s="128"/>
+      <c r="E41" s="155"/>
+      <c r="F41" s="128"/>
+      <c r="G41" s="128"/>
+      <c r="H41" s="128"/>
+      <c r="I41" s="128"/>
+      <c r="J41" s="128"/>
+      <c r="K41" s="128"/>
+      <c r="L41" s="128"/>
+      <c r="M41" s="128"/>
+      <c r="N41" s="155"/>
+      <c r="O41" s="155"/>
+      <c r="P41" s="155"/>
+      <c r="Q41" s="155"/>
     </row>
     <row r="42" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A42" s="23" t="str">
@@ -11880,21 +11881,21 @@
       <c r="B42" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C42" s="129"/>
-      <c r="D42" s="129"/>
-      <c r="E42" s="126"/>
-      <c r="F42" s="129"/>
-      <c r="G42" s="129"/>
-      <c r="H42" s="129"/>
-      <c r="I42" s="129"/>
-      <c r="J42" s="129"/>
-      <c r="K42" s="129"/>
-      <c r="L42" s="129"/>
-      <c r="M42" s="129"/>
-      <c r="N42" s="126"/>
-      <c r="O42" s="126"/>
-      <c r="P42" s="126"/>
-      <c r="Q42" s="126"/>
+      <c r="C42" s="128"/>
+      <c r="D42" s="128"/>
+      <c r="E42" s="155"/>
+      <c r="F42" s="128"/>
+      <c r="G42" s="128"/>
+      <c r="H42" s="128"/>
+      <c r="I42" s="128"/>
+      <c r="J42" s="128"/>
+      <c r="K42" s="128"/>
+      <c r="L42" s="128"/>
+      <c r="M42" s="128"/>
+      <c r="N42" s="155"/>
+      <c r="O42" s="155"/>
+      <c r="P42" s="155"/>
+      <c r="Q42" s="155"/>
     </row>
     <row r="43" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A43" s="23" t="str">
@@ -11904,21 +11905,21 @@
       <c r="B43" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C43" s="129"/>
-      <c r="D43" s="129"/>
-      <c r="E43" s="126"/>
-      <c r="F43" s="129"/>
-      <c r="G43" s="129"/>
-      <c r="H43" s="129"/>
-      <c r="I43" s="129"/>
-      <c r="J43" s="129"/>
-      <c r="K43" s="129"/>
-      <c r="L43" s="129"/>
-      <c r="M43" s="129"/>
-      <c r="N43" s="126"/>
-      <c r="O43" s="126"/>
-      <c r="P43" s="126"/>
-      <c r="Q43" s="126"/>
+      <c r="C43" s="128"/>
+      <c r="D43" s="128"/>
+      <c r="E43" s="155"/>
+      <c r="F43" s="128"/>
+      <c r="G43" s="128"/>
+      <c r="H43" s="128"/>
+      <c r="I43" s="128"/>
+      <c r="J43" s="128"/>
+      <c r="K43" s="128"/>
+      <c r="L43" s="128"/>
+      <c r="M43" s="128"/>
+      <c r="N43" s="155"/>
+      <c r="O43" s="155"/>
+      <c r="P43" s="155"/>
+      <c r="Q43" s="155"/>
     </row>
     <row r="44" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A44" s="97" t="str">
@@ -11928,21 +11929,21 @@
       <c r="B44" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C44" s="130"/>
-      <c r="D44" s="130"/>
-      <c r="E44" s="127"/>
-      <c r="F44" s="130"/>
-      <c r="G44" s="130"/>
-      <c r="H44" s="130"/>
-      <c r="I44" s="130"/>
-      <c r="J44" s="130"/>
-      <c r="K44" s="130"/>
-      <c r="L44" s="130"/>
-      <c r="M44" s="130"/>
-      <c r="N44" s="127"/>
-      <c r="O44" s="127"/>
-      <c r="P44" s="127"/>
-      <c r="Q44" s="127"/>
+      <c r="C44" s="136"/>
+      <c r="D44" s="136"/>
+      <c r="E44" s="156"/>
+      <c r="F44" s="136"/>
+      <c r="G44" s="136"/>
+      <c r="H44" s="136"/>
+      <c r="I44" s="136"/>
+      <c r="J44" s="136"/>
+      <c r="K44" s="136"/>
+      <c r="L44" s="136"/>
+      <c r="M44" s="136"/>
+      <c r="N44" s="156"/>
+      <c r="O44" s="156"/>
+      <c r="P44" s="156"/>
+      <c r="Q44" s="156"/>
     </row>
     <row r="45" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A45" s="23" t="str">
@@ -11952,48 +11953,48 @@
       <c r="B45" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C45" s="128">
+      <c r="C45" s="135">
         <v>3</v>
       </c>
-      <c r="D45" s="128" t="s">
+      <c r="D45" s="135" t="s">
         <v>241</v>
       </c>
-      <c r="E45" s="125" t="s">
+      <c r="E45" s="154" t="s">
         <v>242</v>
       </c>
-      <c r="F45" s="128" t="s">
+      <c r="F45" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G45" s="128"/>
-      <c r="H45" s="128" t="s">
+      <c r="G45" s="135"/>
+      <c r="H45" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I45" s="128"/>
-      <c r="J45" s="128">
+      <c r="I45" s="135"/>
+      <c r="J45" s="135">
         <v>3</v>
       </c>
-      <c r="K45" s="128">
+      <c r="K45" s="135">
         <f>J45*12</f>
         <v>36</v>
       </c>
-      <c r="L45" s="128">
+      <c r="L45" s="135">
         <f>36*J45</f>
         <v>108</v>
       </c>
-      <c r="M45" s="128">
+      <c r="M45" s="135">
         <f>SUM(K45:L45)</f>
         <v>144</v>
       </c>
-      <c r="N45" s="125" t="s">
+      <c r="N45" s="154" t="s">
         <v>243</v>
       </c>
-      <c r="O45" s="125" t="s">
+      <c r="O45" s="154" t="s">
         <v>244</v>
       </c>
-      <c r="P45" s="125" t="s">
+      <c r="P45" s="154" t="s">
         <v>245</v>
       </c>
-      <c r="Q45" s="125" t="s">
+      <c r="Q45" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -12005,21 +12006,21 @@
       <c r="B46" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C46" s="129"/>
-      <c r="D46" s="129"/>
-      <c r="E46" s="126"/>
-      <c r="F46" s="129"/>
-      <c r="G46" s="129"/>
-      <c r="H46" s="129"/>
-      <c r="I46" s="129"/>
-      <c r="J46" s="129"/>
-      <c r="K46" s="129"/>
-      <c r="L46" s="129"/>
-      <c r="M46" s="129"/>
-      <c r="N46" s="126"/>
-      <c r="O46" s="126"/>
-      <c r="P46" s="126"/>
-      <c r="Q46" s="126"/>
+      <c r="C46" s="128"/>
+      <c r="D46" s="128"/>
+      <c r="E46" s="155"/>
+      <c r="F46" s="128"/>
+      <c r="G46" s="128"/>
+      <c r="H46" s="128"/>
+      <c r="I46" s="128"/>
+      <c r="J46" s="128"/>
+      <c r="K46" s="128"/>
+      <c r="L46" s="128"/>
+      <c r="M46" s="128"/>
+      <c r="N46" s="155"/>
+      <c r="O46" s="155"/>
+      <c r="P46" s="155"/>
+      <c r="Q46" s="155"/>
     </row>
     <row r="47" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A47" s="23" t="str">
@@ -12029,21 +12030,21 @@
       <c r="B47" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C47" s="129"/>
-      <c r="D47" s="129"/>
-      <c r="E47" s="126"/>
-      <c r="F47" s="129"/>
-      <c r="G47" s="129"/>
-      <c r="H47" s="129"/>
-      <c r="I47" s="129"/>
-      <c r="J47" s="129"/>
-      <c r="K47" s="129"/>
-      <c r="L47" s="129"/>
-      <c r="M47" s="129"/>
-      <c r="N47" s="126"/>
-      <c r="O47" s="126"/>
-      <c r="P47" s="126"/>
-      <c r="Q47" s="126"/>
+      <c r="C47" s="128"/>
+      <c r="D47" s="128"/>
+      <c r="E47" s="155"/>
+      <c r="F47" s="128"/>
+      <c r="G47" s="128"/>
+      <c r="H47" s="128"/>
+      <c r="I47" s="128"/>
+      <c r="J47" s="128"/>
+      <c r="K47" s="128"/>
+      <c r="L47" s="128"/>
+      <c r="M47" s="128"/>
+      <c r="N47" s="155"/>
+      <c r="O47" s="155"/>
+      <c r="P47" s="155"/>
+      <c r="Q47" s="155"/>
     </row>
     <row r="48" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="97" t="str">
@@ -12053,21 +12054,21 @@
       <c r="B48" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="C48" s="130"/>
-      <c r="D48" s="130"/>
-      <c r="E48" s="127"/>
-      <c r="F48" s="130"/>
-      <c r="G48" s="130"/>
-      <c r="H48" s="130"/>
-      <c r="I48" s="130"/>
-      <c r="J48" s="130"/>
-      <c r="K48" s="130"/>
-      <c r="L48" s="130"/>
-      <c r="M48" s="130"/>
-      <c r="N48" s="127"/>
-      <c r="O48" s="127"/>
-      <c r="P48" s="127"/>
-      <c r="Q48" s="127"/>
+      <c r="C48" s="136"/>
+      <c r="D48" s="136"/>
+      <c r="E48" s="156"/>
+      <c r="F48" s="136"/>
+      <c r="G48" s="136"/>
+      <c r="H48" s="136"/>
+      <c r="I48" s="136"/>
+      <c r="J48" s="136"/>
+      <c r="K48" s="136"/>
+      <c r="L48" s="136"/>
+      <c r="M48" s="136"/>
+      <c r="N48" s="156"/>
+      <c r="O48" s="156"/>
+      <c r="P48" s="156"/>
+      <c r="Q48" s="156"/>
     </row>
     <row r="49" spans="1:17" s="52" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A49" s="107" t="str">
@@ -12130,48 +12131,48 @@
       <c r="B50" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C50" s="128">
+      <c r="C50" s="135">
         <v>3</v>
       </c>
-      <c r="D50" s="128" t="s">
+      <c r="D50" s="135" t="s">
         <v>250</v>
       </c>
-      <c r="E50" s="125" t="s">
+      <c r="E50" s="154" t="s">
         <v>251</v>
       </c>
-      <c r="F50" s="128" t="s">
+      <c r="F50" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G50" s="128"/>
-      <c r="H50" s="128" t="s">
+      <c r="G50" s="135"/>
+      <c r="H50" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I50" s="128"/>
-      <c r="J50" s="128">
+      <c r="I50" s="135"/>
+      <c r="J50" s="135">
         <v>3</v>
       </c>
-      <c r="K50" s="128">
+      <c r="K50" s="135">
         <f>J50*12</f>
         <v>36</v>
       </c>
-      <c r="L50" s="128">
+      <c r="L50" s="135">
         <f>36*J50</f>
         <v>108</v>
       </c>
-      <c r="M50" s="128">
+      <c r="M50" s="135">
         <f>SUM(K50:L50)</f>
         <v>144</v>
       </c>
-      <c r="N50" s="125" t="s">
+      <c r="N50" s="154" t="s">
         <v>252</v>
       </c>
-      <c r="O50" s="125" t="s">
+      <c r="O50" s="154" t="s">
         <v>195</v>
       </c>
-      <c r="P50" s="125" t="s">
+      <c r="P50" s="154" t="s">
         <v>189</v>
       </c>
-      <c r="Q50" s="125" t="s">
+      <c r="Q50" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -12183,21 +12184,21 @@
       <c r="B51" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C51" s="129"/>
-      <c r="D51" s="129"/>
-      <c r="E51" s="126"/>
-      <c r="F51" s="129"/>
-      <c r="G51" s="129"/>
-      <c r="H51" s="129"/>
-      <c r="I51" s="129"/>
-      <c r="J51" s="129"/>
-      <c r="K51" s="129"/>
-      <c r="L51" s="129"/>
-      <c r="M51" s="129"/>
-      <c r="N51" s="126"/>
-      <c r="O51" s="126"/>
-      <c r="P51" s="126"/>
-      <c r="Q51" s="126"/>
+      <c r="C51" s="128"/>
+      <c r="D51" s="128"/>
+      <c r="E51" s="155"/>
+      <c r="F51" s="128"/>
+      <c r="G51" s="128"/>
+      <c r="H51" s="128"/>
+      <c r="I51" s="128"/>
+      <c r="J51" s="128"/>
+      <c r="K51" s="128"/>
+      <c r="L51" s="128"/>
+      <c r="M51" s="128"/>
+      <c r="N51" s="155"/>
+      <c r="O51" s="155"/>
+      <c r="P51" s="155"/>
+      <c r="Q51" s="155"/>
     </row>
     <row r="52" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A52" s="23" t="str">
@@ -12207,21 +12208,21 @@
       <c r="B52" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C52" s="129"/>
-      <c r="D52" s="129"/>
-      <c r="E52" s="126"/>
-      <c r="F52" s="129"/>
-      <c r="G52" s="129"/>
-      <c r="H52" s="129"/>
-      <c r="I52" s="129"/>
-      <c r="J52" s="129"/>
-      <c r="K52" s="129"/>
-      <c r="L52" s="129"/>
-      <c r="M52" s="129"/>
-      <c r="N52" s="126"/>
-      <c r="O52" s="126"/>
-      <c r="P52" s="126"/>
-      <c r="Q52" s="126"/>
+      <c r="C52" s="128"/>
+      <c r="D52" s="128"/>
+      <c r="E52" s="155"/>
+      <c r="F52" s="128"/>
+      <c r="G52" s="128"/>
+      <c r="H52" s="128"/>
+      <c r="I52" s="128"/>
+      <c r="J52" s="128"/>
+      <c r="K52" s="128"/>
+      <c r="L52" s="128"/>
+      <c r="M52" s="128"/>
+      <c r="N52" s="155"/>
+      <c r="O52" s="155"/>
+      <c r="P52" s="155"/>
+      <c r="Q52" s="155"/>
     </row>
     <row r="53" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="97" t="str">
@@ -12231,21 +12232,21 @@
       <c r="B53" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C53" s="129"/>
-      <c r="D53" s="129"/>
-      <c r="E53" s="126"/>
-      <c r="F53" s="129"/>
-      <c r="G53" s="129"/>
-      <c r="H53" s="129"/>
-      <c r="I53" s="129"/>
-      <c r="J53" s="129"/>
-      <c r="K53" s="129"/>
-      <c r="L53" s="129"/>
-      <c r="M53" s="129"/>
-      <c r="N53" s="126"/>
-      <c r="O53" s="126"/>
-      <c r="P53" s="126"/>
-      <c r="Q53" s="126"/>
+      <c r="C53" s="128"/>
+      <c r="D53" s="128"/>
+      <c r="E53" s="155"/>
+      <c r="F53" s="128"/>
+      <c r="G53" s="128"/>
+      <c r="H53" s="128"/>
+      <c r="I53" s="128"/>
+      <c r="J53" s="128"/>
+      <c r="K53" s="128"/>
+      <c r="L53" s="128"/>
+      <c r="M53" s="128"/>
+      <c r="N53" s="155"/>
+      <c r="O53" s="155"/>
+      <c r="P53" s="155"/>
+      <c r="Q53" s="155"/>
     </row>
     <row r="54" spans="1:17" s="12" customFormat="1" ht="216" x14ac:dyDescent="0.3">
       <c r="A54" s="107" t="str">
@@ -12308,45 +12309,45 @@
       <c r="B55" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C55" s="139">
+      <c r="C55" s="165">
         <v>4</v>
       </c>
-      <c r="D55" s="139" t="s">
+      <c r="D55" s="165" t="s">
         <v>257</v>
       </c>
-      <c r="E55" s="140" t="s">
+      <c r="E55" s="166" t="s">
         <v>258</v>
       </c>
-      <c r="F55" s="139" t="s">
+      <c r="F55" s="165" t="s">
         <v>185</v>
       </c>
-      <c r="G55" s="139"/>
-      <c r="H55" s="139" t="s">
+      <c r="G55" s="165"/>
+      <c r="H55" s="165" t="s">
         <v>186</v>
       </c>
-      <c r="I55" s="139"/>
-      <c r="J55" s="139">
+      <c r="I55" s="165"/>
+      <c r="J55" s="165">
         <v>4</v>
       </c>
-      <c r="K55" s="139">
+      <c r="K55" s="165">
         <f>12*J55</f>
         <v>48</v>
       </c>
-      <c r="L55" s="139">
+      <c r="L55" s="165">
         <f>36*J55</f>
         <v>144</v>
       </c>
-      <c r="M55" s="139"/>
-      <c r="N55" s="143" t="s">
+      <c r="M55" s="165"/>
+      <c r="N55" s="167" t="s">
         <v>259</v>
       </c>
-      <c r="O55" s="143" t="s">
+      <c r="O55" s="167" t="s">
         <v>188</v>
       </c>
-      <c r="P55" s="143" t="s">
+      <c r="P55" s="167" t="s">
         <v>260</v>
       </c>
-      <c r="Q55" s="143" t="s">
+      <c r="Q55" s="167" t="s">
         <v>190</v>
       </c>
     </row>
@@ -12358,21 +12359,21 @@
       <c r="B56" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C56" s="129"/>
-      <c r="D56" s="129"/>
-      <c r="E56" s="141"/>
-      <c r="F56" s="129"/>
-      <c r="G56" s="129"/>
-      <c r="H56" s="129"/>
-      <c r="I56" s="129"/>
-      <c r="J56" s="129"/>
-      <c r="K56" s="129"/>
-      <c r="L56" s="129"/>
-      <c r="M56" s="129"/>
-      <c r="N56" s="126"/>
-      <c r="O56" s="126"/>
-      <c r="P56" s="126"/>
-      <c r="Q56" s="126"/>
+      <c r="C56" s="128"/>
+      <c r="D56" s="128"/>
+      <c r="E56" s="126"/>
+      <c r="F56" s="128"/>
+      <c r="G56" s="128"/>
+      <c r="H56" s="128"/>
+      <c r="I56" s="128"/>
+      <c r="J56" s="128"/>
+      <c r="K56" s="128"/>
+      <c r="L56" s="128"/>
+      <c r="M56" s="128"/>
+      <c r="N56" s="155"/>
+      <c r="O56" s="155"/>
+      <c r="P56" s="155"/>
+      <c r="Q56" s="155"/>
     </row>
     <row r="57" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A57" s="23" t="str">
@@ -12382,21 +12383,21 @@
       <c r="B57" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C57" s="129"/>
-      <c r="D57" s="129"/>
-      <c r="E57" s="141"/>
-      <c r="F57" s="129"/>
-      <c r="G57" s="129"/>
-      <c r="H57" s="129"/>
-      <c r="I57" s="129"/>
-      <c r="J57" s="129"/>
-      <c r="K57" s="129"/>
-      <c r="L57" s="129"/>
-      <c r="M57" s="129"/>
-      <c r="N57" s="126"/>
-      <c r="O57" s="126"/>
-      <c r="P57" s="126"/>
-      <c r="Q57" s="126"/>
+      <c r="C57" s="128"/>
+      <c r="D57" s="128"/>
+      <c r="E57" s="126"/>
+      <c r="F57" s="128"/>
+      <c r="G57" s="128"/>
+      <c r="H57" s="128"/>
+      <c r="I57" s="128"/>
+      <c r="J57" s="128"/>
+      <c r="K57" s="128"/>
+      <c r="L57" s="128"/>
+      <c r="M57" s="128"/>
+      <c r="N57" s="155"/>
+      <c r="O57" s="155"/>
+      <c r="P57" s="155"/>
+      <c r="Q57" s="155"/>
     </row>
     <row r="58" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A58" s="23" t="str">
@@ -12406,21 +12407,21 @@
       <c r="B58" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C58" s="129"/>
-      <c r="D58" s="129"/>
-      <c r="E58" s="141"/>
-      <c r="F58" s="129"/>
-      <c r="G58" s="129"/>
-      <c r="H58" s="129"/>
-      <c r="I58" s="129"/>
-      <c r="J58" s="129"/>
-      <c r="K58" s="129"/>
-      <c r="L58" s="129"/>
-      <c r="M58" s="129"/>
-      <c r="N58" s="126"/>
-      <c r="O58" s="126"/>
-      <c r="P58" s="126"/>
-      <c r="Q58" s="126"/>
+      <c r="C58" s="128"/>
+      <c r="D58" s="128"/>
+      <c r="E58" s="126"/>
+      <c r="F58" s="128"/>
+      <c r="G58" s="128"/>
+      <c r="H58" s="128"/>
+      <c r="I58" s="128"/>
+      <c r="J58" s="128"/>
+      <c r="K58" s="128"/>
+      <c r="L58" s="128"/>
+      <c r="M58" s="128"/>
+      <c r="N58" s="155"/>
+      <c r="O58" s="155"/>
+      <c r="P58" s="155"/>
+      <c r="Q58" s="155"/>
     </row>
     <row r="59" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A59" s="113" t="str">
@@ -12430,21 +12431,21 @@
       <c r="B59" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C59" s="130"/>
-      <c r="D59" s="130"/>
-      <c r="E59" s="142"/>
-      <c r="F59" s="130"/>
-      <c r="G59" s="130"/>
-      <c r="H59" s="130"/>
-      <c r="I59" s="130"/>
-      <c r="J59" s="130"/>
-      <c r="K59" s="130"/>
-      <c r="L59" s="130"/>
-      <c r="M59" s="130"/>
-      <c r="N59" s="127"/>
-      <c r="O59" s="127"/>
-      <c r="P59" s="127"/>
-      <c r="Q59" s="127"/>
+      <c r="C59" s="136"/>
+      <c r="D59" s="136"/>
+      <c r="E59" s="134"/>
+      <c r="F59" s="136"/>
+      <c r="G59" s="136"/>
+      <c r="H59" s="136"/>
+      <c r="I59" s="136"/>
+      <c r="J59" s="136"/>
+      <c r="K59" s="136"/>
+      <c r="L59" s="136"/>
+      <c r="M59" s="136"/>
+      <c r="N59" s="156"/>
+      <c r="O59" s="156"/>
+      <c r="P59" s="156"/>
+      <c r="Q59" s="156"/>
     </row>
     <row r="60" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A60" s="23" t="str">
@@ -12454,48 +12455,48 @@
       <c r="B60" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C60" s="128">
+      <c r="C60" s="135">
         <v>4</v>
       </c>
-      <c r="D60" s="128" t="s">
+      <c r="D60" s="135" t="s">
         <v>261</v>
       </c>
-      <c r="E60" s="125" t="s">
+      <c r="E60" s="154" t="s">
         <v>262</v>
       </c>
-      <c r="F60" s="128" t="s">
+      <c r="F60" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G60" s="128"/>
-      <c r="H60" s="128" t="s">
+      <c r="G60" s="135"/>
+      <c r="H60" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I60" s="128"/>
-      <c r="J60" s="128">
+      <c r="I60" s="135"/>
+      <c r="J60" s="135">
         <v>3</v>
       </c>
-      <c r="K60" s="128">
+      <c r="K60" s="135">
         <f>J60*12</f>
         <v>36</v>
       </c>
-      <c r="L60" s="128">
+      <c r="L60" s="135">
         <f>36*J60</f>
         <v>108</v>
       </c>
-      <c r="M60" s="128">
+      <c r="M60" s="135">
         <f>SUM(K60:L60)</f>
         <v>144</v>
       </c>
-      <c r="N60" s="125" t="s">
+      <c r="N60" s="154" t="s">
         <v>263</v>
       </c>
-      <c r="O60" s="125" t="s">
+      <c r="O60" s="154" t="s">
         <v>244</v>
       </c>
-      <c r="P60" s="125" t="s">
+      <c r="P60" s="154" t="s">
         <v>264</v>
       </c>
-      <c r="Q60" s="125" t="s">
+      <c r="Q60" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -12507,21 +12508,21 @@
       <c r="B61" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C61" s="129"/>
-      <c r="D61" s="129"/>
-      <c r="E61" s="126"/>
-      <c r="F61" s="129"/>
-      <c r="G61" s="129"/>
-      <c r="H61" s="129"/>
-      <c r="I61" s="129"/>
-      <c r="J61" s="129"/>
-      <c r="K61" s="129"/>
-      <c r="L61" s="129"/>
-      <c r="M61" s="129"/>
-      <c r="N61" s="126"/>
-      <c r="O61" s="126"/>
-      <c r="P61" s="126"/>
-      <c r="Q61" s="126"/>
+      <c r="C61" s="128"/>
+      <c r="D61" s="128"/>
+      <c r="E61" s="155"/>
+      <c r="F61" s="128"/>
+      <c r="G61" s="128"/>
+      <c r="H61" s="128"/>
+      <c r="I61" s="128"/>
+      <c r="J61" s="128"/>
+      <c r="K61" s="128"/>
+      <c r="L61" s="128"/>
+      <c r="M61" s="128"/>
+      <c r="N61" s="155"/>
+      <c r="O61" s="155"/>
+      <c r="P61" s="155"/>
+      <c r="Q61" s="155"/>
     </row>
     <row r="62" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A62" s="23" t="str">
@@ -12531,21 +12532,21 @@
       <c r="B62" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C62" s="129"/>
-      <c r="D62" s="129"/>
-      <c r="E62" s="126"/>
-      <c r="F62" s="129"/>
-      <c r="G62" s="129"/>
-      <c r="H62" s="129"/>
-      <c r="I62" s="129"/>
-      <c r="J62" s="129"/>
-      <c r="K62" s="129"/>
-      <c r="L62" s="129"/>
-      <c r="M62" s="129"/>
-      <c r="N62" s="126"/>
-      <c r="O62" s="126"/>
-      <c r="P62" s="126"/>
-      <c r="Q62" s="126"/>
+      <c r="C62" s="128"/>
+      <c r="D62" s="128"/>
+      <c r="E62" s="155"/>
+      <c r="F62" s="128"/>
+      <c r="G62" s="128"/>
+      <c r="H62" s="128"/>
+      <c r="I62" s="128"/>
+      <c r="J62" s="128"/>
+      <c r="K62" s="128"/>
+      <c r="L62" s="128"/>
+      <c r="M62" s="128"/>
+      <c r="N62" s="155"/>
+      <c r="O62" s="155"/>
+      <c r="P62" s="155"/>
+      <c r="Q62" s="155"/>
     </row>
     <row r="63" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="97" t="str">
@@ -12555,21 +12556,21 @@
       <c r="B63" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C63" s="130"/>
-      <c r="D63" s="130"/>
-      <c r="E63" s="127"/>
-      <c r="F63" s="130"/>
-      <c r="G63" s="130"/>
-      <c r="H63" s="130"/>
-      <c r="I63" s="130"/>
-      <c r="J63" s="130"/>
-      <c r="K63" s="130"/>
-      <c r="L63" s="130"/>
-      <c r="M63" s="130"/>
-      <c r="N63" s="127"/>
-      <c r="O63" s="127"/>
-      <c r="P63" s="127"/>
-      <c r="Q63" s="127"/>
+      <c r="C63" s="136"/>
+      <c r="D63" s="136"/>
+      <c r="E63" s="156"/>
+      <c r="F63" s="136"/>
+      <c r="G63" s="136"/>
+      <c r="H63" s="136"/>
+      <c r="I63" s="136"/>
+      <c r="J63" s="136"/>
+      <c r="K63" s="136"/>
+      <c r="L63" s="136"/>
+      <c r="M63" s="136"/>
+      <c r="N63" s="156"/>
+      <c r="O63" s="156"/>
+      <c r="P63" s="156"/>
+      <c r="Q63" s="156"/>
     </row>
     <row r="64" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A64" s="23" t="str">
@@ -12579,48 +12580,48 @@
       <c r="B64" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C64" s="128">
+      <c r="C64" s="135">
         <v>4</v>
       </c>
-      <c r="D64" s="128" t="s">
+      <c r="D64" s="135" t="s">
         <v>265</v>
       </c>
-      <c r="E64" s="135" t="s">
+      <c r="E64" s="161" t="s">
         <v>266</v>
       </c>
-      <c r="F64" s="128" t="s">
+      <c r="F64" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G64" s="128"/>
-      <c r="H64" s="128" t="s">
+      <c r="G64" s="135"/>
+      <c r="H64" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I64" s="128"/>
-      <c r="J64" s="128">
+      <c r="I64" s="135"/>
+      <c r="J64" s="135">
         <v>3</v>
       </c>
-      <c r="K64" s="128">
+      <c r="K64" s="135">
         <f>J64*12</f>
         <v>36</v>
       </c>
-      <c r="L64" s="128">
+      <c r="L64" s="135">
         <f>36*J64</f>
         <v>108</v>
       </c>
-      <c r="M64" s="128">
+      <c r="M64" s="135">
         <f>SUM(K64:L64)</f>
         <v>144</v>
       </c>
-      <c r="N64" s="125" t="s">
+      <c r="N64" s="154" t="s">
         <v>267</v>
       </c>
-      <c r="O64" s="125" t="s">
+      <c r="O64" s="154" t="s">
         <v>195</v>
       </c>
-      <c r="P64" s="125" t="s">
+      <c r="P64" s="154" t="s">
         <v>189</v>
       </c>
-      <c r="Q64" s="125" t="s">
+      <c r="Q64" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -12632,21 +12633,21 @@
       <c r="B65" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C65" s="129"/>
-      <c r="D65" s="129"/>
-      <c r="E65" s="131"/>
-      <c r="F65" s="129"/>
-      <c r="G65" s="129"/>
-      <c r="H65" s="129"/>
-      <c r="I65" s="129"/>
-      <c r="J65" s="129"/>
-      <c r="K65" s="129"/>
-      <c r="L65" s="129"/>
-      <c r="M65" s="129"/>
-      <c r="N65" s="126"/>
-      <c r="O65" s="126"/>
-      <c r="P65" s="126"/>
-      <c r="Q65" s="126"/>
+      <c r="C65" s="128"/>
+      <c r="D65" s="128"/>
+      <c r="E65" s="157"/>
+      <c r="F65" s="128"/>
+      <c r="G65" s="128"/>
+      <c r="H65" s="128"/>
+      <c r="I65" s="128"/>
+      <c r="J65" s="128"/>
+      <c r="K65" s="128"/>
+      <c r="L65" s="128"/>
+      <c r="M65" s="128"/>
+      <c r="N65" s="155"/>
+      <c r="O65" s="155"/>
+      <c r="P65" s="155"/>
+      <c r="Q65" s="155"/>
     </row>
     <row r="66" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A66" s="23" t="str">
@@ -12656,21 +12657,21 @@
       <c r="B66" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C66" s="129"/>
-      <c r="D66" s="129"/>
-      <c r="E66" s="131"/>
-      <c r="F66" s="129"/>
-      <c r="G66" s="129"/>
-      <c r="H66" s="129"/>
-      <c r="I66" s="129"/>
-      <c r="J66" s="129"/>
-      <c r="K66" s="129"/>
-      <c r="L66" s="129"/>
-      <c r="M66" s="129"/>
-      <c r="N66" s="126"/>
-      <c r="O66" s="126"/>
-      <c r="P66" s="126"/>
-      <c r="Q66" s="126"/>
+      <c r="C66" s="128"/>
+      <c r="D66" s="128"/>
+      <c r="E66" s="157"/>
+      <c r="F66" s="128"/>
+      <c r="G66" s="128"/>
+      <c r="H66" s="128"/>
+      <c r="I66" s="128"/>
+      <c r="J66" s="128"/>
+      <c r="K66" s="128"/>
+      <c r="L66" s="128"/>
+      <c r="M66" s="128"/>
+      <c r="N66" s="155"/>
+      <c r="O66" s="155"/>
+      <c r="P66" s="155"/>
+      <c r="Q66" s="155"/>
     </row>
     <row r="67" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A67" s="23" t="str">
@@ -12680,21 +12681,21 @@
       <c r="B67" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C67" s="129"/>
-      <c r="D67" s="129"/>
-      <c r="E67" s="131"/>
-      <c r="F67" s="129"/>
-      <c r="G67" s="129"/>
-      <c r="H67" s="129"/>
-      <c r="I67" s="129"/>
-      <c r="J67" s="129"/>
-      <c r="K67" s="129"/>
-      <c r="L67" s="129"/>
-      <c r="M67" s="129"/>
-      <c r="N67" s="126"/>
-      <c r="O67" s="126"/>
-      <c r="P67" s="126"/>
-      <c r="Q67" s="126"/>
+      <c r="C67" s="128"/>
+      <c r="D67" s="128"/>
+      <c r="E67" s="157"/>
+      <c r="F67" s="128"/>
+      <c r="G67" s="128"/>
+      <c r="H67" s="128"/>
+      <c r="I67" s="128"/>
+      <c r="J67" s="128"/>
+      <c r="K67" s="128"/>
+      <c r="L67" s="128"/>
+      <c r="M67" s="128"/>
+      <c r="N67" s="155"/>
+      <c r="O67" s="155"/>
+      <c r="P67" s="155"/>
+      <c r="Q67" s="155"/>
     </row>
     <row r="68" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A68" s="97" t="str">
@@ -12704,21 +12705,21 @@
       <c r="B68" s="98" t="s">
         <v>104</v>
       </c>
-      <c r="C68" s="130"/>
-      <c r="D68" s="130"/>
-      <c r="E68" s="132"/>
-      <c r="F68" s="130"/>
-      <c r="G68" s="130"/>
-      <c r="H68" s="130"/>
-      <c r="I68" s="130"/>
-      <c r="J68" s="130"/>
-      <c r="K68" s="130"/>
-      <c r="L68" s="130"/>
-      <c r="M68" s="130"/>
-      <c r="N68" s="127"/>
-      <c r="O68" s="127"/>
-      <c r="P68" s="127"/>
-      <c r="Q68" s="127"/>
+      <c r="C68" s="136"/>
+      <c r="D68" s="136"/>
+      <c r="E68" s="158"/>
+      <c r="F68" s="136"/>
+      <c r="G68" s="136"/>
+      <c r="H68" s="136"/>
+      <c r="I68" s="136"/>
+      <c r="J68" s="136"/>
+      <c r="K68" s="136"/>
+      <c r="L68" s="136"/>
+      <c r="M68" s="136"/>
+      <c r="N68" s="156"/>
+      <c r="O68" s="156"/>
+      <c r="P68" s="156"/>
+      <c r="Q68" s="156"/>
     </row>
     <row r="69" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A69" s="23" t="str">
@@ -12728,48 +12729,48 @@
       <c r="B69" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C69" s="128">
+      <c r="C69" s="135">
         <v>4</v>
       </c>
-      <c r="D69" s="128" t="s">
+      <c r="D69" s="135" t="s">
         <v>268</v>
       </c>
-      <c r="E69" s="144" t="s">
+      <c r="E69" s="133" t="s">
         <v>269</v>
       </c>
-      <c r="F69" s="128" t="s">
+      <c r="F69" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G69" s="128"/>
-      <c r="H69" s="128" t="s">
+      <c r="G69" s="135"/>
+      <c r="H69" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I69" s="128"/>
-      <c r="J69" s="128">
+      <c r="I69" s="135"/>
+      <c r="J69" s="135">
         <v>3</v>
       </c>
-      <c r="K69" s="128">
+      <c r="K69" s="135">
         <f>J69*12</f>
         <v>36</v>
       </c>
-      <c r="L69" s="128">
+      <c r="L69" s="135">
         <f>36*J69</f>
         <v>108</v>
       </c>
-      <c r="M69" s="128">
+      <c r="M69" s="135">
         <f>SUM(K69:L69)</f>
         <v>144</v>
       </c>
-      <c r="N69" s="125" t="s">
+      <c r="N69" s="154" t="s">
         <v>270</v>
       </c>
-      <c r="O69" s="125" t="s">
+      <c r="O69" s="154" t="s">
         <v>195</v>
       </c>
-      <c r="P69" s="125" t="s">
+      <c r="P69" s="154" t="s">
         <v>189</v>
       </c>
-      <c r="Q69" s="125" t="s">
+      <c r="Q69" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -12781,21 +12782,21 @@
       <c r="B70" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C70" s="129"/>
-      <c r="D70" s="129"/>
-      <c r="E70" s="141"/>
-      <c r="F70" s="129"/>
-      <c r="G70" s="129"/>
-      <c r="H70" s="129"/>
-      <c r="I70" s="129"/>
-      <c r="J70" s="129"/>
-      <c r="K70" s="129"/>
-      <c r="L70" s="129"/>
-      <c r="M70" s="129"/>
-      <c r="N70" s="126"/>
-      <c r="O70" s="126"/>
-      <c r="P70" s="126"/>
-      <c r="Q70" s="126"/>
+      <c r="C70" s="128"/>
+      <c r="D70" s="128"/>
+      <c r="E70" s="126"/>
+      <c r="F70" s="128"/>
+      <c r="G70" s="128"/>
+      <c r="H70" s="128"/>
+      <c r="I70" s="128"/>
+      <c r="J70" s="128"/>
+      <c r="K70" s="128"/>
+      <c r="L70" s="128"/>
+      <c r="M70" s="128"/>
+      <c r="N70" s="155"/>
+      <c r="O70" s="155"/>
+      <c r="P70" s="155"/>
+      <c r="Q70" s="155"/>
     </row>
     <row r="71" spans="1:17" s="52" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="23" t="str">
@@ -12805,21 +12806,21 @@
       <c r="B71" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C71" s="129"/>
-      <c r="D71" s="129"/>
-      <c r="E71" s="141"/>
-      <c r="F71" s="129"/>
-      <c r="G71" s="129"/>
-      <c r="H71" s="129"/>
-      <c r="I71" s="129"/>
-      <c r="J71" s="129"/>
-      <c r="K71" s="129"/>
-      <c r="L71" s="129"/>
-      <c r="M71" s="129"/>
-      <c r="N71" s="126"/>
-      <c r="O71" s="126"/>
-      <c r="P71" s="126"/>
-      <c r="Q71" s="126"/>
+      <c r="C71" s="128"/>
+      <c r="D71" s="128"/>
+      <c r="E71" s="126"/>
+      <c r="F71" s="128"/>
+      <c r="G71" s="128"/>
+      <c r="H71" s="128"/>
+      <c r="I71" s="128"/>
+      <c r="J71" s="128"/>
+      <c r="K71" s="128"/>
+      <c r="L71" s="128"/>
+      <c r="M71" s="128"/>
+      <c r="N71" s="155"/>
+      <c r="O71" s="155"/>
+      <c r="P71" s="155"/>
+      <c r="Q71" s="155"/>
     </row>
     <row r="72" spans="1:17" s="52" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="97" t="str">
@@ -12829,21 +12830,21 @@
       <c r="B72" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C72" s="130"/>
-      <c r="D72" s="130"/>
-      <c r="E72" s="142"/>
-      <c r="F72" s="130"/>
-      <c r="G72" s="130"/>
-      <c r="H72" s="130"/>
-      <c r="I72" s="130"/>
-      <c r="J72" s="130"/>
-      <c r="K72" s="130"/>
-      <c r="L72" s="130"/>
-      <c r="M72" s="130"/>
-      <c r="N72" s="127"/>
-      <c r="O72" s="127"/>
-      <c r="P72" s="127"/>
-      <c r="Q72" s="127"/>
+      <c r="C72" s="136"/>
+      <c r="D72" s="136"/>
+      <c r="E72" s="134"/>
+      <c r="F72" s="136"/>
+      <c r="G72" s="136"/>
+      <c r="H72" s="136"/>
+      <c r="I72" s="136"/>
+      <c r="J72" s="136"/>
+      <c r="K72" s="136"/>
+      <c r="L72" s="136"/>
+      <c r="M72" s="136"/>
+      <c r="N72" s="156"/>
+      <c r="O72" s="156"/>
+      <c r="P72" s="156"/>
+      <c r="Q72" s="156"/>
     </row>
     <row r="73" spans="1:17" s="52" customFormat="1" ht="396" x14ac:dyDescent="0.3">
       <c r="A73" s="107" t="str">
@@ -12906,48 +12907,48 @@
       <c r="B74" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C74" s="128">
+      <c r="C74" s="135">
         <v>5</v>
       </c>
-      <c r="D74" s="128" t="s">
+      <c r="D74" s="135" t="s">
         <v>275</v>
       </c>
-      <c r="E74" s="125" t="s">
+      <c r="E74" s="154" t="s">
         <v>276</v>
       </c>
-      <c r="F74" s="128" t="s">
+      <c r="F74" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="G74" s="128"/>
-      <c r="H74" s="128" t="s">
+      <c r="G74" s="135"/>
+      <c r="H74" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I74" s="128"/>
-      <c r="J74" s="128">
+      <c r="I74" s="135"/>
+      <c r="J74" s="135">
         <v>3</v>
       </c>
-      <c r="K74" s="128">
+      <c r="K74" s="135">
         <f>J74*12</f>
         <v>36</v>
       </c>
-      <c r="L74" s="128">
+      <c r="L74" s="135">
         <f>36*J74</f>
         <v>108</v>
       </c>
-      <c r="M74" s="128">
+      <c r="M74" s="135">
         <f>SUM(K74:L74)</f>
         <v>144</v>
       </c>
-      <c r="N74" s="125" t="s">
+      <c r="N74" s="154" t="s">
         <v>277</v>
       </c>
-      <c r="O74" s="125" t="s">
+      <c r="O74" s="154" t="s">
         <v>195</v>
       </c>
-      <c r="P74" s="125" t="s">
+      <c r="P74" s="154" t="s">
         <v>240</v>
       </c>
-      <c r="Q74" s="125" t="s">
+      <c r="Q74" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -12959,21 +12960,21 @@
       <c r="B75" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C75" s="129"/>
-      <c r="D75" s="129"/>
-      <c r="E75" s="126"/>
-      <c r="F75" s="129"/>
-      <c r="G75" s="129"/>
-      <c r="H75" s="129"/>
-      <c r="I75" s="129"/>
-      <c r="J75" s="129"/>
-      <c r="K75" s="129"/>
-      <c r="L75" s="129"/>
-      <c r="M75" s="129"/>
-      <c r="N75" s="126"/>
-      <c r="O75" s="126"/>
-      <c r="P75" s="126"/>
-      <c r="Q75" s="126"/>
+      <c r="C75" s="128"/>
+      <c r="D75" s="128"/>
+      <c r="E75" s="155"/>
+      <c r="F75" s="128"/>
+      <c r="G75" s="128"/>
+      <c r="H75" s="128"/>
+      <c r="I75" s="128"/>
+      <c r="J75" s="128"/>
+      <c r="K75" s="128"/>
+      <c r="L75" s="128"/>
+      <c r="M75" s="128"/>
+      <c r="N75" s="155"/>
+      <c r="O75" s="155"/>
+      <c r="P75" s="155"/>
+      <c r="Q75" s="155"/>
     </row>
     <row r="76" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A76" s="23" t="str">
@@ -12983,21 +12984,21 @@
       <c r="B76" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C76" s="129"/>
-      <c r="D76" s="129"/>
-      <c r="E76" s="126"/>
-      <c r="F76" s="129"/>
-      <c r="G76" s="129"/>
-      <c r="H76" s="129"/>
-      <c r="I76" s="129"/>
-      <c r="J76" s="129"/>
-      <c r="K76" s="129"/>
-      <c r="L76" s="129"/>
-      <c r="M76" s="129"/>
-      <c r="N76" s="126"/>
-      <c r="O76" s="126"/>
-      <c r="P76" s="126"/>
-      <c r="Q76" s="126"/>
+      <c r="C76" s="128"/>
+      <c r="D76" s="128"/>
+      <c r="E76" s="155"/>
+      <c r="F76" s="128"/>
+      <c r="G76" s="128"/>
+      <c r="H76" s="128"/>
+      <c r="I76" s="128"/>
+      <c r="J76" s="128"/>
+      <c r="K76" s="128"/>
+      <c r="L76" s="128"/>
+      <c r="M76" s="128"/>
+      <c r="N76" s="155"/>
+      <c r="O76" s="155"/>
+      <c r="P76" s="155"/>
+      <c r="Q76" s="155"/>
     </row>
     <row r="77" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A77" s="23" t="str">
@@ -13007,21 +13008,21 @@
       <c r="B77" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C77" s="129"/>
-      <c r="D77" s="129"/>
-      <c r="E77" s="126"/>
-      <c r="F77" s="129"/>
-      <c r="G77" s="129"/>
-      <c r="H77" s="129"/>
-      <c r="I77" s="129"/>
-      <c r="J77" s="129"/>
-      <c r="K77" s="129"/>
-      <c r="L77" s="129"/>
-      <c r="M77" s="129"/>
-      <c r="N77" s="126"/>
-      <c r="O77" s="126"/>
-      <c r="P77" s="126"/>
-      <c r="Q77" s="126"/>
+      <c r="C77" s="128"/>
+      <c r="D77" s="128"/>
+      <c r="E77" s="155"/>
+      <c r="F77" s="128"/>
+      <c r="G77" s="128"/>
+      <c r="H77" s="128"/>
+      <c r="I77" s="128"/>
+      <c r="J77" s="128"/>
+      <c r="K77" s="128"/>
+      <c r="L77" s="128"/>
+      <c r="M77" s="128"/>
+      <c r="N77" s="155"/>
+      <c r="O77" s="155"/>
+      <c r="P77" s="155"/>
+      <c r="Q77" s="155"/>
     </row>
     <row r="78" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="97" t="str">
@@ -13031,21 +13032,21 @@
       <c r="B78" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C78" s="130"/>
-      <c r="D78" s="130"/>
-      <c r="E78" s="127"/>
-      <c r="F78" s="130"/>
-      <c r="G78" s="130"/>
-      <c r="H78" s="130"/>
-      <c r="I78" s="130"/>
-      <c r="J78" s="130"/>
-      <c r="K78" s="130"/>
-      <c r="L78" s="130"/>
-      <c r="M78" s="130"/>
-      <c r="N78" s="127"/>
-      <c r="O78" s="127"/>
-      <c r="P78" s="127"/>
-      <c r="Q78" s="127"/>
+      <c r="C78" s="136"/>
+      <c r="D78" s="136"/>
+      <c r="E78" s="156"/>
+      <c r="F78" s="136"/>
+      <c r="G78" s="136"/>
+      <c r="H78" s="136"/>
+      <c r="I78" s="136"/>
+      <c r="J78" s="136"/>
+      <c r="K78" s="136"/>
+      <c r="L78" s="136"/>
+      <c r="M78" s="136"/>
+      <c r="N78" s="156"/>
+      <c r="O78" s="156"/>
+      <c r="P78" s="156"/>
+      <c r="Q78" s="156"/>
     </row>
     <row r="79" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A79" s="23" t="str">
@@ -13055,48 +13056,48 @@
       <c r="B79" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C79" s="128">
+      <c r="C79" s="135">
         <v>5</v>
       </c>
-      <c r="D79" s="128" t="s">
+      <c r="D79" s="135" t="s">
         <v>278</v>
       </c>
-      <c r="E79" s="125" t="s">
+      <c r="E79" s="154" t="s">
         <v>279</v>
       </c>
-      <c r="F79" s="128" t="s">
+      <c r="F79" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G79" s="128"/>
-      <c r="H79" s="128" t="s">
+      <c r="G79" s="135"/>
+      <c r="H79" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I79" s="128"/>
-      <c r="J79" s="128">
+      <c r="I79" s="135"/>
+      <c r="J79" s="135">
         <v>4</v>
       </c>
-      <c r="K79" s="128">
+      <c r="K79" s="135">
         <f>J79*12</f>
         <v>48</v>
       </c>
-      <c r="L79" s="128">
+      <c r="L79" s="135">
         <f>36*J79</f>
         <v>144</v>
       </c>
-      <c r="M79" s="128">
+      <c r="M79" s="135">
         <f>SUM(K79:L79)</f>
         <v>192</v>
       </c>
-      <c r="N79" s="125" t="s">
+      <c r="N79" s="154" t="s">
         <v>280</v>
       </c>
-      <c r="O79" s="125" t="s">
+      <c r="O79" s="154" t="s">
         <v>195</v>
       </c>
-      <c r="P79" s="125" t="s">
+      <c r="P79" s="154" t="s">
         <v>281</v>
       </c>
-      <c r="Q79" s="125" t="s">
+      <c r="Q79" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -13108,21 +13109,21 @@
       <c r="B80" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C80" s="129"/>
-      <c r="D80" s="129"/>
-      <c r="E80" s="126"/>
-      <c r="F80" s="129"/>
-      <c r="G80" s="129"/>
-      <c r="H80" s="129"/>
-      <c r="I80" s="129"/>
-      <c r="J80" s="129"/>
-      <c r="K80" s="129"/>
-      <c r="L80" s="129"/>
-      <c r="M80" s="129"/>
-      <c r="N80" s="126"/>
-      <c r="O80" s="126"/>
-      <c r="P80" s="126"/>
-      <c r="Q80" s="126"/>
+      <c r="C80" s="128"/>
+      <c r="D80" s="128"/>
+      <c r="E80" s="155"/>
+      <c r="F80" s="128"/>
+      <c r="G80" s="128"/>
+      <c r="H80" s="128"/>
+      <c r="I80" s="128"/>
+      <c r="J80" s="128"/>
+      <c r="K80" s="128"/>
+      <c r="L80" s="128"/>
+      <c r="M80" s="128"/>
+      <c r="N80" s="155"/>
+      <c r="O80" s="155"/>
+      <c r="P80" s="155"/>
+      <c r="Q80" s="155"/>
     </row>
     <row r="81" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A81" s="23" t="str">
@@ -13132,21 +13133,21 @@
       <c r="B81" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C81" s="129"/>
-      <c r="D81" s="129"/>
-      <c r="E81" s="126"/>
-      <c r="F81" s="129"/>
-      <c r="G81" s="129"/>
-      <c r="H81" s="129"/>
-      <c r="I81" s="129"/>
-      <c r="J81" s="129"/>
-      <c r="K81" s="129"/>
-      <c r="L81" s="129"/>
-      <c r="M81" s="129"/>
-      <c r="N81" s="126"/>
-      <c r="O81" s="126"/>
-      <c r="P81" s="126"/>
-      <c r="Q81" s="126"/>
+      <c r="C81" s="128"/>
+      <c r="D81" s="128"/>
+      <c r="E81" s="155"/>
+      <c r="F81" s="128"/>
+      <c r="G81" s="128"/>
+      <c r="H81" s="128"/>
+      <c r="I81" s="128"/>
+      <c r="J81" s="128"/>
+      <c r="K81" s="128"/>
+      <c r="L81" s="128"/>
+      <c r="M81" s="128"/>
+      <c r="N81" s="155"/>
+      <c r="O81" s="155"/>
+      <c r="P81" s="155"/>
+      <c r="Q81" s="155"/>
     </row>
     <row r="82" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A82" s="23" t="str">
@@ -13156,21 +13157,21 @@
       <c r="B82" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C82" s="129"/>
-      <c r="D82" s="129"/>
-      <c r="E82" s="126"/>
-      <c r="F82" s="129"/>
-      <c r="G82" s="129"/>
-      <c r="H82" s="129"/>
-      <c r="I82" s="129"/>
-      <c r="J82" s="129"/>
-      <c r="K82" s="129"/>
-      <c r="L82" s="129"/>
-      <c r="M82" s="129"/>
-      <c r="N82" s="126"/>
-      <c r="O82" s="126"/>
-      <c r="P82" s="126"/>
-      <c r="Q82" s="126"/>
+      <c r="C82" s="128"/>
+      <c r="D82" s="128"/>
+      <c r="E82" s="155"/>
+      <c r="F82" s="128"/>
+      <c r="G82" s="128"/>
+      <c r="H82" s="128"/>
+      <c r="I82" s="128"/>
+      <c r="J82" s="128"/>
+      <c r="K82" s="128"/>
+      <c r="L82" s="128"/>
+      <c r="M82" s="128"/>
+      <c r="N82" s="155"/>
+      <c r="O82" s="155"/>
+      <c r="P82" s="155"/>
+      <c r="Q82" s="155"/>
     </row>
     <row r="83" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="97" t="str">
@@ -13180,21 +13181,21 @@
       <c r="B83" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C83" s="130"/>
-      <c r="D83" s="130"/>
-      <c r="E83" s="138"/>
-      <c r="F83" s="130"/>
-      <c r="G83" s="130"/>
-      <c r="H83" s="130"/>
-      <c r="I83" s="130"/>
-      <c r="J83" s="130"/>
-      <c r="K83" s="130"/>
-      <c r="L83" s="130"/>
-      <c r="M83" s="130"/>
-      <c r="N83" s="127"/>
-      <c r="O83" s="127"/>
-      <c r="P83" s="127"/>
-      <c r="Q83" s="127"/>
+      <c r="C83" s="136"/>
+      <c r="D83" s="136"/>
+      <c r="E83" s="164"/>
+      <c r="F83" s="136"/>
+      <c r="G83" s="136"/>
+      <c r="H83" s="136"/>
+      <c r="I83" s="136"/>
+      <c r="J83" s="136"/>
+      <c r="K83" s="136"/>
+      <c r="L83" s="136"/>
+      <c r="M83" s="136"/>
+      <c r="N83" s="156"/>
+      <c r="O83" s="156"/>
+      <c r="P83" s="156"/>
+      <c r="Q83" s="156"/>
     </row>
     <row r="84" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A84" s="23" t="str">
@@ -13204,48 +13205,48 @@
       <c r="B84" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C84" s="128">
+      <c r="C84" s="135">
         <v>5</v>
       </c>
-      <c r="D84" s="128" t="s">
+      <c r="D84" s="135" t="s">
         <v>282</v>
       </c>
-      <c r="E84" s="133" t="s">
+      <c r="E84" s="159" t="s">
         <v>283</v>
       </c>
-      <c r="F84" s="128" t="s">
+      <c r="F84" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="G84" s="128"/>
-      <c r="H84" s="128" t="s">
+      <c r="G84" s="135"/>
+      <c r="H84" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I84" s="128"/>
-      <c r="J84" s="128">
+      <c r="I84" s="135"/>
+      <c r="J84" s="135">
         <v>3</v>
       </c>
-      <c r="K84" s="128">
+      <c r="K84" s="135">
         <f>J84*12</f>
         <v>36</v>
       </c>
-      <c r="L84" s="128">
+      <c r="L84" s="135">
         <f>36*J84</f>
         <v>108</v>
       </c>
-      <c r="M84" s="128">
+      <c r="M84" s="135">
         <f>SUM(K84:L84)</f>
         <v>144</v>
       </c>
-      <c r="N84" s="125" t="s">
+      <c r="N84" s="154" t="s">
         <v>284</v>
       </c>
-      <c r="O84" s="125" t="s">
+      <c r="O84" s="154" t="s">
         <v>195</v>
       </c>
-      <c r="P84" s="125" t="s">
+      <c r="P84" s="154" t="s">
         <v>240</v>
       </c>
-      <c r="Q84" s="125" t="s">
+      <c r="Q84" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -13257,21 +13258,21 @@
       <c r="B85" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C85" s="129"/>
-      <c r="D85" s="129"/>
-      <c r="E85" s="126"/>
-      <c r="F85" s="129"/>
-      <c r="G85" s="129"/>
-      <c r="H85" s="129"/>
-      <c r="I85" s="129"/>
-      <c r="J85" s="129"/>
-      <c r="K85" s="129"/>
-      <c r="L85" s="129"/>
-      <c r="M85" s="129"/>
-      <c r="N85" s="126"/>
-      <c r="O85" s="126"/>
-      <c r="P85" s="126"/>
-      <c r="Q85" s="126"/>
+      <c r="C85" s="128"/>
+      <c r="D85" s="128"/>
+      <c r="E85" s="155"/>
+      <c r="F85" s="128"/>
+      <c r="G85" s="128"/>
+      <c r="H85" s="128"/>
+      <c r="I85" s="128"/>
+      <c r="J85" s="128"/>
+      <c r="K85" s="128"/>
+      <c r="L85" s="128"/>
+      <c r="M85" s="128"/>
+      <c r="N85" s="155"/>
+      <c r="O85" s="155"/>
+      <c r="P85" s="155"/>
+      <c r="Q85" s="155"/>
     </row>
     <row r="86" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A86" s="23" t="str">
@@ -13281,21 +13282,21 @@
       <c r="B86" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C86" s="129"/>
-      <c r="D86" s="129"/>
-      <c r="E86" s="126"/>
-      <c r="F86" s="129"/>
-      <c r="G86" s="129"/>
-      <c r="H86" s="129"/>
-      <c r="I86" s="129"/>
-      <c r="J86" s="129"/>
-      <c r="K86" s="129"/>
-      <c r="L86" s="129"/>
-      <c r="M86" s="129"/>
-      <c r="N86" s="126"/>
-      <c r="O86" s="126"/>
-      <c r="P86" s="126"/>
-      <c r="Q86" s="126"/>
+      <c r="C86" s="128"/>
+      <c r="D86" s="128"/>
+      <c r="E86" s="155"/>
+      <c r="F86" s="128"/>
+      <c r="G86" s="128"/>
+      <c r="H86" s="128"/>
+      <c r="I86" s="128"/>
+      <c r="J86" s="128"/>
+      <c r="K86" s="128"/>
+      <c r="L86" s="128"/>
+      <c r="M86" s="128"/>
+      <c r="N86" s="155"/>
+      <c r="O86" s="155"/>
+      <c r="P86" s="155"/>
+      <c r="Q86" s="155"/>
     </row>
     <row r="87" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A87" s="23" t="str">
@@ -13305,21 +13306,21 @@
       <c r="B87" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C87" s="129"/>
-      <c r="D87" s="129"/>
-      <c r="E87" s="126"/>
-      <c r="F87" s="129"/>
-      <c r="G87" s="129"/>
-      <c r="H87" s="129"/>
-      <c r="I87" s="129"/>
-      <c r="J87" s="129"/>
-      <c r="K87" s="129"/>
-      <c r="L87" s="129"/>
-      <c r="M87" s="129"/>
-      <c r="N87" s="126"/>
-      <c r="O87" s="126"/>
-      <c r="P87" s="126"/>
-      <c r="Q87" s="126"/>
+      <c r="C87" s="128"/>
+      <c r="D87" s="128"/>
+      <c r="E87" s="155"/>
+      <c r="F87" s="128"/>
+      <c r="G87" s="128"/>
+      <c r="H87" s="128"/>
+      <c r="I87" s="128"/>
+      <c r="J87" s="128"/>
+      <c r="K87" s="128"/>
+      <c r="L87" s="128"/>
+      <c r="M87" s="128"/>
+      <c r="N87" s="155"/>
+      <c r="O87" s="155"/>
+      <c r="P87" s="155"/>
+      <c r="Q87" s="155"/>
     </row>
     <row r="88" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="97" t="str">
@@ -13329,21 +13330,21 @@
       <c r="B88" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C88" s="130"/>
-      <c r="D88" s="130"/>
-      <c r="E88" s="127"/>
-      <c r="F88" s="130"/>
-      <c r="G88" s="130"/>
-      <c r="H88" s="130"/>
-      <c r="I88" s="130"/>
-      <c r="J88" s="130"/>
-      <c r="K88" s="130"/>
-      <c r="L88" s="130"/>
-      <c r="M88" s="130"/>
-      <c r="N88" s="127"/>
-      <c r="O88" s="127"/>
-      <c r="P88" s="127"/>
-      <c r="Q88" s="127"/>
+      <c r="C88" s="136"/>
+      <c r="D88" s="136"/>
+      <c r="E88" s="156"/>
+      <c r="F88" s="136"/>
+      <c r="G88" s="136"/>
+      <c r="H88" s="136"/>
+      <c r="I88" s="136"/>
+      <c r="J88" s="136"/>
+      <c r="K88" s="136"/>
+      <c r="L88" s="136"/>
+      <c r="M88" s="136"/>
+      <c r="N88" s="156"/>
+      <c r="O88" s="156"/>
+      <c r="P88" s="156"/>
+      <c r="Q88" s="156"/>
     </row>
     <row r="89" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A89" s="23" t="str">
@@ -13353,48 +13354,48 @@
       <c r="B89" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C89" s="128">
+      <c r="C89" s="135">
         <v>5</v>
       </c>
-      <c r="D89" s="128" t="s">
+      <c r="D89" s="135" t="s">
         <v>285</v>
       </c>
-      <c r="E89" s="135" t="s">
+      <c r="E89" s="161" t="s">
         <v>286</v>
       </c>
-      <c r="F89" s="128" t="s">
+      <c r="F89" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G89" s="128"/>
-      <c r="H89" s="128" t="s">
+      <c r="G89" s="135"/>
+      <c r="H89" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I89" s="128"/>
-      <c r="J89" s="128">
+      <c r="I89" s="135"/>
+      <c r="J89" s="135">
         <v>3</v>
       </c>
-      <c r="K89" s="128">
+      <c r="K89" s="135">
         <f>J89*12</f>
         <v>36</v>
       </c>
-      <c r="L89" s="128">
+      <c r="L89" s="135">
         <f>36*J89</f>
         <v>108</v>
       </c>
-      <c r="M89" s="128">
+      <c r="M89" s="135">
         <f>SUM(K89:L89)</f>
         <v>144</v>
       </c>
-      <c r="N89" s="125" t="s">
+      <c r="N89" s="154" t="s">
         <v>287</v>
       </c>
-      <c r="O89" s="125" t="s">
+      <c r="O89" s="154" t="s">
         <v>195</v>
       </c>
-      <c r="P89" s="125" t="s">
+      <c r="P89" s="154" t="s">
         <v>288</v>
       </c>
-      <c r="Q89" s="125" t="s">
+      <c r="Q89" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -13406,21 +13407,21 @@
       <c r="B90" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C90" s="129"/>
-      <c r="D90" s="129"/>
-      <c r="E90" s="131"/>
-      <c r="F90" s="129"/>
-      <c r="G90" s="129"/>
-      <c r="H90" s="129"/>
-      <c r="I90" s="129"/>
-      <c r="J90" s="129"/>
-      <c r="K90" s="129"/>
-      <c r="L90" s="129"/>
-      <c r="M90" s="129"/>
-      <c r="N90" s="126"/>
-      <c r="O90" s="126"/>
-      <c r="P90" s="126"/>
-      <c r="Q90" s="126"/>
+      <c r="C90" s="128"/>
+      <c r="D90" s="128"/>
+      <c r="E90" s="157"/>
+      <c r="F90" s="128"/>
+      <c r="G90" s="128"/>
+      <c r="H90" s="128"/>
+      <c r="I90" s="128"/>
+      <c r="J90" s="128"/>
+      <c r="K90" s="128"/>
+      <c r="L90" s="128"/>
+      <c r="M90" s="128"/>
+      <c r="N90" s="155"/>
+      <c r="O90" s="155"/>
+      <c r="P90" s="155"/>
+      <c r="Q90" s="155"/>
     </row>
     <row r="91" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A91" s="23" t="str">
@@ -13430,21 +13431,21 @@
       <c r="B91" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C91" s="129"/>
-      <c r="D91" s="129"/>
-      <c r="E91" s="131"/>
-      <c r="F91" s="129"/>
-      <c r="G91" s="129"/>
-      <c r="H91" s="129"/>
-      <c r="I91" s="129"/>
-      <c r="J91" s="129"/>
-      <c r="K91" s="129"/>
-      <c r="L91" s="129"/>
-      <c r="M91" s="129"/>
-      <c r="N91" s="126"/>
-      <c r="O91" s="126"/>
-      <c r="P91" s="126"/>
-      <c r="Q91" s="126"/>
+      <c r="C91" s="128"/>
+      <c r="D91" s="128"/>
+      <c r="E91" s="157"/>
+      <c r="F91" s="128"/>
+      <c r="G91" s="128"/>
+      <c r="H91" s="128"/>
+      <c r="I91" s="128"/>
+      <c r="J91" s="128"/>
+      <c r="K91" s="128"/>
+      <c r="L91" s="128"/>
+      <c r="M91" s="128"/>
+      <c r="N91" s="155"/>
+      <c r="O91" s="155"/>
+      <c r="P91" s="155"/>
+      <c r="Q91" s="155"/>
     </row>
     <row r="92" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A92" s="23" t="str">
@@ -13454,21 +13455,21 @@
       <c r="B92" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C92" s="129"/>
-      <c r="D92" s="129"/>
-      <c r="E92" s="131"/>
-      <c r="F92" s="129"/>
-      <c r="G92" s="129"/>
-      <c r="H92" s="129"/>
-      <c r="I92" s="129"/>
-      <c r="J92" s="129"/>
-      <c r="K92" s="129"/>
-      <c r="L92" s="129"/>
-      <c r="M92" s="129"/>
-      <c r="N92" s="126"/>
-      <c r="O92" s="126"/>
-      <c r="P92" s="126"/>
-      <c r="Q92" s="126"/>
+      <c r="C92" s="128"/>
+      <c r="D92" s="128"/>
+      <c r="E92" s="157"/>
+      <c r="F92" s="128"/>
+      <c r="G92" s="128"/>
+      <c r="H92" s="128"/>
+      <c r="I92" s="128"/>
+      <c r="J92" s="128"/>
+      <c r="K92" s="128"/>
+      <c r="L92" s="128"/>
+      <c r="M92" s="128"/>
+      <c r="N92" s="155"/>
+      <c r="O92" s="155"/>
+      <c r="P92" s="155"/>
+      <c r="Q92" s="155"/>
     </row>
     <row r="93" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="97" t="str">
@@ -13478,21 +13479,21 @@
       <c r="B93" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C93" s="130"/>
-      <c r="D93" s="130"/>
-      <c r="E93" s="132"/>
-      <c r="F93" s="130"/>
-      <c r="G93" s="130"/>
-      <c r="H93" s="130"/>
-      <c r="I93" s="130"/>
-      <c r="J93" s="130"/>
-      <c r="K93" s="130"/>
-      <c r="L93" s="130"/>
-      <c r="M93" s="130"/>
-      <c r="N93" s="127"/>
-      <c r="O93" s="127"/>
-      <c r="P93" s="127"/>
-      <c r="Q93" s="127"/>
+      <c r="C93" s="136"/>
+      <c r="D93" s="136"/>
+      <c r="E93" s="158"/>
+      <c r="F93" s="136"/>
+      <c r="G93" s="136"/>
+      <c r="H93" s="136"/>
+      <c r="I93" s="136"/>
+      <c r="J93" s="136"/>
+      <c r="K93" s="136"/>
+      <c r="L93" s="136"/>
+      <c r="M93" s="136"/>
+      <c r="N93" s="156"/>
+      <c r="O93" s="156"/>
+      <c r="P93" s="156"/>
+      <c r="Q93" s="156"/>
     </row>
     <row r="94" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A94" s="23" t="str">
@@ -13502,48 +13503,48 @@
       <c r="B94" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C94" s="128">
+      <c r="C94" s="135">
         <v>5</v>
       </c>
-      <c r="D94" s="128" t="s">
+      <c r="D94" s="135" t="s">
         <v>289</v>
       </c>
-      <c r="E94" s="126" t="s">
+      <c r="E94" s="155" t="s">
         <v>290</v>
       </c>
-      <c r="F94" s="129" t="s">
+      <c r="F94" s="128" t="s">
         <v>185</v>
       </c>
-      <c r="G94" s="129"/>
-      <c r="H94" s="129" t="s">
+      <c r="G94" s="128"/>
+      <c r="H94" s="128" t="s">
         <v>186</v>
       </c>
-      <c r="I94" s="129"/>
-      <c r="J94" s="129">
+      <c r="I94" s="128"/>
+      <c r="J94" s="128">
         <v>3</v>
       </c>
-      <c r="K94" s="129">
+      <c r="K94" s="128">
         <f>J94*12</f>
         <v>36</v>
       </c>
-      <c r="L94" s="129">
+      <c r="L94" s="128">
         <f>36*J94</f>
         <v>108</v>
       </c>
-      <c r="M94" s="129">
+      <c r="M94" s="128">
         <f>SUM(K94:L94)</f>
         <v>144</v>
       </c>
-      <c r="N94" s="126" t="s">
+      <c r="N94" s="155" t="s">
         <v>291</v>
       </c>
-      <c r="O94" s="125" t="s">
+      <c r="O94" s="154" t="s">
         <v>244</v>
       </c>
-      <c r="P94" s="125" t="s">
+      <c r="P94" s="154" t="s">
         <v>292</v>
       </c>
-      <c r="Q94" s="125" t="s">
+      <c r="Q94" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -13555,21 +13556,21 @@
       <c r="B95" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C95" s="129"/>
-      <c r="D95" s="129"/>
-      <c r="E95" s="126"/>
-      <c r="F95" s="129"/>
-      <c r="G95" s="129"/>
-      <c r="H95" s="129"/>
-      <c r="I95" s="129"/>
-      <c r="J95" s="129"/>
-      <c r="K95" s="129"/>
-      <c r="L95" s="129"/>
-      <c r="M95" s="129"/>
-      <c r="N95" s="126"/>
-      <c r="O95" s="126"/>
-      <c r="P95" s="126"/>
-      <c r="Q95" s="126"/>
+      <c r="C95" s="128"/>
+      <c r="D95" s="128"/>
+      <c r="E95" s="155"/>
+      <c r="F95" s="128"/>
+      <c r="G95" s="128"/>
+      <c r="H95" s="128"/>
+      <c r="I95" s="128"/>
+      <c r="J95" s="128"/>
+      <c r="K95" s="128"/>
+      <c r="L95" s="128"/>
+      <c r="M95" s="128"/>
+      <c r="N95" s="155"/>
+      <c r="O95" s="155"/>
+      <c r="P95" s="155"/>
+      <c r="Q95" s="155"/>
     </row>
     <row r="96" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A96" s="23" t="str">
@@ -13579,21 +13580,21 @@
       <c r="B96" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C96" s="129"/>
-      <c r="D96" s="129"/>
-      <c r="E96" s="126"/>
-      <c r="F96" s="129"/>
-      <c r="G96" s="129"/>
-      <c r="H96" s="129"/>
-      <c r="I96" s="129"/>
-      <c r="J96" s="129"/>
-      <c r="K96" s="129"/>
-      <c r="L96" s="129"/>
-      <c r="M96" s="129"/>
-      <c r="N96" s="126"/>
-      <c r="O96" s="126"/>
-      <c r="P96" s="126"/>
-      <c r="Q96" s="126"/>
+      <c r="C96" s="128"/>
+      <c r="D96" s="128"/>
+      <c r="E96" s="155"/>
+      <c r="F96" s="128"/>
+      <c r="G96" s="128"/>
+      <c r="H96" s="128"/>
+      <c r="I96" s="128"/>
+      <c r="J96" s="128"/>
+      <c r="K96" s="128"/>
+      <c r="L96" s="128"/>
+      <c r="M96" s="128"/>
+      <c r="N96" s="155"/>
+      <c r="O96" s="155"/>
+      <c r="P96" s="155"/>
+      <c r="Q96" s="155"/>
     </row>
     <row r="97" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="113" t="str">
@@ -13603,21 +13604,21 @@
       <c r="B97" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C97" s="129"/>
-      <c r="D97" s="129"/>
-      <c r="E97" s="126"/>
-      <c r="F97" s="129"/>
-      <c r="G97" s="129"/>
-      <c r="H97" s="129"/>
-      <c r="I97" s="129"/>
-      <c r="J97" s="129"/>
-      <c r="K97" s="129"/>
-      <c r="L97" s="129"/>
-      <c r="M97" s="129"/>
-      <c r="N97" s="126"/>
-      <c r="O97" s="126"/>
-      <c r="P97" s="126"/>
-      <c r="Q97" s="126"/>
+      <c r="C97" s="128"/>
+      <c r="D97" s="128"/>
+      <c r="E97" s="155"/>
+      <c r="F97" s="128"/>
+      <c r="G97" s="128"/>
+      <c r="H97" s="128"/>
+      <c r="I97" s="128"/>
+      <c r="J97" s="128"/>
+      <c r="K97" s="128"/>
+      <c r="L97" s="128"/>
+      <c r="M97" s="128"/>
+      <c r="N97" s="155"/>
+      <c r="O97" s="155"/>
+      <c r="P97" s="155"/>
+      <c r="Q97" s="155"/>
     </row>
     <row r="98" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A98" s="23" t="str">
@@ -13627,48 +13628,48 @@
       <c r="B98" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C98" s="128">
+      <c r="C98" s="135">
         <v>6</v>
       </c>
-      <c r="D98" s="128" t="s">
+      <c r="D98" s="135" t="s">
         <v>293</v>
       </c>
-      <c r="E98" s="133" t="s">
+      <c r="E98" s="159" t="s">
         <v>294</v>
       </c>
-      <c r="F98" s="128" t="s">
+      <c r="F98" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G98" s="128"/>
-      <c r="H98" s="128" t="s">
+      <c r="G98" s="135"/>
+      <c r="H98" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I98" s="128"/>
-      <c r="J98" s="128">
+      <c r="I98" s="135"/>
+      <c r="J98" s="135">
         <v>4</v>
       </c>
-      <c r="K98" s="128">
+      <c r="K98" s="135">
         <f>J98*12</f>
         <v>48</v>
       </c>
-      <c r="L98" s="128">
+      <c r="L98" s="135">
         <f>36*J98</f>
         <v>144</v>
       </c>
-      <c r="M98" s="128">
+      <c r="M98" s="135">
         <f>SUM(K98:L98)</f>
         <v>192</v>
       </c>
-      <c r="N98" s="125" t="s">
+      <c r="N98" s="154" t="s">
         <v>295</v>
       </c>
-      <c r="O98" s="125" t="s">
+      <c r="O98" s="154" t="s">
         <v>195</v>
       </c>
-      <c r="P98" s="125" t="s">
+      <c r="P98" s="154" t="s">
         <v>274</v>
       </c>
-      <c r="Q98" s="125" t="s">
+      <c r="Q98" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -13680,21 +13681,21 @@
       <c r="B99" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C99" s="129"/>
-      <c r="D99" s="129"/>
-      <c r="E99" s="126"/>
-      <c r="F99" s="129"/>
-      <c r="G99" s="129"/>
-      <c r="H99" s="129"/>
-      <c r="I99" s="129"/>
-      <c r="J99" s="129"/>
-      <c r="K99" s="129"/>
-      <c r="L99" s="129"/>
-      <c r="M99" s="129"/>
-      <c r="N99" s="126"/>
-      <c r="O99" s="126"/>
-      <c r="P99" s="126"/>
-      <c r="Q99" s="126"/>
+      <c r="C99" s="128"/>
+      <c r="D99" s="128"/>
+      <c r="E99" s="155"/>
+      <c r="F99" s="128"/>
+      <c r="G99" s="128"/>
+      <c r="H99" s="128"/>
+      <c r="I99" s="128"/>
+      <c r="J99" s="128"/>
+      <c r="K99" s="128"/>
+      <c r="L99" s="128"/>
+      <c r="M99" s="128"/>
+      <c r="N99" s="155"/>
+      <c r="O99" s="155"/>
+      <c r="P99" s="155"/>
+      <c r="Q99" s="155"/>
     </row>
     <row r="100" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A100" s="23" t="str">
@@ -13704,21 +13705,21 @@
       <c r="B100" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C100" s="129"/>
-      <c r="D100" s="129"/>
-      <c r="E100" s="126"/>
-      <c r="F100" s="129"/>
-      <c r="G100" s="129"/>
-      <c r="H100" s="129"/>
-      <c r="I100" s="129"/>
-      <c r="J100" s="129"/>
-      <c r="K100" s="129"/>
-      <c r="L100" s="129"/>
-      <c r="M100" s="129"/>
-      <c r="N100" s="126"/>
-      <c r="O100" s="126"/>
-      <c r="P100" s="126"/>
-      <c r="Q100" s="126"/>
+      <c r="C100" s="128"/>
+      <c r="D100" s="128"/>
+      <c r="E100" s="155"/>
+      <c r="F100" s="128"/>
+      <c r="G100" s="128"/>
+      <c r="H100" s="128"/>
+      <c r="I100" s="128"/>
+      <c r="J100" s="128"/>
+      <c r="K100" s="128"/>
+      <c r="L100" s="128"/>
+      <c r="M100" s="128"/>
+      <c r="N100" s="155"/>
+      <c r="O100" s="155"/>
+      <c r="P100" s="155"/>
+      <c r="Q100" s="155"/>
     </row>
     <row r="101" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A101" s="23" t="str">
@@ -13728,21 +13729,21 @@
       <c r="B101" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C101" s="129"/>
-      <c r="D101" s="129"/>
-      <c r="E101" s="126"/>
-      <c r="F101" s="129"/>
-      <c r="G101" s="129"/>
-      <c r="H101" s="129"/>
-      <c r="I101" s="129"/>
-      <c r="J101" s="129"/>
-      <c r="K101" s="129"/>
-      <c r="L101" s="129"/>
-      <c r="M101" s="129"/>
-      <c r="N101" s="126"/>
-      <c r="O101" s="126"/>
-      <c r="P101" s="126"/>
-      <c r="Q101" s="126"/>
+      <c r="C101" s="128"/>
+      <c r="D101" s="128"/>
+      <c r="E101" s="155"/>
+      <c r="F101" s="128"/>
+      <c r="G101" s="128"/>
+      <c r="H101" s="128"/>
+      <c r="I101" s="128"/>
+      <c r="J101" s="128"/>
+      <c r="K101" s="128"/>
+      <c r="L101" s="128"/>
+      <c r="M101" s="128"/>
+      <c r="N101" s="155"/>
+      <c r="O101" s="155"/>
+      <c r="P101" s="155"/>
+      <c r="Q101" s="155"/>
     </row>
     <row r="102" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="97" t="str">
@@ -13752,21 +13753,21 @@
       <c r="B102" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C102" s="130"/>
-      <c r="D102" s="130"/>
-      <c r="E102" s="127"/>
-      <c r="F102" s="130"/>
-      <c r="G102" s="130"/>
-      <c r="H102" s="130"/>
-      <c r="I102" s="130"/>
-      <c r="J102" s="130"/>
-      <c r="K102" s="130"/>
-      <c r="L102" s="130"/>
-      <c r="M102" s="130"/>
-      <c r="N102" s="127"/>
-      <c r="O102" s="127"/>
-      <c r="P102" s="127"/>
-      <c r="Q102" s="127"/>
+      <c r="C102" s="136"/>
+      <c r="D102" s="136"/>
+      <c r="E102" s="156"/>
+      <c r="F102" s="136"/>
+      <c r="G102" s="136"/>
+      <c r="H102" s="136"/>
+      <c r="I102" s="136"/>
+      <c r="J102" s="136"/>
+      <c r="K102" s="136"/>
+      <c r="L102" s="136"/>
+      <c r="M102" s="136"/>
+      <c r="N102" s="156"/>
+      <c r="O102" s="156"/>
+      <c r="P102" s="156"/>
+      <c r="Q102" s="156"/>
     </row>
     <row r="103" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A103" s="23" t="str">
@@ -13776,48 +13777,48 @@
       <c r="B103" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C103" s="128">
+      <c r="C103" s="135">
         <v>6</v>
       </c>
-      <c r="D103" s="128" t="s">
+      <c r="D103" s="135" t="s">
         <v>296</v>
       </c>
-      <c r="E103" s="125" t="s">
+      <c r="E103" s="154" t="s">
         <v>297</v>
       </c>
-      <c r="F103" s="128" t="s">
+      <c r="F103" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G103" s="128"/>
-      <c r="H103" s="128" t="s">
+      <c r="G103" s="135"/>
+      <c r="H103" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I103" s="128"/>
-      <c r="J103" s="128">
+      <c r="I103" s="135"/>
+      <c r="J103" s="135">
         <v>3</v>
       </c>
-      <c r="K103" s="128">
+      <c r="K103" s="135">
         <f>J103*12</f>
         <v>36</v>
       </c>
-      <c r="L103" s="128">
+      <c r="L103" s="135">
         <f>36*J103</f>
         <v>108</v>
       </c>
-      <c r="M103" s="128">
+      <c r="M103" s="135">
         <f>SUM(K103:L103)</f>
         <v>144</v>
       </c>
-      <c r="N103" s="125" t="s">
+      <c r="N103" s="154" t="s">
         <v>298</v>
       </c>
-      <c r="O103" s="125" t="s">
+      <c r="O103" s="154" t="s">
         <v>195</v>
       </c>
-      <c r="P103" s="125" t="s">
+      <c r="P103" s="154" t="s">
         <v>249</v>
       </c>
-      <c r="Q103" s="125" t="s">
+      <c r="Q103" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -13829,21 +13830,21 @@
       <c r="B104" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C104" s="129"/>
-      <c r="D104" s="129"/>
-      <c r="E104" s="126"/>
-      <c r="F104" s="129"/>
-      <c r="G104" s="129"/>
-      <c r="H104" s="129"/>
-      <c r="I104" s="129"/>
-      <c r="J104" s="129"/>
-      <c r="K104" s="129"/>
-      <c r="L104" s="129"/>
-      <c r="M104" s="129"/>
-      <c r="N104" s="126"/>
-      <c r="O104" s="126"/>
-      <c r="P104" s="126"/>
-      <c r="Q104" s="126"/>
+      <c r="C104" s="128"/>
+      <c r="D104" s="128"/>
+      <c r="E104" s="155"/>
+      <c r="F104" s="128"/>
+      <c r="G104" s="128"/>
+      <c r="H104" s="128"/>
+      <c r="I104" s="128"/>
+      <c r="J104" s="128"/>
+      <c r="K104" s="128"/>
+      <c r="L104" s="128"/>
+      <c r="M104" s="128"/>
+      <c r="N104" s="155"/>
+      <c r="O104" s="155"/>
+      <c r="P104" s="155"/>
+      <c r="Q104" s="155"/>
     </row>
     <row r="105" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A105" s="23" t="str">
@@ -13853,21 +13854,21 @@
       <c r="B105" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C105" s="129"/>
-      <c r="D105" s="129"/>
-      <c r="E105" s="126"/>
-      <c r="F105" s="129"/>
-      <c r="G105" s="129"/>
-      <c r="H105" s="129"/>
-      <c r="I105" s="129"/>
-      <c r="J105" s="129"/>
-      <c r="K105" s="129"/>
-      <c r="L105" s="129"/>
-      <c r="M105" s="129"/>
-      <c r="N105" s="126"/>
-      <c r="O105" s="126"/>
-      <c r="P105" s="126"/>
-      <c r="Q105" s="126"/>
+      <c r="C105" s="128"/>
+      <c r="D105" s="128"/>
+      <c r="E105" s="155"/>
+      <c r="F105" s="128"/>
+      <c r="G105" s="128"/>
+      <c r="H105" s="128"/>
+      <c r="I105" s="128"/>
+      <c r="J105" s="128"/>
+      <c r="K105" s="128"/>
+      <c r="L105" s="128"/>
+      <c r="M105" s="128"/>
+      <c r="N105" s="155"/>
+      <c r="O105" s="155"/>
+      <c r="P105" s="155"/>
+      <c r="Q105" s="155"/>
     </row>
     <row r="106" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A106" s="23" t="str">
@@ -13877,21 +13878,21 @@
       <c r="B106" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C106" s="129"/>
-      <c r="D106" s="129"/>
-      <c r="E106" s="126"/>
-      <c r="F106" s="129"/>
-      <c r="G106" s="129"/>
-      <c r="H106" s="129"/>
-      <c r="I106" s="129"/>
-      <c r="J106" s="129"/>
-      <c r="K106" s="129"/>
-      <c r="L106" s="129"/>
-      <c r="M106" s="129"/>
-      <c r="N106" s="126"/>
-      <c r="O106" s="126"/>
-      <c r="P106" s="126"/>
-      <c r="Q106" s="126"/>
+      <c r="C106" s="128"/>
+      <c r="D106" s="128"/>
+      <c r="E106" s="155"/>
+      <c r="F106" s="128"/>
+      <c r="G106" s="128"/>
+      <c r="H106" s="128"/>
+      <c r="I106" s="128"/>
+      <c r="J106" s="128"/>
+      <c r="K106" s="128"/>
+      <c r="L106" s="128"/>
+      <c r="M106" s="128"/>
+      <c r="N106" s="155"/>
+      <c r="O106" s="155"/>
+      <c r="P106" s="155"/>
+      <c r="Q106" s="155"/>
     </row>
     <row r="107" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="97" t="str">
@@ -13901,21 +13902,21 @@
       <c r="B107" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C107" s="130"/>
-      <c r="D107" s="130"/>
-      <c r="E107" s="127"/>
-      <c r="F107" s="130"/>
-      <c r="G107" s="130"/>
-      <c r="H107" s="130"/>
-      <c r="I107" s="130"/>
-      <c r="J107" s="130"/>
-      <c r="K107" s="130"/>
-      <c r="L107" s="130"/>
-      <c r="M107" s="130"/>
-      <c r="N107" s="127"/>
-      <c r="O107" s="127"/>
-      <c r="P107" s="127"/>
-      <c r="Q107" s="127"/>
+      <c r="C107" s="136"/>
+      <c r="D107" s="136"/>
+      <c r="E107" s="156"/>
+      <c r="F107" s="136"/>
+      <c r="G107" s="136"/>
+      <c r="H107" s="136"/>
+      <c r="I107" s="136"/>
+      <c r="J107" s="136"/>
+      <c r="K107" s="136"/>
+      <c r="L107" s="136"/>
+      <c r="M107" s="136"/>
+      <c r="N107" s="156"/>
+      <c r="O107" s="156"/>
+      <c r="P107" s="156"/>
+      <c r="Q107" s="156"/>
     </row>
     <row r="108" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A108" s="23" t="str">
@@ -13925,48 +13926,48 @@
       <c r="B108" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C108" s="128">
+      <c r="C108" s="135">
         <v>6</v>
       </c>
-      <c r="D108" s="128" t="s">
+      <c r="D108" s="135" t="s">
         <v>299</v>
       </c>
-      <c r="E108" s="137" t="s">
+      <c r="E108" s="163" t="s">
         <v>300</v>
       </c>
-      <c r="F108" s="128" t="s">
+      <c r="F108" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G108" s="128"/>
-      <c r="H108" s="128" t="s">
+      <c r="G108" s="135"/>
+      <c r="H108" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I108" s="128"/>
-      <c r="J108" s="128">
+      <c r="I108" s="135"/>
+      <c r="J108" s="135">
         <v>4</v>
       </c>
-      <c r="K108" s="128">
+      <c r="K108" s="135">
         <f>J108*12</f>
         <v>48</v>
       </c>
-      <c r="L108" s="128">
+      <c r="L108" s="135">
         <f>36*J108</f>
         <v>144</v>
       </c>
-      <c r="M108" s="128">
+      <c r="M108" s="135">
         <f>SUM(K108:L108)</f>
         <v>192</v>
       </c>
-      <c r="N108" s="125" t="s">
+      <c r="N108" s="154" t="s">
         <v>301</v>
       </c>
-      <c r="O108" s="125" t="s">
+      <c r="O108" s="154" t="s">
         <v>302</v>
       </c>
-      <c r="P108" s="125" t="s">
+      <c r="P108" s="154" t="s">
         <v>274</v>
       </c>
-      <c r="Q108" s="125" t="s">
+      <c r="Q108" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -13978,21 +13979,21 @@
       <c r="B109" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C109" s="129"/>
-      <c r="D109" s="129"/>
-      <c r="E109" s="126"/>
-      <c r="F109" s="129"/>
-      <c r="G109" s="129"/>
-      <c r="H109" s="129"/>
-      <c r="I109" s="129"/>
-      <c r="J109" s="129"/>
-      <c r="K109" s="129"/>
-      <c r="L109" s="129"/>
-      <c r="M109" s="129"/>
-      <c r="N109" s="126"/>
-      <c r="O109" s="126"/>
-      <c r="P109" s="126"/>
-      <c r="Q109" s="126"/>
+      <c r="C109" s="128"/>
+      <c r="D109" s="128"/>
+      <c r="E109" s="155"/>
+      <c r="F109" s="128"/>
+      <c r="G109" s="128"/>
+      <c r="H109" s="128"/>
+      <c r="I109" s="128"/>
+      <c r="J109" s="128"/>
+      <c r="K109" s="128"/>
+      <c r="L109" s="128"/>
+      <c r="M109" s="128"/>
+      <c r="N109" s="155"/>
+      <c r="O109" s="155"/>
+      <c r="P109" s="155"/>
+      <c r="Q109" s="155"/>
     </row>
     <row r="110" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A110" s="23" t="str">
@@ -14002,21 +14003,21 @@
       <c r="B110" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C110" s="129"/>
-      <c r="D110" s="129"/>
-      <c r="E110" s="126"/>
-      <c r="F110" s="129"/>
-      <c r="G110" s="129"/>
-      <c r="H110" s="129"/>
-      <c r="I110" s="129"/>
-      <c r="J110" s="129"/>
-      <c r="K110" s="129"/>
-      <c r="L110" s="129"/>
-      <c r="M110" s="129"/>
-      <c r="N110" s="126"/>
-      <c r="O110" s="126"/>
-      <c r="P110" s="126"/>
-      <c r="Q110" s="126"/>
+      <c r="C110" s="128"/>
+      <c r="D110" s="128"/>
+      <c r="E110" s="155"/>
+      <c r="F110" s="128"/>
+      <c r="G110" s="128"/>
+      <c r="H110" s="128"/>
+      <c r="I110" s="128"/>
+      <c r="J110" s="128"/>
+      <c r="K110" s="128"/>
+      <c r="L110" s="128"/>
+      <c r="M110" s="128"/>
+      <c r="N110" s="155"/>
+      <c r="O110" s="155"/>
+      <c r="P110" s="155"/>
+      <c r="Q110" s="155"/>
     </row>
     <row r="111" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A111" s="23" t="str">
@@ -14026,21 +14027,21 @@
       <c r="B111" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C111" s="129"/>
-      <c r="D111" s="129"/>
-      <c r="E111" s="126"/>
-      <c r="F111" s="129"/>
-      <c r="G111" s="129"/>
-      <c r="H111" s="129"/>
-      <c r="I111" s="129"/>
-      <c r="J111" s="129"/>
-      <c r="K111" s="129"/>
-      <c r="L111" s="129"/>
-      <c r="M111" s="129"/>
-      <c r="N111" s="126"/>
-      <c r="O111" s="126"/>
-      <c r="P111" s="126"/>
-      <c r="Q111" s="126"/>
+      <c r="C111" s="128"/>
+      <c r="D111" s="128"/>
+      <c r="E111" s="155"/>
+      <c r="F111" s="128"/>
+      <c r="G111" s="128"/>
+      <c r="H111" s="128"/>
+      <c r="I111" s="128"/>
+      <c r="J111" s="128"/>
+      <c r="K111" s="128"/>
+      <c r="L111" s="128"/>
+      <c r="M111" s="128"/>
+      <c r="N111" s="155"/>
+      <c r="O111" s="155"/>
+      <c r="P111" s="155"/>
+      <c r="Q111" s="155"/>
     </row>
     <row r="112" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="97" t="str">
@@ -14050,21 +14051,21 @@
       <c r="B112" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C112" s="130"/>
-      <c r="D112" s="130"/>
-      <c r="E112" s="127"/>
-      <c r="F112" s="130"/>
-      <c r="G112" s="130"/>
-      <c r="H112" s="130"/>
-      <c r="I112" s="130"/>
-      <c r="J112" s="130"/>
-      <c r="K112" s="130"/>
-      <c r="L112" s="130"/>
-      <c r="M112" s="130"/>
-      <c r="N112" s="127"/>
-      <c r="O112" s="127"/>
-      <c r="P112" s="127"/>
-      <c r="Q112" s="127"/>
+      <c r="C112" s="136"/>
+      <c r="D112" s="136"/>
+      <c r="E112" s="156"/>
+      <c r="F112" s="136"/>
+      <c r="G112" s="136"/>
+      <c r="H112" s="136"/>
+      <c r="I112" s="136"/>
+      <c r="J112" s="136"/>
+      <c r="K112" s="136"/>
+      <c r="L112" s="136"/>
+      <c r="M112" s="136"/>
+      <c r="N112" s="156"/>
+      <c r="O112" s="156"/>
+      <c r="P112" s="156"/>
+      <c r="Q112" s="156"/>
     </row>
     <row r="113" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A113" s="23" t="str">
@@ -14074,48 +14075,48 @@
       <c r="B113" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C113" s="128">
+      <c r="C113" s="135">
         <v>6</v>
       </c>
-      <c r="D113" s="128" t="s">
+      <c r="D113" s="135" t="s">
         <v>303</v>
       </c>
-      <c r="E113" s="125" t="s">
+      <c r="E113" s="154" t="s">
         <v>304</v>
       </c>
-      <c r="F113" s="128" t="s">
+      <c r="F113" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G113" s="128"/>
-      <c r="H113" s="128" t="s">
+      <c r="G113" s="135"/>
+      <c r="H113" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I113" s="128"/>
-      <c r="J113" s="128">
+      <c r="I113" s="135"/>
+      <c r="J113" s="135">
         <v>3</v>
       </c>
-      <c r="K113" s="128">
+      <c r="K113" s="135">
         <f>J113*12</f>
         <v>36</v>
       </c>
-      <c r="L113" s="128">
+      <c r="L113" s="135">
         <f>36*J113</f>
         <v>108</v>
       </c>
-      <c r="M113" s="128">
+      <c r="M113" s="135">
         <f>SUM(K113:L113)</f>
         <v>144</v>
       </c>
-      <c r="N113" s="125" t="s">
+      <c r="N113" s="154" t="s">
         <v>305</v>
       </c>
-      <c r="O113" s="125" t="s">
+      <c r="O113" s="154" t="s">
         <v>195</v>
       </c>
-      <c r="P113" s="125" t="s">
+      <c r="P113" s="154" t="s">
         <v>292</v>
       </c>
-      <c r="Q113" s="125" t="s">
+      <c r="Q113" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -14127,21 +14128,21 @@
       <c r="B114" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C114" s="129"/>
-      <c r="D114" s="129"/>
-      <c r="E114" s="126"/>
-      <c r="F114" s="129"/>
-      <c r="G114" s="129"/>
-      <c r="H114" s="129"/>
-      <c r="I114" s="129"/>
-      <c r="J114" s="129"/>
-      <c r="K114" s="129"/>
-      <c r="L114" s="129"/>
-      <c r="M114" s="129"/>
-      <c r="N114" s="126"/>
-      <c r="O114" s="126"/>
-      <c r="P114" s="126"/>
-      <c r="Q114" s="126"/>
+      <c r="C114" s="128"/>
+      <c r="D114" s="128"/>
+      <c r="E114" s="155"/>
+      <c r="F114" s="128"/>
+      <c r="G114" s="128"/>
+      <c r="H114" s="128"/>
+      <c r="I114" s="128"/>
+      <c r="J114" s="128"/>
+      <c r="K114" s="128"/>
+      <c r="L114" s="128"/>
+      <c r="M114" s="128"/>
+      <c r="N114" s="155"/>
+      <c r="O114" s="155"/>
+      <c r="P114" s="155"/>
+      <c r="Q114" s="155"/>
     </row>
     <row r="115" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A115" s="23" t="str">
@@ -14151,21 +14152,21 @@
       <c r="B115" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C115" s="129"/>
-      <c r="D115" s="129"/>
-      <c r="E115" s="126"/>
-      <c r="F115" s="129"/>
-      <c r="G115" s="129"/>
-      <c r="H115" s="129"/>
-      <c r="I115" s="129"/>
-      <c r="J115" s="129"/>
-      <c r="K115" s="129"/>
-      <c r="L115" s="129"/>
-      <c r="M115" s="129"/>
-      <c r="N115" s="126"/>
-      <c r="O115" s="126"/>
-      <c r="P115" s="126"/>
-      <c r="Q115" s="126"/>
+      <c r="C115" s="128"/>
+      <c r="D115" s="128"/>
+      <c r="E115" s="155"/>
+      <c r="F115" s="128"/>
+      <c r="G115" s="128"/>
+      <c r="H115" s="128"/>
+      <c r="I115" s="128"/>
+      <c r="J115" s="128"/>
+      <c r="K115" s="128"/>
+      <c r="L115" s="128"/>
+      <c r="M115" s="128"/>
+      <c r="N115" s="155"/>
+      <c r="O115" s="155"/>
+      <c r="P115" s="155"/>
+      <c r="Q115" s="155"/>
     </row>
     <row r="116" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="113" t="str">
@@ -14175,21 +14176,21 @@
       <c r="B116" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C116" s="130"/>
-      <c r="D116" s="130"/>
-      <c r="E116" s="127"/>
-      <c r="F116" s="129"/>
-      <c r="G116" s="129"/>
-      <c r="H116" s="129"/>
-      <c r="I116" s="129"/>
-      <c r="J116" s="129"/>
-      <c r="K116" s="129"/>
-      <c r="L116" s="129"/>
-      <c r="M116" s="129"/>
-      <c r="N116" s="126"/>
-      <c r="O116" s="126"/>
-      <c r="P116" s="126"/>
-      <c r="Q116" s="126"/>
+      <c r="C116" s="136"/>
+      <c r="D116" s="136"/>
+      <c r="E116" s="156"/>
+      <c r="F116" s="128"/>
+      <c r="G116" s="128"/>
+      <c r="H116" s="128"/>
+      <c r="I116" s="128"/>
+      <c r="J116" s="128"/>
+      <c r="K116" s="128"/>
+      <c r="L116" s="128"/>
+      <c r="M116" s="128"/>
+      <c r="N116" s="155"/>
+      <c r="O116" s="155"/>
+      <c r="P116" s="155"/>
+      <c r="Q116" s="155"/>
     </row>
     <row r="117" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A117" s="23" t="str">
@@ -14199,48 +14200,48 @@
       <c r="B117" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C117" s="129">
+      <c r="C117" s="128">
         <v>6</v>
       </c>
-      <c r="D117" s="129" t="s">
+      <c r="D117" s="128" t="s">
         <v>306</v>
       </c>
-      <c r="E117" s="126" t="s">
+      <c r="E117" s="155" t="s">
         <v>307</v>
       </c>
-      <c r="F117" s="128" t="s">
+      <c r="F117" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G117" s="128"/>
-      <c r="H117" s="128" t="s">
+      <c r="G117" s="135"/>
+      <c r="H117" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I117" s="128"/>
-      <c r="J117" s="128">
+      <c r="I117" s="135"/>
+      <c r="J117" s="135">
         <v>4</v>
       </c>
-      <c r="K117" s="128">
+      <c r="K117" s="135">
         <f>J117*12</f>
         <v>48</v>
       </c>
-      <c r="L117" s="128">
+      <c r="L117" s="135">
         <f>36*J117</f>
         <v>144</v>
       </c>
-      <c r="M117" s="128">
+      <c r="M117" s="135">
         <f>SUM(K117:L117)</f>
         <v>192</v>
       </c>
-      <c r="N117" s="125" t="s">
+      <c r="N117" s="154" t="s">
         <v>308</v>
       </c>
-      <c r="O117" s="125" t="s">
+      <c r="O117" s="154" t="s">
         <v>302</v>
       </c>
-      <c r="P117" s="125" t="s">
+      <c r="P117" s="154" t="s">
         <v>249</v>
       </c>
-      <c r="Q117" s="125" t="s">
+      <c r="Q117" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -14252,21 +14253,21 @@
       <c r="B118" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C118" s="129"/>
-      <c r="D118" s="129"/>
-      <c r="E118" s="126"/>
-      <c r="F118" s="129"/>
-      <c r="G118" s="129"/>
-      <c r="H118" s="129"/>
-      <c r="I118" s="129"/>
-      <c r="J118" s="129"/>
-      <c r="K118" s="129"/>
-      <c r="L118" s="129"/>
-      <c r="M118" s="129"/>
-      <c r="N118" s="126"/>
-      <c r="O118" s="126"/>
-      <c r="P118" s="126"/>
-      <c r="Q118" s="126"/>
+      <c r="C118" s="128"/>
+      <c r="D118" s="128"/>
+      <c r="E118" s="155"/>
+      <c r="F118" s="128"/>
+      <c r="G118" s="128"/>
+      <c r="H118" s="128"/>
+      <c r="I118" s="128"/>
+      <c r="J118" s="128"/>
+      <c r="K118" s="128"/>
+      <c r="L118" s="128"/>
+      <c r="M118" s="128"/>
+      <c r="N118" s="155"/>
+      <c r="O118" s="155"/>
+      <c r="P118" s="155"/>
+      <c r="Q118" s="155"/>
     </row>
     <row r="119" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A119" s="23" t="str">
@@ -14276,21 +14277,21 @@
       <c r="B119" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C119" s="129"/>
-      <c r="D119" s="129"/>
-      <c r="E119" s="126"/>
-      <c r="F119" s="129"/>
-      <c r="G119" s="129"/>
-      <c r="H119" s="129"/>
-      <c r="I119" s="129"/>
-      <c r="J119" s="129"/>
-      <c r="K119" s="129"/>
-      <c r="L119" s="129"/>
-      <c r="M119" s="129"/>
-      <c r="N119" s="126"/>
-      <c r="O119" s="126"/>
-      <c r="P119" s="126"/>
-      <c r="Q119" s="126"/>
+      <c r="C119" s="128"/>
+      <c r="D119" s="128"/>
+      <c r="E119" s="155"/>
+      <c r="F119" s="128"/>
+      <c r="G119" s="128"/>
+      <c r="H119" s="128"/>
+      <c r="I119" s="128"/>
+      <c r="J119" s="128"/>
+      <c r="K119" s="128"/>
+      <c r="L119" s="128"/>
+      <c r="M119" s="128"/>
+      <c r="N119" s="155"/>
+      <c r="O119" s="155"/>
+      <c r="P119" s="155"/>
+      <c r="Q119" s="155"/>
     </row>
     <row r="120" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A120" s="23" t="str">
@@ -14300,21 +14301,21 @@
       <c r="B120" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C120" s="129"/>
-      <c r="D120" s="129"/>
-      <c r="E120" s="126"/>
-      <c r="F120" s="129"/>
-      <c r="G120" s="129"/>
-      <c r="H120" s="129"/>
-      <c r="I120" s="129"/>
-      <c r="J120" s="129"/>
-      <c r="K120" s="129"/>
-      <c r="L120" s="129"/>
-      <c r="M120" s="129"/>
-      <c r="N120" s="126"/>
-      <c r="O120" s="126"/>
-      <c r="P120" s="126"/>
-      <c r="Q120" s="126"/>
+      <c r="C120" s="128"/>
+      <c r="D120" s="128"/>
+      <c r="E120" s="155"/>
+      <c r="F120" s="128"/>
+      <c r="G120" s="128"/>
+      <c r="H120" s="128"/>
+      <c r="I120" s="128"/>
+      <c r="J120" s="128"/>
+      <c r="K120" s="128"/>
+      <c r="L120" s="128"/>
+      <c r="M120" s="128"/>
+      <c r="N120" s="155"/>
+      <c r="O120" s="155"/>
+      <c r="P120" s="155"/>
+      <c r="Q120" s="155"/>
     </row>
     <row r="121" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="97" t="str">
@@ -14324,21 +14325,21 @@
       <c r="B121" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C121" s="130"/>
-      <c r="D121" s="130"/>
-      <c r="E121" s="138"/>
-      <c r="F121" s="134"/>
-      <c r="G121" s="134"/>
-      <c r="H121" s="134"/>
-      <c r="I121" s="134"/>
-      <c r="J121" s="134"/>
-      <c r="K121" s="134"/>
-      <c r="L121" s="134"/>
-      <c r="M121" s="134"/>
-      <c r="N121" s="138"/>
-      <c r="O121" s="127"/>
-      <c r="P121" s="127"/>
-      <c r="Q121" s="127"/>
+      <c r="C121" s="136"/>
+      <c r="D121" s="136"/>
+      <c r="E121" s="164"/>
+      <c r="F121" s="160"/>
+      <c r="G121" s="160"/>
+      <c r="H121" s="160"/>
+      <c r="I121" s="160"/>
+      <c r="J121" s="160"/>
+      <c r="K121" s="160"/>
+      <c r="L121" s="160"/>
+      <c r="M121" s="160"/>
+      <c r="N121" s="164"/>
+      <c r="O121" s="156"/>
+      <c r="P121" s="156"/>
+      <c r="Q121" s="156"/>
     </row>
     <row r="122" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A122" s="23" t="str">
@@ -14348,48 +14349,48 @@
       <c r="B122" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C122" s="128">
+      <c r="C122" s="135">
         <v>7</v>
       </c>
-      <c r="D122" s="128" t="s">
+      <c r="D122" s="135" t="s">
         <v>309</v>
       </c>
-      <c r="E122" s="133" t="s">
+      <c r="E122" s="159" t="s">
         <v>310</v>
       </c>
-      <c r="F122" s="128" t="s">
+      <c r="F122" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G122" s="128"/>
-      <c r="H122" s="128" t="s">
+      <c r="G122" s="135"/>
+      <c r="H122" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I122" s="128"/>
-      <c r="J122" s="128">
+      <c r="I122" s="135"/>
+      <c r="J122" s="135">
         <v>3</v>
       </c>
-      <c r="K122" s="128">
+      <c r="K122" s="135">
         <f>J122*12</f>
         <v>36</v>
       </c>
-      <c r="L122" s="128">
+      <c r="L122" s="135">
         <f>36*J122</f>
         <v>108</v>
       </c>
-      <c r="M122" s="128">
+      <c r="M122" s="135">
         <f>SUM(K122:L122)</f>
         <v>144</v>
       </c>
-      <c r="N122" s="125" t="s">
+      <c r="N122" s="154" t="s">
         <v>311</v>
       </c>
-      <c r="O122" s="125" t="s">
+      <c r="O122" s="154" t="s">
         <v>195</v>
       </c>
-      <c r="P122" s="125" t="s">
+      <c r="P122" s="154" t="s">
         <v>312</v>
       </c>
-      <c r="Q122" s="125" t="s">
+      <c r="Q122" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -14401,21 +14402,21 @@
       <c r="B123" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C123" s="129"/>
-      <c r="D123" s="129"/>
-      <c r="E123" s="126"/>
-      <c r="F123" s="129"/>
-      <c r="G123" s="129"/>
-      <c r="H123" s="129"/>
-      <c r="I123" s="129"/>
-      <c r="J123" s="129"/>
-      <c r="K123" s="129"/>
-      <c r="L123" s="129"/>
-      <c r="M123" s="129"/>
-      <c r="N123" s="126"/>
-      <c r="O123" s="126"/>
-      <c r="P123" s="126"/>
-      <c r="Q123" s="126"/>
+      <c r="C123" s="128"/>
+      <c r="D123" s="128"/>
+      <c r="E123" s="155"/>
+      <c r="F123" s="128"/>
+      <c r="G123" s="128"/>
+      <c r="H123" s="128"/>
+      <c r="I123" s="128"/>
+      <c r="J123" s="128"/>
+      <c r="K123" s="128"/>
+      <c r="L123" s="128"/>
+      <c r="M123" s="128"/>
+      <c r="N123" s="155"/>
+      <c r="O123" s="155"/>
+      <c r="P123" s="155"/>
+      <c r="Q123" s="155"/>
     </row>
     <row r="124" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A124" s="23" t="str">
@@ -14425,21 +14426,21 @@
       <c r="B124" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C124" s="129"/>
-      <c r="D124" s="129"/>
-      <c r="E124" s="126"/>
-      <c r="F124" s="129"/>
-      <c r="G124" s="129"/>
-      <c r="H124" s="129"/>
-      <c r="I124" s="129"/>
-      <c r="J124" s="129"/>
-      <c r="K124" s="129"/>
-      <c r="L124" s="129"/>
-      <c r="M124" s="129"/>
-      <c r="N124" s="126"/>
-      <c r="O124" s="126"/>
-      <c r="P124" s="126"/>
-      <c r="Q124" s="126"/>
+      <c r="C124" s="128"/>
+      <c r="D124" s="128"/>
+      <c r="E124" s="155"/>
+      <c r="F124" s="128"/>
+      <c r="G124" s="128"/>
+      <c r="H124" s="128"/>
+      <c r="I124" s="128"/>
+      <c r="J124" s="128"/>
+      <c r="K124" s="128"/>
+      <c r="L124" s="128"/>
+      <c r="M124" s="128"/>
+      <c r="N124" s="155"/>
+      <c r="O124" s="155"/>
+      <c r="P124" s="155"/>
+      <c r="Q124" s="155"/>
     </row>
     <row r="125" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A125" s="23" t="str">
@@ -14449,21 +14450,21 @@
       <c r="B125" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C125" s="129"/>
-      <c r="D125" s="129"/>
-      <c r="E125" s="126"/>
-      <c r="F125" s="129"/>
-      <c r="G125" s="129"/>
-      <c r="H125" s="129"/>
-      <c r="I125" s="129"/>
-      <c r="J125" s="129"/>
-      <c r="K125" s="129"/>
-      <c r="L125" s="129"/>
-      <c r="M125" s="129"/>
-      <c r="N125" s="126"/>
-      <c r="O125" s="126"/>
-      <c r="P125" s="126"/>
-      <c r="Q125" s="126"/>
+      <c r="C125" s="128"/>
+      <c r="D125" s="128"/>
+      <c r="E125" s="155"/>
+      <c r="F125" s="128"/>
+      <c r="G125" s="128"/>
+      <c r="H125" s="128"/>
+      <c r="I125" s="128"/>
+      <c r="J125" s="128"/>
+      <c r="K125" s="128"/>
+      <c r="L125" s="128"/>
+      <c r="M125" s="128"/>
+      <c r="N125" s="155"/>
+      <c r="O125" s="155"/>
+      <c r="P125" s="155"/>
+      <c r="Q125" s="155"/>
     </row>
     <row r="126" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="97" t="str">
@@ -14473,21 +14474,21 @@
       <c r="B126" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C126" s="130"/>
-      <c r="D126" s="130"/>
-      <c r="E126" s="127"/>
-      <c r="F126" s="130"/>
-      <c r="G126" s="130"/>
-      <c r="H126" s="130"/>
-      <c r="I126" s="130"/>
-      <c r="J126" s="130"/>
-      <c r="K126" s="130"/>
-      <c r="L126" s="130"/>
-      <c r="M126" s="130"/>
-      <c r="N126" s="127"/>
-      <c r="O126" s="127"/>
-      <c r="P126" s="127"/>
-      <c r="Q126" s="127"/>
+      <c r="C126" s="136"/>
+      <c r="D126" s="136"/>
+      <c r="E126" s="156"/>
+      <c r="F126" s="136"/>
+      <c r="G126" s="136"/>
+      <c r="H126" s="136"/>
+      <c r="I126" s="136"/>
+      <c r="J126" s="136"/>
+      <c r="K126" s="136"/>
+      <c r="L126" s="136"/>
+      <c r="M126" s="136"/>
+      <c r="N126" s="156"/>
+      <c r="O126" s="156"/>
+      <c r="P126" s="156"/>
+      <c r="Q126" s="156"/>
     </row>
     <row r="127" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A127" s="23" t="str">
@@ -14497,48 +14498,48 @@
       <c r="B127" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C127" s="128">
+      <c r="C127" s="135">
         <v>7</v>
       </c>
-      <c r="D127" s="128" t="s">
+      <c r="D127" s="135" t="s">
         <v>313</v>
       </c>
-      <c r="E127" s="135" t="s">
+      <c r="E127" s="161" t="s">
         <v>314</v>
       </c>
-      <c r="F127" s="128" t="s">
+      <c r="F127" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G127" s="128"/>
-      <c r="H127" s="128" t="s">
+      <c r="G127" s="135"/>
+      <c r="H127" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I127" s="128"/>
-      <c r="J127" s="128">
+      <c r="I127" s="135"/>
+      <c r="J127" s="135">
         <v>4</v>
       </c>
-      <c r="K127" s="128">
+      <c r="K127" s="135">
         <f>J127*12</f>
         <v>48</v>
       </c>
-      <c r="L127" s="128">
+      <c r="L127" s="135">
         <f>36*J127</f>
         <v>144</v>
       </c>
-      <c r="M127" s="128">
+      <c r="M127" s="135">
         <f>SUM(K127:L127)</f>
         <v>192</v>
       </c>
-      <c r="N127" s="125" t="s">
+      <c r="N127" s="154" t="s">
         <v>315</v>
       </c>
-      <c r="O127" s="125" t="s">
+      <c r="O127" s="154" t="s">
         <v>302</v>
       </c>
-      <c r="P127" s="125" t="s">
+      <c r="P127" s="154" t="s">
         <v>274</v>
       </c>
-      <c r="Q127" s="125" t="s">
+      <c r="Q127" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -14550,21 +14551,21 @@
       <c r="B128" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C128" s="129"/>
-      <c r="D128" s="129"/>
-      <c r="E128" s="131"/>
-      <c r="F128" s="129"/>
-      <c r="G128" s="129"/>
-      <c r="H128" s="129"/>
-      <c r="I128" s="129"/>
-      <c r="J128" s="129"/>
-      <c r="K128" s="129"/>
-      <c r="L128" s="129"/>
-      <c r="M128" s="129"/>
-      <c r="N128" s="126"/>
-      <c r="O128" s="126"/>
-      <c r="P128" s="126"/>
-      <c r="Q128" s="126"/>
+      <c r="C128" s="128"/>
+      <c r="D128" s="128"/>
+      <c r="E128" s="157"/>
+      <c r="F128" s="128"/>
+      <c r="G128" s="128"/>
+      <c r="H128" s="128"/>
+      <c r="I128" s="128"/>
+      <c r="J128" s="128"/>
+      <c r="K128" s="128"/>
+      <c r="L128" s="128"/>
+      <c r="M128" s="128"/>
+      <c r="N128" s="155"/>
+      <c r="O128" s="155"/>
+      <c r="P128" s="155"/>
+      <c r="Q128" s="155"/>
     </row>
     <row r="129" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A129" s="23" t="str">
@@ -14574,21 +14575,21 @@
       <c r="B129" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C129" s="129"/>
-      <c r="D129" s="129"/>
-      <c r="E129" s="131"/>
-      <c r="F129" s="129"/>
-      <c r="G129" s="129"/>
-      <c r="H129" s="129"/>
-      <c r="I129" s="129"/>
-      <c r="J129" s="129"/>
-      <c r="K129" s="129"/>
-      <c r="L129" s="129"/>
-      <c r="M129" s="129"/>
-      <c r="N129" s="126"/>
-      <c r="O129" s="126"/>
-      <c r="P129" s="126"/>
-      <c r="Q129" s="126"/>
+      <c r="C129" s="128"/>
+      <c r="D129" s="128"/>
+      <c r="E129" s="157"/>
+      <c r="F129" s="128"/>
+      <c r="G129" s="128"/>
+      <c r="H129" s="128"/>
+      <c r="I129" s="128"/>
+      <c r="J129" s="128"/>
+      <c r="K129" s="128"/>
+      <c r="L129" s="128"/>
+      <c r="M129" s="128"/>
+      <c r="N129" s="155"/>
+      <c r="O129" s="155"/>
+      <c r="P129" s="155"/>
+      <c r="Q129" s="155"/>
     </row>
     <row r="130" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A130" s="23" t="str">
@@ -14598,21 +14599,21 @@
       <c r="B130" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C130" s="129"/>
-      <c r="D130" s="129"/>
-      <c r="E130" s="131"/>
-      <c r="F130" s="129"/>
-      <c r="G130" s="129"/>
-      <c r="H130" s="129"/>
-      <c r="I130" s="129"/>
-      <c r="J130" s="129"/>
-      <c r="K130" s="129"/>
-      <c r="L130" s="129"/>
-      <c r="M130" s="129"/>
-      <c r="N130" s="126"/>
-      <c r="O130" s="126"/>
-      <c r="P130" s="126"/>
-      <c r="Q130" s="126"/>
+      <c r="C130" s="128"/>
+      <c r="D130" s="128"/>
+      <c r="E130" s="157"/>
+      <c r="F130" s="128"/>
+      <c r="G130" s="128"/>
+      <c r="H130" s="128"/>
+      <c r="I130" s="128"/>
+      <c r="J130" s="128"/>
+      <c r="K130" s="128"/>
+      <c r="L130" s="128"/>
+      <c r="M130" s="128"/>
+      <c r="N130" s="155"/>
+      <c r="O130" s="155"/>
+      <c r="P130" s="155"/>
+      <c r="Q130" s="155"/>
     </row>
     <row r="131" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="97" t="str">
@@ -14622,21 +14623,21 @@
       <c r="B131" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C131" s="130"/>
-      <c r="D131" s="130"/>
-      <c r="E131" s="132"/>
-      <c r="F131" s="130"/>
-      <c r="G131" s="130"/>
-      <c r="H131" s="130"/>
-      <c r="I131" s="130"/>
-      <c r="J131" s="130"/>
-      <c r="K131" s="130"/>
-      <c r="L131" s="130"/>
-      <c r="M131" s="130"/>
-      <c r="N131" s="127"/>
-      <c r="O131" s="127"/>
-      <c r="P131" s="127"/>
-      <c r="Q131" s="127"/>
+      <c r="C131" s="136"/>
+      <c r="D131" s="136"/>
+      <c r="E131" s="158"/>
+      <c r="F131" s="136"/>
+      <c r="G131" s="136"/>
+      <c r="H131" s="136"/>
+      <c r="I131" s="136"/>
+      <c r="J131" s="136"/>
+      <c r="K131" s="136"/>
+      <c r="L131" s="136"/>
+      <c r="M131" s="136"/>
+      <c r="N131" s="156"/>
+      <c r="O131" s="156"/>
+      <c r="P131" s="156"/>
+      <c r="Q131" s="156"/>
     </row>
     <row r="132" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A132" s="23" t="str">
@@ -14646,48 +14647,48 @@
       <c r="B132" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C132" s="128">
+      <c r="C132" s="135">
         <v>7</v>
       </c>
-      <c r="D132" s="128" t="s">
+      <c r="D132" s="135" t="s">
         <v>316</v>
       </c>
-      <c r="E132" s="125" t="s">
+      <c r="E132" s="154" t="s">
         <v>317</v>
       </c>
-      <c r="F132" s="128" t="s">
+      <c r="F132" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G132" s="128"/>
-      <c r="H132" s="128" t="s">
+      <c r="G132" s="135"/>
+      <c r="H132" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I132" s="128"/>
-      <c r="J132" s="128">
+      <c r="I132" s="135"/>
+      <c r="J132" s="135">
         <v>3</v>
       </c>
-      <c r="K132" s="128">
+      <c r="K132" s="135">
         <f>J132*12</f>
         <v>36</v>
       </c>
-      <c r="L132" s="128">
+      <c r="L132" s="135">
         <f>36*J132</f>
         <v>108</v>
       </c>
-      <c r="M132" s="128">
+      <c r="M132" s="135">
         <f>SUM(K132:L132)</f>
         <v>144</v>
       </c>
-      <c r="N132" s="125" t="s">
+      <c r="N132" s="154" t="s">
         <v>318</v>
       </c>
-      <c r="O132" s="125" t="s">
+      <c r="O132" s="154" t="s">
         <v>302</v>
       </c>
-      <c r="P132" s="125" t="s">
+      <c r="P132" s="154" t="s">
         <v>319</v>
       </c>
-      <c r="Q132" s="125" t="s">
+      <c r="Q132" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -14699,21 +14700,21 @@
       <c r="B133" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C133" s="129"/>
-      <c r="D133" s="129"/>
-      <c r="E133" s="126"/>
-      <c r="F133" s="129"/>
-      <c r="G133" s="129"/>
-      <c r="H133" s="129"/>
-      <c r="I133" s="129"/>
-      <c r="J133" s="129"/>
-      <c r="K133" s="129"/>
-      <c r="L133" s="129"/>
-      <c r="M133" s="129"/>
-      <c r="N133" s="126"/>
-      <c r="O133" s="126"/>
-      <c r="P133" s="126"/>
-      <c r="Q133" s="126"/>
+      <c r="C133" s="128"/>
+      <c r="D133" s="128"/>
+      <c r="E133" s="155"/>
+      <c r="F133" s="128"/>
+      <c r="G133" s="128"/>
+      <c r="H133" s="128"/>
+      <c r="I133" s="128"/>
+      <c r="J133" s="128"/>
+      <c r="K133" s="128"/>
+      <c r="L133" s="128"/>
+      <c r="M133" s="128"/>
+      <c r="N133" s="155"/>
+      <c r="O133" s="155"/>
+      <c r="P133" s="155"/>
+      <c r="Q133" s="155"/>
     </row>
     <row r="134" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A134" s="23" t="str">
@@ -14723,21 +14724,21 @@
       <c r="B134" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C134" s="129"/>
-      <c r="D134" s="129"/>
-      <c r="E134" s="126"/>
-      <c r="F134" s="129"/>
-      <c r="G134" s="129"/>
-      <c r="H134" s="129"/>
-      <c r="I134" s="129"/>
-      <c r="J134" s="129"/>
-      <c r="K134" s="129"/>
-      <c r="L134" s="129"/>
-      <c r="M134" s="129"/>
-      <c r="N134" s="126"/>
-      <c r="O134" s="126"/>
-      <c r="P134" s="126"/>
-      <c r="Q134" s="126"/>
+      <c r="C134" s="128"/>
+      <c r="D134" s="128"/>
+      <c r="E134" s="155"/>
+      <c r="F134" s="128"/>
+      <c r="G134" s="128"/>
+      <c r="H134" s="128"/>
+      <c r="I134" s="128"/>
+      <c r="J134" s="128"/>
+      <c r="K134" s="128"/>
+      <c r="L134" s="128"/>
+      <c r="M134" s="128"/>
+      <c r="N134" s="155"/>
+      <c r="O134" s="155"/>
+      <c r="P134" s="155"/>
+      <c r="Q134" s="155"/>
     </row>
     <row r="135" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="97" t="str">
@@ -14747,21 +14748,21 @@
       <c r="B135" s="98" t="s">
         <v>104</v>
       </c>
-      <c r="C135" s="130"/>
-      <c r="D135" s="130"/>
-      <c r="E135" s="127"/>
-      <c r="F135" s="130"/>
-      <c r="G135" s="130"/>
-      <c r="H135" s="130"/>
-      <c r="I135" s="130"/>
-      <c r="J135" s="130"/>
-      <c r="K135" s="130"/>
-      <c r="L135" s="130"/>
-      <c r="M135" s="130"/>
-      <c r="N135" s="127"/>
-      <c r="O135" s="127"/>
-      <c r="P135" s="127"/>
-      <c r="Q135" s="127"/>
+      <c r="C135" s="136"/>
+      <c r="D135" s="136"/>
+      <c r="E135" s="156"/>
+      <c r="F135" s="136"/>
+      <c r="G135" s="136"/>
+      <c r="H135" s="136"/>
+      <c r="I135" s="136"/>
+      <c r="J135" s="136"/>
+      <c r="K135" s="136"/>
+      <c r="L135" s="136"/>
+      <c r="M135" s="136"/>
+      <c r="N135" s="156"/>
+      <c r="O135" s="156"/>
+      <c r="P135" s="156"/>
+      <c r="Q135" s="156"/>
     </row>
     <row r="136" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A136" s="23" t="str">
@@ -14771,48 +14772,48 @@
       <c r="B136" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C136" s="128">
+      <c r="C136" s="135">
         <v>7</v>
       </c>
-      <c r="D136" s="128" t="s">
+      <c r="D136" s="135" t="s">
         <v>320</v>
       </c>
-      <c r="E136" s="135" t="s">
+      <c r="E136" s="161" t="s">
         <v>321</v>
       </c>
-      <c r="F136" s="128" t="s">
+      <c r="F136" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G136" s="128"/>
-      <c r="H136" s="128" t="s">
+      <c r="G136" s="135"/>
+      <c r="H136" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I136" s="128"/>
-      <c r="J136" s="128">
+      <c r="I136" s="135"/>
+      <c r="J136" s="135">
         <v>4</v>
       </c>
-      <c r="K136" s="128">
+      <c r="K136" s="135">
         <f>J136*12</f>
         <v>48</v>
       </c>
-      <c r="L136" s="128">
+      <c r="L136" s="135">
         <f>36*J136</f>
         <v>144</v>
       </c>
-      <c r="M136" s="128">
+      <c r="M136" s="135">
         <f>SUM(K136:L136)</f>
         <v>192</v>
       </c>
-      <c r="N136" s="125" t="s">
+      <c r="N136" s="154" t="s">
         <v>322</v>
       </c>
-      <c r="O136" s="125" t="s">
+      <c r="O136" s="154" t="s">
         <v>195</v>
       </c>
-      <c r="P136" s="125" t="s">
+      <c r="P136" s="154" t="s">
         <v>274</v>
       </c>
-      <c r="Q136" s="125" t="s">
+      <c r="Q136" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -14824,21 +14825,21 @@
       <c r="B137" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C137" s="129"/>
-      <c r="D137" s="129"/>
-      <c r="E137" s="131"/>
-      <c r="F137" s="129"/>
-      <c r="G137" s="129"/>
-      <c r="H137" s="129"/>
-      <c r="I137" s="129"/>
-      <c r="J137" s="129"/>
-      <c r="K137" s="129"/>
-      <c r="L137" s="129"/>
-      <c r="M137" s="129"/>
-      <c r="N137" s="126"/>
-      <c r="O137" s="126"/>
-      <c r="P137" s="126"/>
-      <c r="Q137" s="126"/>
+      <c r="C137" s="128"/>
+      <c r="D137" s="128"/>
+      <c r="E137" s="157"/>
+      <c r="F137" s="128"/>
+      <c r="G137" s="128"/>
+      <c r="H137" s="128"/>
+      <c r="I137" s="128"/>
+      <c r="J137" s="128"/>
+      <c r="K137" s="128"/>
+      <c r="L137" s="128"/>
+      <c r="M137" s="128"/>
+      <c r="N137" s="155"/>
+      <c r="O137" s="155"/>
+      <c r="P137" s="155"/>
+      <c r="Q137" s="155"/>
     </row>
     <row r="138" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A138" s="23" t="str">
@@ -14848,21 +14849,21 @@
       <c r="B138" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C138" s="129"/>
-      <c r="D138" s="129"/>
-      <c r="E138" s="131"/>
-      <c r="F138" s="129"/>
-      <c r="G138" s="129"/>
-      <c r="H138" s="129"/>
-      <c r="I138" s="129"/>
-      <c r="J138" s="129"/>
-      <c r="K138" s="129"/>
-      <c r="L138" s="129"/>
-      <c r="M138" s="129"/>
-      <c r="N138" s="126"/>
-      <c r="O138" s="126"/>
-      <c r="P138" s="126"/>
-      <c r="Q138" s="126"/>
+      <c r="C138" s="128"/>
+      <c r="D138" s="128"/>
+      <c r="E138" s="157"/>
+      <c r="F138" s="128"/>
+      <c r="G138" s="128"/>
+      <c r="H138" s="128"/>
+      <c r="I138" s="128"/>
+      <c r="J138" s="128"/>
+      <c r="K138" s="128"/>
+      <c r="L138" s="128"/>
+      <c r="M138" s="128"/>
+      <c r="N138" s="155"/>
+      <c r="O138" s="155"/>
+      <c r="P138" s="155"/>
+      <c r="Q138" s="155"/>
     </row>
     <row r="139" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A139" s="23" t="str">
@@ -14872,21 +14873,21 @@
       <c r="B139" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C139" s="129"/>
-      <c r="D139" s="129"/>
-      <c r="E139" s="131"/>
-      <c r="F139" s="129"/>
-      <c r="G139" s="129"/>
-      <c r="H139" s="129"/>
-      <c r="I139" s="129"/>
-      <c r="J139" s="129"/>
-      <c r="K139" s="129"/>
-      <c r="L139" s="129"/>
-      <c r="M139" s="129"/>
-      <c r="N139" s="126"/>
-      <c r="O139" s="126"/>
-      <c r="P139" s="126"/>
-      <c r="Q139" s="126"/>
+      <c r="C139" s="128"/>
+      <c r="D139" s="128"/>
+      <c r="E139" s="157"/>
+      <c r="F139" s="128"/>
+      <c r="G139" s="128"/>
+      <c r="H139" s="128"/>
+      <c r="I139" s="128"/>
+      <c r="J139" s="128"/>
+      <c r="K139" s="128"/>
+      <c r="L139" s="128"/>
+      <c r="M139" s="128"/>
+      <c r="N139" s="155"/>
+      <c r="O139" s="155"/>
+      <c r="P139" s="155"/>
+      <c r="Q139" s="155"/>
     </row>
     <row r="140" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="97" t="str">
@@ -14896,21 +14897,21 @@
       <c r="B140" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C140" s="130"/>
-      <c r="D140" s="134"/>
-      <c r="E140" s="136"/>
-      <c r="F140" s="130"/>
-      <c r="G140" s="130"/>
-      <c r="H140" s="130"/>
-      <c r="I140" s="130"/>
-      <c r="J140" s="130"/>
-      <c r="K140" s="130"/>
-      <c r="L140" s="130"/>
-      <c r="M140" s="130"/>
-      <c r="N140" s="127"/>
-      <c r="O140" s="127"/>
-      <c r="P140" s="127"/>
-      <c r="Q140" s="127"/>
+      <c r="C140" s="136"/>
+      <c r="D140" s="160"/>
+      <c r="E140" s="162"/>
+      <c r="F140" s="136"/>
+      <c r="G140" s="136"/>
+      <c r="H140" s="136"/>
+      <c r="I140" s="136"/>
+      <c r="J140" s="136"/>
+      <c r="K140" s="136"/>
+      <c r="L140" s="136"/>
+      <c r="M140" s="136"/>
+      <c r="N140" s="156"/>
+      <c r="O140" s="156"/>
+      <c r="P140" s="156"/>
+      <c r="Q140" s="156"/>
     </row>
     <row r="141" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A141" s="23" t="str">
@@ -14920,48 +14921,48 @@
       <c r="B141" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C141" s="128">
+      <c r="C141" s="135">
         <v>7</v>
       </c>
-      <c r="D141" s="128" t="s">
+      <c r="D141" s="135" t="s">
         <v>323</v>
       </c>
-      <c r="E141" s="133" t="s">
+      <c r="E141" s="159" t="s">
         <v>324</v>
       </c>
-      <c r="F141" s="128" t="s">
+      <c r="F141" s="135" t="s">
         <v>185</v>
       </c>
-      <c r="G141" s="128"/>
-      <c r="H141" s="128" t="s">
+      <c r="G141" s="135"/>
+      <c r="H141" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I141" s="128"/>
-      <c r="J141" s="128">
+      <c r="I141" s="135"/>
+      <c r="J141" s="135">
         <v>4</v>
       </c>
-      <c r="K141" s="128">
+      <c r="K141" s="135">
         <f>J141*12</f>
         <v>48</v>
       </c>
-      <c r="L141" s="128">
+      <c r="L141" s="135">
         <f>36*J141</f>
         <v>144</v>
       </c>
-      <c r="M141" s="128">
+      <c r="M141" s="135">
         <f>SUM(K141:L141)</f>
         <v>192</v>
       </c>
-      <c r="N141" s="125" t="s">
+      <c r="N141" s="154" t="s">
         <v>325</v>
       </c>
-      <c r="O141" s="125" t="s">
+      <c r="O141" s="154" t="s">
         <v>195</v>
       </c>
-      <c r="P141" s="125" t="s">
+      <c r="P141" s="154" t="s">
         <v>274</v>
       </c>
-      <c r="Q141" s="125" t="s">
+      <c r="Q141" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -14973,21 +14974,21 @@
       <c r="B142" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C142" s="129"/>
-      <c r="D142" s="129"/>
-      <c r="E142" s="126"/>
-      <c r="F142" s="129"/>
-      <c r="G142" s="129"/>
-      <c r="H142" s="129"/>
-      <c r="I142" s="129"/>
-      <c r="J142" s="129"/>
-      <c r="K142" s="129"/>
-      <c r="L142" s="129"/>
-      <c r="M142" s="129"/>
-      <c r="N142" s="126"/>
-      <c r="O142" s="126"/>
-      <c r="P142" s="126"/>
-      <c r="Q142" s="126"/>
+      <c r="C142" s="128"/>
+      <c r="D142" s="128"/>
+      <c r="E142" s="155"/>
+      <c r="F142" s="128"/>
+      <c r="G142" s="128"/>
+      <c r="H142" s="128"/>
+      <c r="I142" s="128"/>
+      <c r="J142" s="128"/>
+      <c r="K142" s="128"/>
+      <c r="L142" s="128"/>
+      <c r="M142" s="128"/>
+      <c r="N142" s="155"/>
+      <c r="O142" s="155"/>
+      <c r="P142" s="155"/>
+      <c r="Q142" s="155"/>
     </row>
     <row r="143" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A143" s="23" t="str">
@@ -14997,21 +14998,21 @@
       <c r="B143" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C143" s="129"/>
-      <c r="D143" s="129"/>
-      <c r="E143" s="126"/>
-      <c r="F143" s="129"/>
-      <c r="G143" s="129"/>
-      <c r="H143" s="129"/>
-      <c r="I143" s="129"/>
-      <c r="J143" s="129"/>
-      <c r="K143" s="129"/>
-      <c r="L143" s="129"/>
-      <c r="M143" s="129"/>
-      <c r="N143" s="126"/>
-      <c r="O143" s="126"/>
-      <c r="P143" s="126"/>
-      <c r="Q143" s="126"/>
+      <c r="C143" s="128"/>
+      <c r="D143" s="128"/>
+      <c r="E143" s="155"/>
+      <c r="F143" s="128"/>
+      <c r="G143" s="128"/>
+      <c r="H143" s="128"/>
+      <c r="I143" s="128"/>
+      <c r="J143" s="128"/>
+      <c r="K143" s="128"/>
+      <c r="L143" s="128"/>
+      <c r="M143" s="128"/>
+      <c r="N143" s="155"/>
+      <c r="O143" s="155"/>
+      <c r="P143" s="155"/>
+      <c r="Q143" s="155"/>
     </row>
     <row r="144" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A144" s="23" t="str">
@@ -15021,21 +15022,21 @@
       <c r="B144" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C144" s="129"/>
-      <c r="D144" s="129"/>
-      <c r="E144" s="126"/>
-      <c r="F144" s="129"/>
-      <c r="G144" s="129"/>
-      <c r="H144" s="129"/>
-      <c r="I144" s="129"/>
-      <c r="J144" s="129"/>
-      <c r="K144" s="129"/>
-      <c r="L144" s="129"/>
-      <c r="M144" s="129"/>
-      <c r="N144" s="126"/>
-      <c r="O144" s="126"/>
-      <c r="P144" s="126"/>
-      <c r="Q144" s="126"/>
+      <c r="C144" s="128"/>
+      <c r="D144" s="128"/>
+      <c r="E144" s="155"/>
+      <c r="F144" s="128"/>
+      <c r="G144" s="128"/>
+      <c r="H144" s="128"/>
+      <c r="I144" s="128"/>
+      <c r="J144" s="128"/>
+      <c r="K144" s="128"/>
+      <c r="L144" s="128"/>
+      <c r="M144" s="128"/>
+      <c r="N144" s="155"/>
+      <c r="O144" s="155"/>
+      <c r="P144" s="155"/>
+      <c r="Q144" s="155"/>
     </row>
     <row r="145" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="97" t="str">
@@ -15045,21 +15046,21 @@
       <c r="B145" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C145" s="130"/>
-      <c r="D145" s="130"/>
-      <c r="E145" s="127"/>
-      <c r="F145" s="130"/>
-      <c r="G145" s="130"/>
-      <c r="H145" s="130"/>
-      <c r="I145" s="130"/>
-      <c r="J145" s="130"/>
-      <c r="K145" s="130"/>
-      <c r="L145" s="130"/>
-      <c r="M145" s="130"/>
-      <c r="N145" s="127"/>
-      <c r="O145" s="127"/>
-      <c r="P145" s="127"/>
-      <c r="Q145" s="127"/>
+      <c r="C145" s="136"/>
+      <c r="D145" s="136"/>
+      <c r="E145" s="156"/>
+      <c r="F145" s="136"/>
+      <c r="G145" s="136"/>
+      <c r="H145" s="136"/>
+      <c r="I145" s="136"/>
+      <c r="J145" s="136"/>
+      <c r="K145" s="136"/>
+      <c r="L145" s="136"/>
+      <c r="M145" s="136"/>
+      <c r="N145" s="156"/>
+      <c r="O145" s="156"/>
+      <c r="P145" s="156"/>
+      <c r="Q145" s="156"/>
     </row>
     <row r="146" spans="1:17" s="52" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A146" s="23" t="str">
@@ -15069,48 +15070,48 @@
       <c r="B146" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C146" s="128">
+      <c r="C146" s="135">
         <v>8</v>
       </c>
-      <c r="D146" s="129" t="s">
+      <c r="D146" s="128" t="s">
         <v>326</v>
       </c>
-      <c r="E146" s="131" t="s">
+      <c r="E146" s="157" t="s">
         <v>327</v>
       </c>
-      <c r="F146" s="128" t="s">
+      <c r="F146" s="135" t="s">
         <v>328</v>
       </c>
-      <c r="G146" s="128"/>
-      <c r="H146" s="128" t="s">
+      <c r="G146" s="135"/>
+      <c r="H146" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="I146" s="128"/>
-      <c r="J146" s="128">
+      <c r="I146" s="135"/>
+      <c r="J146" s="135">
         <v>4</v>
       </c>
-      <c r="K146" s="128">
+      <c r="K146" s="135">
         <f>J146*12</f>
         <v>48</v>
       </c>
-      <c r="L146" s="128">
+      <c r="L146" s="135">
         <f>36*J146</f>
         <v>144</v>
       </c>
-      <c r="M146" s="128">
+      <c r="M146" s="135">
         <f>SUM(K146:L146)</f>
         <v>192</v>
       </c>
-      <c r="N146" s="125" t="s">
+      <c r="N146" s="154" t="s">
         <v>329</v>
       </c>
-      <c r="O146" s="125" t="s">
+      <c r="O146" s="154" t="s">
         <v>195</v>
       </c>
-      <c r="P146" s="125" t="s">
+      <c r="P146" s="154" t="s">
         <v>330</v>
       </c>
-      <c r="Q146" s="125" t="s">
+      <c r="Q146" s="154" t="s">
         <v>190</v>
       </c>
     </row>
@@ -15122,21 +15123,21 @@
       <c r="B147" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C147" s="129"/>
-      <c r="D147" s="129"/>
-      <c r="E147" s="131"/>
-      <c r="F147" s="129"/>
-      <c r="G147" s="129"/>
-      <c r="H147" s="129"/>
-      <c r="I147" s="129"/>
-      <c r="J147" s="129"/>
-      <c r="K147" s="129"/>
-      <c r="L147" s="129"/>
-      <c r="M147" s="129"/>
-      <c r="N147" s="126"/>
-      <c r="O147" s="126"/>
-      <c r="P147" s="126"/>
-      <c r="Q147" s="126"/>
+      <c r="C147" s="128"/>
+      <c r="D147" s="128"/>
+      <c r="E147" s="157"/>
+      <c r="F147" s="128"/>
+      <c r="G147" s="128"/>
+      <c r="H147" s="128"/>
+      <c r="I147" s="128"/>
+      <c r="J147" s="128"/>
+      <c r="K147" s="128"/>
+      <c r="L147" s="128"/>
+      <c r="M147" s="128"/>
+      <c r="N147" s="155"/>
+      <c r="O147" s="155"/>
+      <c r="P147" s="155"/>
+      <c r="Q147" s="155"/>
     </row>
     <row r="148" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A148" s="23" t="str">
@@ -15146,21 +15147,21 @@
       <c r="B148" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C148" s="129"/>
-      <c r="D148" s="129"/>
-      <c r="E148" s="131"/>
-      <c r="F148" s="129"/>
-      <c r="G148" s="129"/>
-      <c r="H148" s="129"/>
-      <c r="I148" s="129"/>
-      <c r="J148" s="129"/>
-      <c r="K148" s="129"/>
-      <c r="L148" s="129"/>
-      <c r="M148" s="129"/>
-      <c r="N148" s="126"/>
-      <c r="O148" s="126"/>
-      <c r="P148" s="126"/>
-      <c r="Q148" s="126"/>
+      <c r="C148" s="128"/>
+      <c r="D148" s="128"/>
+      <c r="E148" s="157"/>
+      <c r="F148" s="128"/>
+      <c r="G148" s="128"/>
+      <c r="H148" s="128"/>
+      <c r="I148" s="128"/>
+      <c r="J148" s="128"/>
+      <c r="K148" s="128"/>
+      <c r="L148" s="128"/>
+      <c r="M148" s="128"/>
+      <c r="N148" s="155"/>
+      <c r="O148" s="155"/>
+      <c r="P148" s="155"/>
+      <c r="Q148" s="155"/>
     </row>
     <row r="149" spans="1:17" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A149" s="23" t="str">
@@ -15170,21 +15171,21 @@
       <c r="B149" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C149" s="129"/>
-      <c r="D149" s="129"/>
-      <c r="E149" s="131"/>
-      <c r="F149" s="129"/>
-      <c r="G149" s="129"/>
-      <c r="H149" s="129"/>
-      <c r="I149" s="129"/>
-      <c r="J149" s="129"/>
-      <c r="K149" s="129"/>
-      <c r="L149" s="129"/>
-      <c r="M149" s="129"/>
-      <c r="N149" s="126"/>
-      <c r="O149" s="126"/>
-      <c r="P149" s="126"/>
-      <c r="Q149" s="126"/>
+      <c r="C149" s="128"/>
+      <c r="D149" s="128"/>
+      <c r="E149" s="157"/>
+      <c r="F149" s="128"/>
+      <c r="G149" s="128"/>
+      <c r="H149" s="128"/>
+      <c r="I149" s="128"/>
+      <c r="J149" s="128"/>
+      <c r="K149" s="128"/>
+      <c r="L149" s="128"/>
+      <c r="M149" s="128"/>
+      <c r="N149" s="155"/>
+      <c r="O149" s="155"/>
+      <c r="P149" s="155"/>
+      <c r="Q149" s="155"/>
     </row>
     <row r="150" spans="1:17" s="52" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="97" t="str">
@@ -15194,21 +15195,21 @@
       <c r="B150" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="C150" s="130"/>
-      <c r="D150" s="130"/>
-      <c r="E150" s="132"/>
-      <c r="F150" s="130"/>
-      <c r="G150" s="130"/>
-      <c r="H150" s="130"/>
-      <c r="I150" s="130"/>
-      <c r="J150" s="130"/>
-      <c r="K150" s="130"/>
-      <c r="L150" s="130"/>
-      <c r="M150" s="130"/>
-      <c r="N150" s="127"/>
-      <c r="O150" s="127"/>
-      <c r="P150" s="127"/>
-      <c r="Q150" s="127"/>
+      <c r="C150" s="136"/>
+      <c r="D150" s="136"/>
+      <c r="E150" s="158"/>
+      <c r="F150" s="136"/>
+      <c r="G150" s="136"/>
+      <c r="H150" s="136"/>
+      <c r="I150" s="136"/>
+      <c r="J150" s="136"/>
+      <c r="K150" s="136"/>
+      <c r="L150" s="136"/>
+      <c r="M150" s="136"/>
+      <c r="N150" s="156"/>
+      <c r="O150" s="156"/>
+      <c r="P150" s="156"/>
+      <c r="Q150" s="156"/>
     </row>
     <row r="151" spans="1:17" s="52" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A151" s="118"/>
@@ -17411,16 +17412,16 @@
       <c r="AG3" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="AL3" s="167" t="s">
+      <c r="AL3" s="149" t="s">
         <v>400</v>
       </c>
-      <c r="AM3" s="167"/>
-      <c r="AN3" s="167"/>
-      <c r="AO3" s="167" t="s">
+      <c r="AM3" s="149"/>
+      <c r="AN3" s="149"/>
+      <c r="AO3" s="149" t="s">
         <v>401</v>
       </c>
-      <c r="AP3" s="167"/>
-      <c r="AQ3" s="167"/>
+      <c r="AP3" s="149"/>
+      <c r="AQ3" s="149"/>
       <c r="AR3" s="13"/>
       <c r="AS3" s="13"/>
       <c r="AT3" s="13"/>
